--- a/NKE.xlsx
+++ b/NKE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4628214E-3895-4F88-9A55-628078AD98F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B45BBA6-548C-4AE6-99A4-B1C13B16932E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" xr2:uid="{B022B215-4C4C-4E36-8893-AFDEA07171F9}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{B022B215-4C4C-4E36-8893-AFDEA07171F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -910,7 +910,7 @@
     <t>Adidas, New Balance, Puma, Lulu Lemon, UA</t>
   </si>
   <si>
-    <t>FQ226</t>
+    <t>FQ326</t>
   </si>
 </sst>
 </file>
@@ -1466,16 +1466,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>4762</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>14287</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>33338</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>147638</xdr:rowOff>
+      <xdr:rowOff>142876</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1490,7 +1490,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="10977562" y="1171575"/>
+          <a:off x="11596687" y="1166813"/>
           <a:ext cx="14288" cy="3833813"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1923,7 +1923,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>58.85</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1940,7 +1940,7 @@
         <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>1479.5</v>
+        <v>1480.5</v>
       </c>
       <c r="J4" s="85" t="s">
         <v>282</v>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="I5" s="14">
         <f>I3*I4</f>
-        <v>87068.574999999997</v>
+        <v>71078.804999999993</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -1973,8 +1973,8 @@
         <v>5</v>
       </c>
       <c r="I6" s="14">
-        <f>6974+1371</f>
-        <v>8345</v>
+        <f>6660+1397</f>
+        <v>8057</v>
       </c>
       <c r="J6" s="85" t="s">
         <v>282</v>
@@ -1985,8 +1985,8 @@
         <v>6</v>
       </c>
       <c r="I7" s="14">
-        <f>7016+999</f>
-        <v>8015</v>
+        <f>7030+999</f>
+        <v>8029</v>
       </c>
       <c r="J7" s="85" t="s">
         <v>282</v>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I8" s="14">
         <f>I5+I7-I6</f>
-        <v>86738.574999999997</v>
+        <v>71050.804999999993</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2617,7 +2617,9 @@
       <c r="P9" s="5">
         <v>7659</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>7353</v>
+      </c>
       <c r="R9" s="5"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -2701,7 +2703,9 @@
       <c r="P10" s="5">
         <v>3906</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>3184</v>
+      </c>
       <c r="R10" s="5"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -2785,7 +2789,9 @@
       <c r="P11" s="5">
         <v>550</v>
       </c>
-      <c r="Q11" s="5"/>
+      <c r="Q11" s="5">
+        <v>468</v>
+      </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
@@ -2869,7 +2875,9 @@
       <c r="P12" s="5">
         <v>9</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>7</v>
+      </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -2965,7 +2973,9 @@
         <f>+SUM(P9:P12)</f>
         <v>12124</v>
       </c>
-      <c r="Q13" s="5"/>
+      <c r="Q13" s="5">
+        <v>11012</v>
+      </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
@@ -3055,7 +3065,9 @@
       <c r="P14" s="5">
         <v>300</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>264</v>
+      </c>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
@@ -3139,7 +3151,9 @@
       <c r="P15" s="5">
         <v>3</v>
       </c>
-      <c r="Q15" s="5"/>
+      <c r="Q15" s="5">
+        <v>3</v>
+      </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
@@ -3222,7 +3236,9 @@
       <c r="P16" s="8">
         <v>12427</v>
       </c>
-      <c r="Q16" s="8"/>
+      <c r="Q16" s="8">
+        <v>11279</v>
+      </c>
       <c r="R16" s="8"/>
       <c r="S16" s="8"/>
       <c r="T16" s="8">
@@ -3311,7 +3327,9 @@
       <c r="P17" s="5">
         <v>7382</v>
       </c>
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="5">
+        <v>6749</v>
+      </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
@@ -3372,7 +3390,7 @@
         <v>5720</v>
       </c>
       <c r="H18" s="5">
-        <f t="shared" ref="H18:P18" si="11">H16-H17</f>
+        <f t="shared" ref="H18:Q18" si="11">H16-H17</f>
         <v>5971</v>
       </c>
       <c r="I18" s="5">
@@ -3407,7 +3425,10 @@
         <f t="shared" si="11"/>
         <v>5045</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="5">
+        <f t="shared" si="11"/>
+        <v>4530</v>
+      </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
@@ -3496,7 +3517,9 @@
       <c r="P19" s="5">
         <v>1273</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="5">
+        <v>1090</v>
+      </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
@@ -3579,7 +3602,9 @@
       <c r="P20" s="5">
         <v>2766</v>
       </c>
-      <c r="Q20" s="5"/>
+      <c r="Q20" s="5">
+        <v>2887</v>
+      </c>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
@@ -3648,7 +3673,7 @@
         <v>4226</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" ref="J21:P21" si="14">J19+J20</f>
+        <f t="shared" ref="J21:Q21" si="14">J19+J20</f>
         <v>4088</v>
       </c>
       <c r="K21" s="5">
@@ -3675,7 +3700,10 @@
         <f t="shared" si="14"/>
         <v>4039</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="5">
+        <f t="shared" si="14"/>
+        <v>3977</v>
+      </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
@@ -3742,7 +3770,7 @@
         <v>1604</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" ref="H22:P22" si="21">H18-H21</f>
+        <f t="shared" ref="H22:Q22" si="21">H18-H21</f>
         <v>1825</v>
       </c>
       <c r="I22" s="5">
@@ -3777,7 +3805,10 @@
         <f t="shared" si="21"/>
         <v>1006</v>
       </c>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="5">
+        <f t="shared" si="21"/>
+        <v>553</v>
+      </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
@@ -3866,7 +3897,9 @@
       <c r="P23" s="5">
         <v>-9</v>
       </c>
-      <c r="Q23" s="5"/>
+      <c r="Q23" s="5">
+        <v>-15</v>
+      </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
@@ -3949,7 +3982,9 @@
       <c r="P24" s="5">
         <v>16</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="5">
+        <v>-82</v>
+      </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
@@ -4010,7 +4045,7 @@
         <v>1648</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:P25" si="24">H22-H23-H24</f>
+        <f t="shared" ref="H25:Q25" si="24">H22-H23-H24</f>
         <v>1922</v>
       </c>
       <c r="I25" s="5">
@@ -4045,7 +4080,10 @@
         <f t="shared" si="24"/>
         <v>999</v>
       </c>
-      <c r="Q25" s="5"/>
+      <c r="Q25" s="5">
+        <f t="shared" si="24"/>
+        <v>650</v>
+      </c>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
@@ -4134,7 +4172,9 @@
       <c r="P26" s="5">
         <v>207</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="5">
+        <v>130</v>
+      </c>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
@@ -4211,7 +4251,7 @@
         <v>1051</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27:P27" si="27">L25-L26</f>
+        <f t="shared" ref="L27:Q27" si="27">L25-L26</f>
         <v>1163</v>
       </c>
       <c r="M27" s="5">
@@ -4230,7 +4270,10 @@
         <f t="shared" si="27"/>
         <v>792</v>
       </c>
-      <c r="Q27" s="5"/>
+      <c r="Q27" s="5">
+        <f t="shared" si="27"/>
+        <v>520</v>
+      </c>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
@@ -4310,7 +4353,7 @@
         <v>35</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:P29" si="29">C27/C30</f>
+        <f t="shared" ref="C29:Q29" si="29">C27/C30</f>
         <v>0.92994376447237848</v>
       </c>
       <c r="D29" s="9">
@@ -4365,7 +4408,10 @@
         <f t="shared" si="29"/>
         <v>0.53531598513011147</v>
       </c>
-      <c r="Q29" s="9"/>
+      <c r="Q29" s="9">
+        <f t="shared" si="29"/>
+        <v>0.35123269165822357</v>
+      </c>
       <c r="R29" s="9"/>
       <c r="S29" s="5"/>
       <c r="T29" s="9">
@@ -4451,7 +4497,9 @@
       <c r="P30" s="5">
         <v>1479.5</v>
       </c>
-      <c r="Q30" s="5"/>
+      <c r="Q30" s="5">
+        <v>1480.5</v>
+      </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
@@ -4559,7 +4607,7 @@
         <v>-0.11060764494016495</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" ref="M32:P37" si="37">M9/I9-1</f>
+        <f t="shared" ref="M32:Q37" si="37">M9/I9-1</f>
         <v>-0.11688311688311692</v>
       </c>
       <c r="N32" s="10">
@@ -4574,7 +4622,10 @@
         <f t="shared" si="37"/>
         <v>5.2253429131288165E-4</v>
       </c>
-      <c r="Q32" s="10"/>
+      <c r="Q32" s="10">
+        <f t="shared" si="37"/>
+        <v>2.0116537180909999E-2</v>
+      </c>
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
       <c r="T32" s="10">
@@ -4652,7 +4703,10 @@
         <f t="shared" si="37"/>
         <v>4.4943820224719211E-2</v>
       </c>
-      <c r="Q33" s="10"/>
+      <c r="Q33" s="10">
+        <f t="shared" si="37"/>
+        <v>-2.8186658315064728E-3</v>
+      </c>
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
       <c r="T33" s="10">
@@ -4729,7 +4783,10 @@
         <f t="shared" si="37"/>
         <v>1.1029411764705843E-2</v>
       </c>
-      <c r="Q34" s="10"/>
+      <c r="Q34" s="10">
+        <f t="shared" si="37"/>
+        <v>-1.8867924528301883E-2</v>
+      </c>
       <c r="R34" s="10"/>
       <c r="T34" s="10">
         <f t="shared" ref="T34:Z34" si="38">T9/T16</f>
@@ -4812,7 +4869,10 @@
         <f t="shared" si="37"/>
         <v>-0.30769230769230771</v>
       </c>
-      <c r="Q35" s="10"/>
+      <c r="Q35" s="10">
+        <f t="shared" si="37"/>
+        <v>-0.41666666666666663</v>
+      </c>
       <c r="R35" s="10"/>
       <c r="T35" s="10">
         <f t="shared" ref="T35:Z35" si="40">T10/T16</f>
@@ -4895,7 +4955,10 @@
         <f t="shared" si="37"/>
         <v>1.4560669456066933E-2</v>
       </c>
-      <c r="Q36" s="10"/>
+      <c r="Q36" s="10">
+        <f t="shared" si="37"/>
+        <v>1.120293847566578E-2</v>
+      </c>
       <c r="R36" s="10"/>
       <c r="T36" s="10">
         <f t="shared" ref="T36:Z36" si="42">T11/T16</f>
@@ -4978,7 +5041,10 @@
         <f t="shared" si="37"/>
         <v>-0.30069930069930073</v>
       </c>
-      <c r="Q37" s="10"/>
+      <c r="Q37" s="10">
+        <f t="shared" si="37"/>
+        <v>-0.3481481481481481</v>
+      </c>
       <c r="R37" s="10"/>
       <c r="T37" s="10">
         <f t="shared" ref="T37:Z37" si="44">T14/T16</f>
@@ -5034,7 +5100,7 @@
         <v>-2.8238828389034909E-2</v>
       </c>
       <c r="H38" s="13">
-        <f t="shared" ref="H38:P38" si="46">H16/D16-1</f>
+        <f t="shared" ref="H38:Q38" si="46">H16/D16-1</f>
         <v>5.482538490424238E-3</v>
       </c>
       <c r="I38" s="13">
@@ -5069,7 +5135,10 @@
         <f t="shared" si="46"/>
         <v>5.9090173223248499E-3</v>
       </c>
-      <c r="Q38" s="13"/>
+      <c r="Q38" s="13">
+        <f t="shared" si="46"/>
+        <v>8.8739018546446502E-4</v>
+      </c>
       <c r="R38" s="13"/>
       <c r="S38" s="13"/>
       <c r="T38" s="12" t="s">
@@ -5165,39 +5234,42 @@
         <f t="shared" si="49"/>
         <v>0.40597086988009978</v>
       </c>
-      <c r="Q39" s="10"/>
+      <c r="Q39" s="10">
+        <f t="shared" ref="Q39" si="50">Q18/Q16</f>
+        <v>0.40163135029701214</v>
+      </c>
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
       <c r="T39" s="10">
-        <f t="shared" ref="T39:AA39" si="50">T18/T16</f>
+        <f t="shared" ref="T39:AA39" si="51">T18/T16</f>
         <v>0.43838777921257244</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44671114860546568</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.43421650669732376</v>
       </c>
       <c r="W39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44820153576721</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.45983729394134021</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.43524610969014194</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44560180678322497</v>
       </c>
       <c r="AA39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.42734673605562634</v>
       </c>
       <c r="AB39" s="10"/>
@@ -5207,94 +5279,97 @@
         <v>40</v>
       </c>
       <c r="C40" s="10">
-        <f t="shared" ref="C40:N40" si="51">C22/C16</f>
+        <f t="shared" ref="C40:N40" si="52">C22/C16</f>
         <v>0.13360132419011586</v>
       </c>
       <c r="D40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.11918888471648517</v>
       </c>
       <c r="E40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.11396287328490719</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.23815821110843952</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.12396630342375763</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.1363161039737078</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.10749054630300105</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.12264001269236871</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.10432306497540772</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.1120284927958556</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>6.9926346614606436E-2</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>2.8926736955934035E-2</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" ref="O40:P40" si="52">O22/O16</f>
+        <f t="shared" ref="O40:P40" si="53">O22/O16</f>
         <v>7.909556313993174E-2</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>8.095276414259274E-2</v>
       </c>
-      <c r="Q40" s="10"/>
+      <c r="Q40" s="10">
+        <f t="shared" ref="Q40" si="54">Q22/Q16</f>
+        <v>4.9029169252593312E-2</v>
+      </c>
       <c r="R40" s="10"/>
       <c r="S40" s="10"/>
       <c r="T40" s="10">
-        <f t="shared" ref="T40:AA40" si="53">T22/T16</f>
+        <f t="shared" ref="T40:AA40" si="55">T22/T16</f>
         <v>0.12212544989971701</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.12199299537285579</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>8.3282089671951443E-2</v>
       </c>
       <c r="W40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.15575463649018814</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.14290301862556198</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.11548899779370131</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>0.12287294108484872</v>
       </c>
       <c r="AA40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="55"/>
         <v>7.9941264117126265E-2</v>
       </c>
       <c r="AB40" s="10"/>
@@ -5304,94 +5379,97 @@
         <v>41</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" ref="C41:N41" si="54">C27/C16</f>
+        <f t="shared" ref="C41:N41" si="56">C27/C16</f>
         <v>0.11570899345787027</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.9962448366503948E-2</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0.10008071025020178</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0.24128396249098341</v>
       </c>
       <c r="G41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0.11206430172347168</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0.11786674634000598</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.4295599002333252E-2</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>0.11899095668729176</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.0689446889291564E-2</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>9.4139549943338188E-2</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>7.045878072588517E-2</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="56"/>
         <v>1.9014147967919257E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" ref="O41:P41" si="55">O27/O16</f>
+        <f t="shared" ref="O41:P41" si="57">O27/O16</f>
         <v>6.2030716723549491E-2</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="57"/>
         <v>6.3732196024784749E-2</v>
       </c>
-      <c r="Q41" s="10"/>
+      <c r="Q41" s="10">
+        <f t="shared" ref="Q41" si="58">Q27/Q16</f>
+        <v>4.6103377959038919E-2</v>
+      </c>
       <c r="R41" s="10"/>
       <c r="S41" s="10"/>
       <c r="T41" s="10">
-        <f t="shared" ref="T41:AA41" si="56">T27/T16</f>
+        <f t="shared" ref="T41:AA41" si="59">T27/T16</f>
         <v>5.3108772701046789E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.10299869621903521</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>6.7882255434056085E-2</v>
       </c>
       <c r="W41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.12858682473393507</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.12943695140226932</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>9.8990569537458259E-2</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>0.11097698687745804</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="59"/>
         <v>6.9511326092120324E-2</v>
       </c>
       <c r="AB41" s="10"/>
@@ -5401,86 +5479,89 @@
         <v>42</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" ref="C42:N42" si="57">C26/C25</f>
+        <f t="shared" ref="C42:N42" si="60">C26/C25</f>
         <v>0.19693654266958424</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.19333333333333333</v>
       </c>
       <c r="E42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.16046039268788084</v>
       </c>
       <c r="F42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>-0.18337264150943397</v>
       </c>
       <c r="G42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.12014563106796117</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.17898022892819979</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.16524216524216523</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.13093858632676708</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.19586840091813312</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.1786723163841808</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>5.9241706161137442E-2</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="60"/>
         <v>0.33647798742138363</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" ref="O42:P42" si="58">O26/O25</f>
+        <f t="shared" ref="O42:P42" si="61">O26/O25</f>
         <v>0.21149674620390455</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="61"/>
         <v>0.2072072072072072</v>
       </c>
-      <c r="Q42" s="10"/>
+      <c r="Q42" s="10">
+        <f t="shared" ref="Q42" si="62">Q26/Q25</f>
+        <v>0.2</v>
+      </c>
       <c r="R42" s="10"/>
       <c r="S42" s="10"/>
       <c r="T42" s="10">
-        <f t="shared" ref="T42:Y42" si="59">T26/T25</f>
+        <f t="shared" ref="T42:Y42" si="63">T26/T25</f>
         <v>0.55306358381502885</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.16079983336804832</v>
       </c>
       <c r="V42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.12054035330793211</v>
       </c>
       <c r="W42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.14021918630836211</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>9.0963764847391368E-2</v>
       </c>
       <c r="Y42" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>0.18238993710691823</v>
       </c>
       <c r="Z42" s="10">
@@ -5852,31 +5933,31 @@
         <v>51</v>
       </c>
       <c r="C52" s="8">
-        <f t="shared" ref="C52:I52" si="60">SUM(C47:C51)</f>
+        <f t="shared" ref="C52:I52" si="64">SUM(C47:C51)</f>
         <v>0</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="E52" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>25202</v>
       </c>
       <c r="F52" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>0</v>
       </c>
       <c r="G52" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>24250</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>24631</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="60"/>
+        <f t="shared" si="64"/>
         <v>24753</v>
       </c>
       <c r="J52" s="8">
@@ -5896,31 +5977,31 @@
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
       <c r="T52" s="8">
-        <f t="shared" ref="T52:Z52" si="61">SUM(T47:T51)</f>
+        <f t="shared" ref="T52:Z52" si="65">SUM(T47:T51)</f>
         <v>15134</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>16525</v>
       </c>
       <c r="V52" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>20556</v>
       </c>
       <c r="W52" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>26291</v>
       </c>
       <c r="X52" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>28213</v>
       </c>
       <c r="Y52" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>25202</v>
       </c>
       <c r="Z52" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="65"/>
         <v>25382</v>
       </c>
       <c r="AA52" s="5"/>
@@ -6248,31 +6329,31 @@
         <v>57</v>
       </c>
       <c r="C58" s="8">
-        <f t="shared" ref="C58:I58" si="62">SUM(C53:C57)</f>
+        <f t="shared" ref="C58:I58" si="66">SUM(C53:C57)</f>
         <v>0</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="E58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>12329</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="G58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>12536</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>12572</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="66"/>
         <v>12603</v>
       </c>
       <c r="J58" s="8">
@@ -6292,31 +6373,31 @@
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
       <c r="T58" s="8">
-        <f t="shared" ref="T58:Z58" si="63">SUM(T53:T57)</f>
+        <f t="shared" ref="T58:Z58" si="67">SUM(T53:T57)</f>
         <v>7402</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>7192</v>
       </c>
       <c r="V58" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>10786</v>
       </c>
       <c r="W58" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>11449</v>
       </c>
       <c r="X58" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>12108</v>
       </c>
       <c r="Y58" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>12329</v>
       </c>
       <c r="Z58" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>12728</v>
       </c>
       <c r="AA58" s="5"/>
@@ -6369,31 +6450,31 @@
         <v>58</v>
       </c>
       <c r="C60" s="8">
-        <f t="shared" ref="C60:I60" si="64">C58+C52</f>
+        <f t="shared" ref="C60:I60" si="68">C58+C52</f>
         <v>0</v>
       </c>
       <c r="D60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="E60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>37531</v>
       </c>
       <c r="F60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="G60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>36786</v>
       </c>
       <c r="H60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>37203</v>
       </c>
       <c r="I60" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>37356</v>
       </c>
       <c r="J60" s="8">
@@ -6413,31 +6494,31 @@
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
       <c r="T60" s="8">
-        <f t="shared" ref="T60:Z60" si="65">T58+T52</f>
+        <f t="shared" ref="T60:Z60" si="69">T58+T52</f>
         <v>22536</v>
       </c>
       <c r="U60" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>23717</v>
       </c>
       <c r="V60" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>31342</v>
       </c>
       <c r="W60" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>37740</v>
       </c>
       <c r="X60" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>40321</v>
       </c>
       <c r="Y60" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>37531</v>
       </c>
       <c r="Z60" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>38110</v>
       </c>
       <c r="AA60" s="5"/>
@@ -6635,7 +6716,7 @@
         <v>6</v>
       </c>
       <c r="Z64" s="5">
-        <f t="shared" ref="Z64" si="66">I64</f>
+        <f t="shared" ref="Z64" si="70">I64</f>
         <v>6</v>
       </c>
       <c r="AA64" s="5"/>
@@ -6901,31 +6982,31 @@
         <v>51</v>
       </c>
       <c r="C69" s="8">
-        <f t="shared" ref="C69:I69" si="67">SUM(C63:C68)</f>
+        <f t="shared" ref="C69:I69" si="71">SUM(C63:C68)</f>
         <v>0</v>
       </c>
       <c r="D69" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="E69" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>9256</v>
       </c>
       <c r="F69" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="G69" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>8461</v>
       </c>
       <c r="H69" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>8999</v>
       </c>
       <c r="I69" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>9029</v>
       </c>
       <c r="J69" s="8">
@@ -6945,31 +7026,31 @@
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
       <c r="T69" s="8">
-        <f t="shared" ref="T69:V69" si="68">SUM(T63:T68)</f>
+        <f t="shared" ref="T69:V69" si="72">SUM(T63:T68)</f>
         <v>6040</v>
       </c>
       <c r="U69" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>7866</v>
       </c>
       <c r="V69" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>8284</v>
       </c>
       <c r="W69" s="8">
-        <f t="shared" ref="W69" si="69">SUM(W63:W68)</f>
+        <f t="shared" ref="W69" si="73">SUM(W63:W68)</f>
         <v>9674</v>
       </c>
       <c r="X69" s="8">
-        <f t="shared" ref="X69" si="70">SUM(X63:X68)</f>
+        <f t="shared" ref="X69" si="74">SUM(X63:X68)</f>
         <v>10730</v>
       </c>
       <c r="Y69" s="8">
-        <f t="shared" ref="Y69" si="71">SUM(Y63:Y68)</f>
+        <f t="shared" ref="Y69" si="75">SUM(Y63:Y68)</f>
         <v>9256</v>
       </c>
       <c r="Z69" s="8">
-        <f t="shared" ref="Z69" si="72">SUM(Z63:Z68)</f>
+        <f t="shared" ref="Z69" si="76">SUM(Z63:Z68)</f>
         <v>10593</v>
       </c>
       <c r="AA69" s="5"/>
@@ -7173,31 +7254,31 @@
         <v>69</v>
       </c>
       <c r="C73" s="8">
-        <f t="shared" ref="C73:I73" si="73">SUM(C70:C72)</f>
+        <f t="shared" ref="C73:I73" si="77">SUM(C70:C72)</f>
         <v>0</v>
       </c>
       <c r="D73" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="E73" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>14271</v>
       </c>
       <c r="F73" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="G73" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>14354</v>
       </c>
       <c r="H73" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>14058</v>
       </c>
       <c r="I73" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>14101</v>
       </c>
       <c r="J73" s="8">
@@ -7217,31 +7298,31 @@
       <c r="R73" s="5"/>
       <c r="S73" s="5"/>
       <c r="T73" s="8">
-        <f t="shared" ref="T73:Z73" si="74">SUM(T70:T72)</f>
+        <f t="shared" ref="T73:Z73" si="78">SUM(T70:T72)</f>
         <v>6684</v>
       </c>
       <c r="U73" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>6811</v>
       </c>
       <c r="V73" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>15003</v>
       </c>
       <c r="W73" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>15299</v>
       </c>
       <c r="X73" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>14310</v>
       </c>
       <c r="Y73" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>14271</v>
       </c>
       <c r="Z73" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>13087</v>
       </c>
       <c r="AA73" s="5"/>
@@ -7294,31 +7375,31 @@
         <v>70</v>
       </c>
       <c r="C75" s="8">
-        <f t="shared" ref="C75:I75" si="75">C73+C69</f>
+        <f t="shared" ref="C75:I75" si="79">C73+C69</f>
         <v>0</v>
       </c>
       <c r="D75" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="E75" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>23527</v>
       </c>
       <c r="F75" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="G75" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>22815</v>
       </c>
       <c r="H75" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>23057</v>
       </c>
       <c r="I75" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>23130</v>
       </c>
       <c r="J75" s="8">
@@ -7338,31 +7419,31 @@
       <c r="R75" s="5"/>
       <c r="S75" s="5"/>
       <c r="T75" s="8">
-        <f t="shared" ref="T75:Z75" si="76">T73+T69</f>
+        <f t="shared" ref="T75:Z75" si="80">T73+T69</f>
         <v>12724</v>
       </c>
       <c r="U75" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>14677</v>
       </c>
       <c r="V75" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>23287</v>
       </c>
       <c r="W75" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>24973</v>
       </c>
       <c r="X75" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>25040</v>
       </c>
       <c r="Y75" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>23527</v>
       </c>
       <c r="Z75" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>23680</v>
       </c>
       <c r="AA75" s="5"/>
@@ -7753,31 +7834,31 @@
         <v>77</v>
       </c>
       <c r="C83" s="8">
-        <f t="shared" ref="C83:I83" si="77">SUM(C78:C82)</f>
+        <f t="shared" ref="C83:I83" si="81">SUM(C78:C82)</f>
         <v>0</v>
       </c>
       <c r="D83" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="E83" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>14004</v>
       </c>
       <c r="F83" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="G83" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>13971</v>
       </c>
       <c r="H83" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>14146</v>
       </c>
       <c r="I83" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>14226</v>
       </c>
       <c r="J83" s="8">
@@ -7796,31 +7877,31 @@
       <c r="R83" s="5"/>
       <c r="S83" s="5"/>
       <c r="T83" s="8">
-        <f t="shared" ref="T83:Z83" si="78">SUM(T78:T82)</f>
+        <f t="shared" ref="T83:Z83" si="82">SUM(T78:T82)</f>
         <v>9812</v>
       </c>
       <c r="U83" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>9040</v>
       </c>
       <c r="V83" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>8055</v>
       </c>
       <c r="W83" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>12767</v>
       </c>
       <c r="X83" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>15281</v>
       </c>
       <c r="Y83" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>14004</v>
       </c>
       <c r="Z83" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>14430</v>
       </c>
       <c r="AA83" s="5"/>
@@ -7873,19 +7954,19 @@
         <v>78</v>
       </c>
       <c r="C85" s="8">
-        <f t="shared" ref="C85:I85" si="79">C83+C75</f>
+        <f t="shared" ref="C85:I85" si="83">C83+C75</f>
         <v>0</v>
       </c>
       <c r="D85" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="E85" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>37531</v>
       </c>
       <c r="F85" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="G85" s="8">
@@ -7893,11 +7974,11 @@
         <v>36786</v>
       </c>
       <c r="H85" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>37203</v>
       </c>
       <c r="I85" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>37356</v>
       </c>
       <c r="J85" s="8">
@@ -7921,27 +8002,27 @@
         <v>22536</v>
       </c>
       <c r="U85" s="8">
-        <f t="shared" ref="U85:Z85" si="80">U83+U75</f>
+        <f t="shared" ref="U85:Z85" si="84">U83+U75</f>
         <v>23717</v>
       </c>
       <c r="V85" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>31342</v>
       </c>
       <c r="W85" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>37740</v>
       </c>
       <c r="X85" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>40321</v>
       </c>
       <c r="Y85" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>37531</v>
       </c>
       <c r="Z85" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>38110</v>
       </c>
       <c r="AA85" s="5"/>
@@ -8035,35 +8116,35 @@
         <v>80</v>
       </c>
       <c r="C88" s="5">
-        <f t="shared" ref="C88:J88" si="81">C27</f>
+        <f t="shared" ref="C88:J88" si="85">C27</f>
         <v>1468</v>
       </c>
       <c r="D88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>1331</v>
       </c>
       <c r="E88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>1240</v>
       </c>
       <c r="F88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>2007</v>
       </c>
       <c r="G88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>1450</v>
       </c>
       <c r="H88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>1578</v>
       </c>
       <c r="I88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>1172</v>
       </c>
       <c r="J88" s="5">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>1500</v>
       </c>
       <c r="K88" s="5"/>
@@ -8076,31 +8157,31 @@
       <c r="R88" s="5"/>
       <c r="S88" s="5"/>
       <c r="T88" s="5">
-        <f t="shared" ref="T88:Z88" si="82">T27</f>
+        <f t="shared" ref="T88:Z88" si="86">T27</f>
         <v>1933</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>4029</v>
       </c>
       <c r="V88" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>2539</v>
       </c>
       <c r="W88" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>5727</v>
       </c>
       <c r="X88" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>6046</v>
       </c>
       <c r="Y88" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>5070</v>
       </c>
       <c r="Z88" s="5">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>5700</v>
       </c>
       <c r="AA88" s="5"/>
@@ -8642,31 +8723,31 @@
         <v>92</v>
       </c>
       <c r="C99" s="5">
-        <f t="shared" ref="C99:I99" si="83">SUM(C95:C98)</f>
+        <f t="shared" ref="C99:I99" si="87">SUM(C95:C98)</f>
         <v>0</v>
       </c>
       <c r="D99" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="E99" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="F99" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="H99" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0</v>
       </c>
       <c r="I99" s="5">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>-285</v>
       </c>
       <c r="J99" s="5">
@@ -8683,31 +8764,31 @@
       <c r="R99" s="5"/>
       <c r="S99" s="5"/>
       <c r="T99" s="5">
-        <f t="shared" ref="T99:Z99" si="84">SUM(T95:T98)</f>
+        <f t="shared" ref="T99:Z99" si="88">SUM(T95:T98)</f>
         <v>1482</v>
       </c>
       <c r="U99" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>562</v>
       </c>
       <c r="V99" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>-1245</v>
       </c>
       <c r="W99" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>45</v>
       </c>
       <c r="X99" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>-1660</v>
       </c>
       <c r="Y99" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>-513</v>
       </c>
       <c r="Z99" s="5">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>716</v>
       </c>
       <c r="AA99" s="5"/>
@@ -8725,31 +8806,31 @@
         <v>91</v>
       </c>
       <c r="C100" s="8">
-        <f t="shared" ref="C100:I100" si="85">C88+SUM(C89:C93)+C99</f>
+        <f t="shared" ref="C100:I100" si="89">C88+SUM(C89:C93)+C99</f>
         <v>1468</v>
       </c>
       <c r="D100" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1331</v>
       </c>
       <c r="E100" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1240</v>
       </c>
       <c r="F100" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>2007</v>
       </c>
       <c r="G100" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1450</v>
       </c>
       <c r="H100" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1578</v>
       </c>
       <c r="I100" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1783</v>
       </c>
       <c r="J100" s="8">
@@ -8766,31 +8847,31 @@
       <c r="R100" s="5"/>
       <c r="S100" s="5"/>
       <c r="T100" s="8">
-        <f t="shared" ref="T100:Z100" si="86">T88+SUM(T89:T93)+T99</f>
+        <f t="shared" ref="T100:Z100" si="90">T88+SUM(T89:T93)+T99</f>
         <v>4955</v>
       </c>
       <c r="U100" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>5903</v>
       </c>
       <c r="V100" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>2485</v>
       </c>
       <c r="W100" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>6657</v>
       </c>
       <c r="X100" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>5188</v>
       </c>
       <c r="Y100" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>5841</v>
       </c>
       <c r="Z100" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="90"/>
         <v>7429</v>
       </c>
       <c r="AA100" s="5"/>
@@ -9068,31 +9149,31 @@
         <v>106</v>
       </c>
       <c r="C106" s="8">
-        <f t="shared" ref="C106:I106" si="87">SUM(C101:C105)</f>
+        <f t="shared" ref="C106:I106" si="91">SUM(C101:C105)</f>
         <v>0</v>
       </c>
       <c r="D106" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="E106" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="F106" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="G106" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="H106" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="I106" s="8">
-        <f t="shared" si="87"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="J106" s="8">
@@ -9109,31 +9190,31 @@
       <c r="R106" s="5"/>
       <c r="S106" s="5"/>
       <c r="T106" s="8">
-        <f t="shared" ref="T106:Z106" si="88">SUM(T101:T105)</f>
+        <f t="shared" ref="T106:Z106" si="92">SUM(T101:T105)</f>
         <v>276</v>
       </c>
       <c r="U106" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>-264</v>
       </c>
       <c r="V106" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>-1028</v>
       </c>
       <c r="W106" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>-3800</v>
       </c>
       <c r="X106" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>-1524</v>
       </c>
       <c r="Y106" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>564</v>
       </c>
       <c r="Z106" s="8">
-        <f t="shared" si="88"/>
+        <f t="shared" si="92"/>
         <v>894</v>
       </c>
       <c r="AA106" s="5"/>
@@ -9519,31 +9600,31 @@
         <v>0</v>
       </c>
       <c r="D114" s="8">
-        <f t="shared" ref="D114:J114" si="89">SUM(D108:D113)</f>
+        <f t="shared" ref="D114:J114" si="93">SUM(D108:D113)</f>
         <v>0</v>
       </c>
       <c r="E114" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="F114" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="G114" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="H114" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="I114" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="J114" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="K114" s="8"/>
@@ -9556,23 +9637,23 @@
       <c r="R114" s="5"/>
       <c r="S114" s="5"/>
       <c r="T114" s="8">
-        <f t="shared" ref="T114:X114" si="90">SUM(T107:T113)</f>
+        <f t="shared" ref="T114:X114" si="94">SUM(T107:T113)</f>
         <v>-4835</v>
       </c>
       <c r="U114" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>-5293</v>
       </c>
       <c r="V114" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>2491</v>
       </c>
       <c r="W114" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>-1459</v>
       </c>
       <c r="X114" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="94"/>
         <v>-4836</v>
       </c>
       <c r="Y114" s="8">
@@ -9580,7 +9661,7 @@
         <v>-7447</v>
       </c>
       <c r="Z114" s="8">
-        <f t="shared" ref="Z114" si="91">SUM(Z108:Z113)</f>
+        <f t="shared" ref="Z114" si="95">SUM(Z108:Z113)</f>
         <v>-5888</v>
       </c>
       <c r="AA114" s="5"/>
@@ -9654,31 +9735,31 @@
         <v>1468</v>
       </c>
       <c r="D116" s="8">
-        <f t="shared" ref="D116:J116" si="92">D100+D106+D114+D115</f>
+        <f t="shared" ref="D116:J116" si="96">D100+D106+D114+D115</f>
         <v>1331</v>
       </c>
       <c r="E116" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1240</v>
       </c>
       <c r="F116" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>2007</v>
       </c>
       <c r="G116" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1450</v>
       </c>
       <c r="H116" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1578</v>
       </c>
       <c r="I116" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1783</v>
       </c>
       <c r="J116" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="96"/>
         <v>1500</v>
       </c>
       <c r="K116" s="8"/>
@@ -9691,31 +9772,31 @@
       <c r="R116" s="5"/>
       <c r="S116" s="5"/>
       <c r="T116" s="8">
-        <f t="shared" ref="T116" si="93">T100+T106+T114+T115</f>
+        <f t="shared" ref="T116" si="97">T100+T106+T114+T115</f>
         <v>441</v>
       </c>
       <c r="U116" s="8">
-        <f t="shared" ref="U116" si="94">U100+U106+U114+U115</f>
+        <f t="shared" ref="U116" si="98">U100+U106+U114+U115</f>
         <v>217</v>
       </c>
       <c r="V116" s="8">
-        <f t="shared" ref="V116" si="95">V100+V106+V114+V115</f>
+        <f t="shared" ref="V116" si="99">V100+V106+V114+V115</f>
         <v>3882</v>
       </c>
       <c r="W116" s="8">
-        <f t="shared" ref="W116" si="96">W100+W106+W114+W115</f>
+        <f t="shared" ref="W116" si="100">W100+W106+W114+W115</f>
         <v>1541</v>
       </c>
       <c r="X116" s="8">
-        <f t="shared" ref="X116" si="97">X100+X106+X114+X115</f>
+        <f t="shared" ref="X116" si="101">X100+X106+X114+X115</f>
         <v>-1315</v>
       </c>
       <c r="Y116" s="8">
-        <f t="shared" ref="Y116" si="98">Y100+Y106+Y114+Y115</f>
+        <f t="shared" ref="Y116" si="102">Y100+Y106+Y114+Y115</f>
         <v>-1133</v>
       </c>
       <c r="Z116" s="8">
-        <f t="shared" ref="Z116" si="99">Z100+Z106+Z114+Z115</f>
+        <f t="shared" ref="Z116" si="103">Z100+Z106+Z114+Z115</f>
         <v>2419</v>
       </c>
       <c r="AA116" s="5"/>
@@ -11351,7 +11432,7 @@
       </c>
       <c r="I32" s="5">
         <f>Main!I5</f>
-        <v>87068.574999999997</v>
+        <v>71078.804999999993</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.2">
@@ -11417,7 +11498,7 @@
       </c>
       <c r="I34" s="5">
         <f>I32+I33</f>
-        <v>86961.574999999997</v>
+        <v>70971.804999999993</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.2">
@@ -11462,15 +11543,15 @@
       </c>
       <c r="I36" s="30">
         <f>I32/Model!Z27</f>
-        <v>15.275188596491228</v>
+        <v>12.469965789473683</v>
       </c>
       <c r="L36" s="30">
         <f>AVERAGE(C36:I36)</f>
-        <v>38.06445044430972</v>
+        <v>37.663704329021492</v>
       </c>
       <c r="M36" s="30">
         <f>AVERAGE(D36:J36)</f>
-        <v>34.00236305337534</v>
+        <v>33.534825918872421</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.2">
@@ -11502,15 +11583,15 @@
       </c>
       <c r="I37" s="30">
         <f>I36/((Model!Z27/Model!Y27-1)*100)</f>
-        <v>1.2292889870509611</v>
+        <v>1.0035353421052633</v>
       </c>
       <c r="L37" s="30">
         <f t="shared" ref="L37:M41" si="11">AVERAGE(C37:I37)</f>
-        <v>0.5654803859980726</v>
+        <v>0.52785477850712292</v>
       </c>
       <c r="M37" s="30">
         <f t="shared" si="11"/>
-        <v>0.5654803859980726</v>
+        <v>0.52785477850712292</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.2">
@@ -11543,15 +11624,15 @@
       </c>
       <c r="I38" s="30">
         <f>Ratios!I32/Model!Z83</f>
-        <v>6.0338582813582811</v>
+        <v>4.9257661122661114</v>
       </c>
       <c r="L38" s="30">
         <f t="shared" si="11"/>
-        <v>12.966255245759609</v>
+        <v>12.807956364460727</v>
       </c>
       <c r="M38" s="30">
         <f t="shared" si="11"/>
-        <v>13.077245601149023</v>
+        <v>12.892563572966997</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.2">
@@ -11584,15 +11665,15 @@
       </c>
       <c r="I39" s="30">
         <f>I32/(Model!Z83-Model!Z55-Model!Z56)</f>
-        <v>6.2499874380877181</v>
+        <v>5.1022040772378148</v>
       </c>
       <c r="L39" s="30">
         <f t="shared" si="11"/>
-        <v>13.587477865099354</v>
+        <v>13.423508813549367</v>
       </c>
       <c r="M39" s="30">
         <f t="shared" si="11"/>
-        <v>13.705987729615671</v>
+        <v>13.514690502807355</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
@@ -11625,15 +11706,15 @@
       </c>
       <c r="I40" s="30">
         <f>I32/Model!Z100</f>
-        <v>11.72009355229506</v>
+        <v>9.5677486875757154</v>
       </c>
       <c r="L40" s="30">
         <f t="shared" si="11"/>
-        <v>30.161215208081568</v>
+        <v>29.853737370264522</v>
       </c>
       <c r="M40" s="30">
         <f t="shared" si="11"/>
-        <v>31.12852597455101</v>
+        <v>30.76980183043112</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.2">
@@ -11666,15 +11747,15 @@
       </c>
       <c r="I41" s="30">
         <f>I32/Model!Z16</f>
-        <v>1.6951944044235037</v>
+        <v>1.3838792297807716</v>
       </c>
       <c r="L41" s="30">
         <f t="shared" si="11"/>
-        <v>3.4228006730472624</v>
+        <v>3.3783270766697293</v>
       </c>
       <c r="M41" s="30">
         <f t="shared" si="11"/>
-        <v>3.4406089348453666</v>
+        <v>3.3887230724049111</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.2">
@@ -11712,15 +11793,15 @@
       </c>
       <c r="I43" s="30">
         <f>I34/Model!Z16</f>
-        <v>1.6931111522136988</v>
+        <v>1.3817959775709667</v>
       </c>
       <c r="L43" s="30">
         <f t="shared" ref="L43:M46" si="12">AVERAGE(C43:I43)</f>
-        <v>3.4238668542976711</v>
+        <v>3.379393257920138</v>
       </c>
       <c r="M43" s="30">
         <f t="shared" si="12"/>
-        <v>3.4484238673617735</v>
+        <v>3.3965380049213181</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.2">
@@ -11753,15 +11834,15 @@
       </c>
       <c r="I44" s="30">
         <f>I34/Model!Z22</f>
-        <v>13.779365393756931</v>
+        <v>11.245730470606876</v>
       </c>
       <c r="L44" s="30">
         <f t="shared" si="12"/>
-        <v>28.66144450731715</v>
+        <v>28.299496661152855</v>
       </c>
       <c r="M44" s="30">
         <f t="shared" si="12"/>
-        <v>28.966823156215426</v>
+        <v>28.544550669023749</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.2">
@@ -11794,15 +11875,15 @@
       </c>
       <c r="I45" s="30">
         <f>Ratios!I34/(Model!Z22+Model!Y89+Model!Y92)</f>
-        <v>12.128532078103207</v>
+        <v>9.8984386331938623</v>
       </c>
       <c r="L45" s="30">
         <f t="shared" si="12"/>
-        <v>24.139922312528267</v>
+        <v>23.82133753468408</v>
       </c>
       <c r="M45" s="30">
         <f t="shared" si="12"/>
-        <v>24.354860751570786</v>
+        <v>23.983178510752566</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
@@ -11835,15 +11916,15 @@
       </c>
       <c r="I46" s="30">
         <f>I34/(Model!Z22*(1-Model!Z42)+Model!Z89+Model!Z92+Model!Y104+Model!Y98)</f>
-        <v>16.12486811632094</v>
+        <v>13.159961691152063</v>
       </c>
       <c r="L46" s="30">
         <f t="shared" si="12"/>
-        <v>29.377375249353161</v>
+        <v>28.95381718861475</v>
       </c>
       <c r="M46" s="30">
         <f t="shared" si="12"/>
-        <v>27.073824583025004</v>
+        <v>26.579673512163527</v>
       </c>
     </row>
   </sheetData>
@@ -11931,7 +12012,7 @@
       </c>
       <c r="J3" s="34">
         <f>Main!I3</f>
-        <v>58.85</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -11946,7 +12027,7 @@
       </c>
       <c r="J4" s="36">
         <f ca="1">V60</f>
-        <v>69.410176430719147</v>
+        <v>69.159308361532567</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.2">
@@ -11961,7 +12042,7 @@
       </c>
       <c r="J5" s="38">
         <f ca="1">J4/J3-1</f>
-        <v>0.17944225030958627</v>
+        <v>0.44051881611190513</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.2">
@@ -13532,7 +13613,7 @@
       <c r="Q56" s="11"/>
       <c r="V56" s="11">
         <f>Main!I6</f>
-        <v>8345</v>
+        <v>8057</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
@@ -13560,7 +13641,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="64">
         <f>Main!I7</f>
-        <v>8015</v>
+        <v>8029</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
@@ -13573,7 +13654,7 @@
       <c r="Q58" s="11"/>
       <c r="V58" s="11">
         <f ca="1">V55+V56-V57</f>
-        <v>102692.35602924897</v>
+        <v>102390.35602924897</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
@@ -13601,7 +13682,7 @@
       <c r="U59" s="64"/>
       <c r="V59" s="64">
         <f>Main!I4</f>
-        <v>1479.5</v>
+        <v>1480.5</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
@@ -13610,7 +13691,7 @@
       </c>
       <c r="V60" s="30">
         <f ca="1">V58/V59</f>
-        <v>69.410176430719147</v>
+        <v>69.159308361532567</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.2">
@@ -14019,7 +14100,7 @@
       </c>
       <c r="F35" s="76">
         <f>+Main!I7</f>
-        <v>8015</v>
+        <v>8029</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -14028,7 +14109,7 @@
       </c>
       <c r="F36" s="76">
         <f>+Main!I5</f>
-        <v>87068.574999999997</v>
+        <v>71078.804999999993</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -14037,7 +14118,7 @@
       </c>
       <c r="F37" s="76">
         <f>F35+F36</f>
-        <v>95083.574999999997</v>
+        <v>79107.804999999993</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -14060,7 +14141,7 @@
       <c r="E41" s="20"/>
       <c r="F41" s="74">
         <f>(F32*(F35/F37)*(1-F39))+((F36/F37)*F22)</f>
-        <v>8.2383005725147743E-2</v>
+        <v>8.1373477775778413E-2</v>
       </c>
       <c r="H41" s="72" t="s">
         <v>273</v>

--- a/NKE.xlsx
+++ b/NKE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B45BBA6-548C-4AE6-99A4-B1C13B16932E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5317A824-7CA5-44EA-870A-555A9F93E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{B022B215-4C4C-4E36-8893-AFDEA07171F9}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="283">
   <si>
     <t>Main</t>
   </si>
@@ -910,7 +910,7 @@
     <t>Adidas, New Balance, Puma, Lulu Lemon, UA</t>
   </si>
   <si>
-    <t>FQ326</t>
+    <t>FQ426</t>
   </si>
 </sst>
 </file>
@@ -930,13 +930,19 @@
     <numFmt numFmtId="173" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="174" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1261,138 +1267,140 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="173" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="15" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="8" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="14" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -1416,16 +1424,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>17463</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>50802</xdr:rowOff>
+      <xdr:rowOff>3177</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>17479</xdr:colOff>
       <xdr:row>121</xdr:row>
-      <xdr:rowOff>169863</xdr:rowOff>
+      <xdr:rowOff>112713</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1440,8 +1448,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="15000288" y="50802"/>
-          <a:ext cx="16" cy="23360061"/>
+          <a:off x="18048288" y="3177"/>
+          <a:ext cx="16" cy="19702461"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1466,16 +1474,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>14287</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>14286</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>33338</xdr:rowOff>
+      <xdr:rowOff>90488</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>142876</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>28574</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1490,7 +1498,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="11596687" y="1166813"/>
+          <a:off x="12206286" y="1223963"/>
           <a:ext cx="14288" cy="3833813"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1923,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>48.01</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1940,9 +1948,9 @@
         <v>3</v>
       </c>
       <c r="I4" s="5">
-        <v>1480.5</v>
-      </c>
-      <c r="J4" s="85" t="s">
+        <v>1483.498703</v>
+      </c>
+      <c r="J4" s="80" t="s">
         <v>282</v>
       </c>
     </row>
@@ -1961,7 +1969,7 @@
       </c>
       <c r="I5" s="14">
         <f>I3*I4</f>
-        <v>71078.804999999993</v>
+        <v>65348.117867149995</v>
       </c>
       <c r="J5" s="4"/>
     </row>
@@ -1973,10 +1981,10 @@
         <v>5</v>
       </c>
       <c r="I6" s="14">
-        <f>6660+1397</f>
-        <v>8057</v>
-      </c>
-      <c r="J6" s="85" t="s">
+        <f>7563+1464</f>
+        <v>9027</v>
+      </c>
+      <c r="J6" s="80" t="s">
         <v>282</v>
       </c>
     </row>
@@ -1985,10 +1993,10 @@
         <v>6</v>
       </c>
       <c r="I7" s="14">
-        <f>7030+999</f>
-        <v>8029</v>
-      </c>
-      <c r="J7" s="85" t="s">
+        <f>2000+5942</f>
+        <v>7942</v>
+      </c>
+      <c r="J7" s="80" t="s">
         <v>282</v>
       </c>
     </row>
@@ -2004,7 +2012,7 @@
       </c>
       <c r="I8" s="14">
         <f>I5+I7-I6</f>
-        <v>71050.804999999993</v>
+        <v>64263.117867149995</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -2040,6 +2048,13 @@
       </c>
       <c r="F10" s="24" t="s">
         <v>231</v>
+      </c>
+      <c r="H10" s="86" t="s">
+        <v>157</v>
+      </c>
+      <c r="I10" s="30">
+        <f>+I8/Model!AB22</f>
+        <v>16.924708419054515</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -2298,7 +2313,9 @@
       <c r="AA3" s="5">
         <v>376</v>
       </c>
-      <c r="AB3" s="5"/>
+      <c r="AB3" s="5">
+        <v>347</v>
+      </c>
       <c r="AC3" s="5"/>
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
@@ -2350,7 +2367,9 @@
       <c r="AA4" s="5">
         <v>658</v>
       </c>
-      <c r="AB4" s="5"/>
+      <c r="AB4" s="5">
+        <v>641</v>
+      </c>
       <c r="AC4" s="5"/>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
@@ -2410,7 +2429,10 @@
         <f>SUM(AA3:AA4)</f>
         <v>1034</v>
       </c>
-      <c r="AB5" s="5"/>
+      <c r="AB5" s="8">
+        <f>SUM(AB3:AB4)</f>
+        <v>988</v>
+      </c>
       <c r="AC5" s="5"/>
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
@@ -2500,9 +2522,12 @@
         <v>22599.279999999999</v>
       </c>
       <c r="AA7" s="5">
-        <v>25883</v>
-      </c>
-      <c r="AB7" s="5"/>
+        <f>18783+48</f>
+        <v>18831</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>17720</v>
+      </c>
       <c r="AC7" s="5"/>
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
@@ -2559,10 +2584,11 @@
         <v>28762.720000000001</v>
       </c>
       <c r="AA8" s="5">
-        <f>18783+48</f>
-        <v>18831</v>
-      </c>
-      <c r="AB8" s="5"/>
+        <v>25883</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>27453</v>
+      </c>
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
@@ -2620,7 +2646,10 @@
       <c r="Q9" s="5">
         <v>7353</v>
       </c>
-      <c r="R9" s="5"/>
+      <c r="R9" s="5">
+        <f>+AB9-SUM(O9:Q9)</f>
+        <v>7103</v>
+      </c>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <v>22268</v>
@@ -2648,7 +2677,9 @@
         <f>+SUM(K9:N9)</f>
         <v>29510</v>
       </c>
-      <c r="AB9" s="5"/>
+      <c r="AB9" s="5">
+        <v>29525</v>
+      </c>
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
@@ -2706,7 +2737,10 @@
       <c r="Q10" s="5">
         <v>3184</v>
       </c>
-      <c r="R10" s="5"/>
+      <c r="R10" s="5">
+        <f t="shared" ref="R10:R15" si="4">+AB10-SUM(O10:Q10)</f>
+        <v>3046</v>
+      </c>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <v>10733</v>
@@ -2727,14 +2761,16 @@
         <v>13843</v>
       </c>
       <c r="Z10" s="5">
-        <f t="shared" ref="Z10:Z12" si="4">SUM(G10:J10)</f>
+        <f t="shared" ref="Z10:Z12" si="5">SUM(G10:J10)</f>
         <v>13775</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" ref="AA10:AA26" si="5">+SUM(K10:N10)</f>
+        <f t="shared" ref="AA10:AB26" si="6">+SUM(K10:N10)</f>
         <v>12965</v>
       </c>
-      <c r="AB10" s="5"/>
+      <c r="AB10" s="5">
+        <v>13449</v>
+      </c>
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
       <c r="AE10" s="5"/>
@@ -2792,7 +2828,10 @@
       <c r="Q11" s="5">
         <v>468</v>
       </c>
-      <c r="R11" s="5"/>
+      <c r="R11" s="5">
+        <f t="shared" si="4"/>
+        <v>551</v>
+      </c>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <v>1396</v>
@@ -2813,14 +2852,16 @@
         <v>1727</v>
       </c>
       <c r="Z11" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2075</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2191</v>
       </c>
-      <c r="AB11" s="5"/>
+      <c r="AB11" s="5">
+        <v>2199</v>
+      </c>
       <c r="AC11" s="5"/>
       <c r="AD11" s="5"/>
       <c r="AE11" s="5"/>
@@ -2878,7 +2919,10 @@
       <c r="Q12" s="5">
         <v>7</v>
       </c>
-      <c r="R12" s="5"/>
+      <c r="R12" s="5">
+        <f t="shared" si="4"/>
+        <v>24</v>
+      </c>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <v>88</v>
@@ -2899,14 +2943,16 @@
         <v>58</v>
       </c>
       <c r="Z12" s="5">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>45</v>
       </c>
       <c r="AA12" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>48</v>
       </c>
-      <c r="AB12" s="5"/>
+      <c r="AB12" s="5">
+        <v>49</v>
+      </c>
       <c r="AC12" s="5"/>
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
@@ -2919,39 +2965,39 @@
         <v>98</v>
       </c>
       <c r="C13" s="5">
-        <f t="shared" ref="C13:K13" si="6">SUM(C9:C12)</f>
+        <f t="shared" ref="C13:K13" si="7">SUM(C9:C12)</f>
         <v>12048</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12724</v>
       </c>
       <c r="E13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11766</v>
       </c>
       <c r="F13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7898</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12353</v>
       </c>
       <c r="H13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12872</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11948</v>
       </c>
       <c r="J13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>12149</v>
       </c>
       <c r="K13" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>11111</v>
       </c>
       <c r="L13" s="5">
@@ -2976,41 +3022,47 @@
       <c r="Q13" s="5">
         <v>11012</v>
       </c>
-      <c r="R13" s="5"/>
+      <c r="R13" s="5">
+        <f t="shared" si="4"/>
+        <v>10724</v>
+      </c>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
-        <f>SUM(T9:T12)</f>
+        <f>+SUM(T9:T12)</f>
         <v>34485</v>
       </c>
       <c r="U13" s="5">
-        <f t="shared" ref="U13:X13" si="7">SUM(U9:U12)</f>
+        <f>+SUM(U9:U12)</f>
         <v>37218</v>
       </c>
       <c r="V13" s="5">
-        <f t="shared" si="7"/>
+        <f>+SUM(V9:V12)</f>
         <v>35568</v>
       </c>
       <c r="W13" s="5">
-        <f t="shared" si="7"/>
+        <f>+SUM(W9:W12)</f>
         <v>42293</v>
       </c>
       <c r="X13" s="5">
-        <f t="shared" si="7"/>
+        <f>+SUM(X9:X12)</f>
         <v>44436</v>
       </c>
       <c r="Y13" s="5">
-        <f>SUM(Y9:Y12)</f>
+        <f>+SUM(Y9:Y12)</f>
         <v>48763</v>
       </c>
       <c r="Z13" s="5">
-        <f>SUM(Z9:Z12)</f>
+        <f>+SUM(Z9:Z12)</f>
         <v>49322</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" si="5"/>
+        <f>+SUM(AA9:AA12)</f>
         <v>44714</v>
       </c>
-      <c r="AB13" s="5"/>
+      <c r="AB13" s="5">
+        <f>+SUM(AB9:AB12)</f>
+        <v>45222</v>
+      </c>
       <c r="AC13" s="5"/>
       <c r="AD13" s="5"/>
       <c r="AE13" s="5"/>
@@ -3068,7 +3120,10 @@
       <c r="Q14" s="5">
         <v>264</v>
       </c>
-      <c r="R14" s="5"/>
+      <c r="R14" s="5">
+        <f t="shared" si="4"/>
+        <v>244</v>
+      </c>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <v>1886</v>
@@ -3093,10 +3148,12 @@
         <v>2082</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1692</v>
       </c>
-      <c r="AB14" s="5"/>
+      <c r="AB14" s="5">
+        <v>1174</v>
+      </c>
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
@@ -3154,7 +3211,10 @@
       <c r="Q15" s="5">
         <v>3</v>
       </c>
-      <c r="R15" s="5"/>
+      <c r="R15" s="5">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <v>26</v>
@@ -3179,10 +3239,12 @@
         <v>-42</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-97</v>
       </c>
-      <c r="AB15" s="5"/>
+      <c r="AB15" s="5">
+        <v>2</v>
+      </c>
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
       <c r="AE15" s="5"/>
@@ -3239,41 +3301,37 @@
       <c r="Q16" s="8">
         <v>11279</v>
       </c>
-      <c r="R16" s="8"/>
+      <c r="R16" s="8">
+        <v>10972</v>
+      </c>
       <c r="S16" s="8"/>
       <c r="T16" s="8">
-        <f>T13+T14+T15</f>
         <v>36397</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" ref="U16:Y16" si="9">U13+U14+U15</f>
         <v>39117</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="9"/>
         <v>37403</v>
       </c>
       <c r="W16" s="8">
-        <f t="shared" si="9"/>
         <v>44538</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="9"/>
         <v>46710</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" si="9"/>
         <v>51217</v>
       </c>
       <c r="Z16" s="8">
-        <f>SUM(G16:J16)</f>
         <v>51362</v>
       </c>
       <c r="AA16" s="8">
-        <f t="shared" si="5"/>
         <v>46309</v>
       </c>
-      <c r="AB16" s="5"/>
+      <c r="AB16" s="8">
+        <v>46398</v>
+      </c>
       <c r="AC16" s="5"/>
       <c r="AD16" s="5"/>
       <c r="AE16" s="5"/>
@@ -3330,7 +3388,9 @@
       <c r="Q17" s="5">
         <v>6749</v>
       </c>
-      <c r="R17" s="5"/>
+      <c r="R17" s="5">
+        <v>5579</v>
+      </c>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <v>20441</v>
@@ -3355,10 +3415,12 @@
         <v>28475</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>26519</v>
       </c>
-      <c r="AB17" s="5"/>
+      <c r="AB17" s="5">
+        <v>26487</v>
+      </c>
       <c r="AC17" s="5"/>
       <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
@@ -3370,89 +3432,92 @@
         <v>26</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18:G18" si="10">C16-C17</f>
+        <f t="shared" ref="C18:G18" si="9">C16-C17</f>
         <v>5615</v>
       </c>
       <c r="D18" s="5">
+        <f t="shared" si="9"/>
+        <v>5711</v>
+      </c>
+      <c r="E18" s="5">
+        <f t="shared" si="9"/>
+        <v>5371</v>
+      </c>
+      <c r="F18" s="5">
+        <f t="shared" si="9"/>
+        <v>4782</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="9"/>
+        <v>5720</v>
+      </c>
+      <c r="H18" s="5">
+        <f t="shared" ref="H18:R18" si="10">H16-H17</f>
+        <v>5971</v>
+      </c>
+      <c r="I18" s="5">
         <f t="shared" si="10"/>
-        <v>5711</v>
-      </c>
-      <c r="E18" s="5">
+        <v>5562</v>
+      </c>
+      <c r="J18" s="5">
         <f t="shared" si="10"/>
-        <v>5371</v>
-      </c>
-      <c r="F18" s="5">
+        <v>5634</v>
+      </c>
+      <c r="K18" s="5">
         <f t="shared" si="10"/>
-        <v>4782</v>
-      </c>
-      <c r="G18" s="5">
+        <v>5257</v>
+      </c>
+      <c r="L18" s="5">
         <f t="shared" si="10"/>
-        <v>5720</v>
-      </c>
-      <c r="H18" s="5">
-        <f t="shared" ref="H18:Q18" si="11">H16-H17</f>
-        <v>5971</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="11"/>
-        <v>5562</v>
-      </c>
-      <c r="J18" s="5">
-        <f t="shared" si="11"/>
-        <v>5634</v>
-      </c>
-      <c r="K18" s="5">
-        <f t="shared" si="11"/>
-        <v>5257</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="11"/>
         <v>5389</v>
       </c>
       <c r="M18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4675</v>
       </c>
       <c r="N18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4469</v>
       </c>
       <c r="O18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4943</v>
       </c>
       <c r="P18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>5045</v>
       </c>
       <c r="Q18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>4530</v>
       </c>
-      <c r="R18" s="5"/>
+      <c r="R18" s="5">
+        <f t="shared" si="10"/>
+        <v>5393</v>
+      </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
-        <f t="shared" ref="T18:Y18" si="12">T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="11">T16-T17</f>
         <v>15956</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>17474</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>16241</v>
       </c>
       <c r="W18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>19962</v>
       </c>
       <c r="X18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>21479</v>
       </c>
       <c r="Y18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>22292</v>
       </c>
       <c r="Z18" s="5">
@@ -3463,7 +3528,10 @@
         <f>AA16-AA17</f>
         <v>19790</v>
       </c>
-      <c r="AB18" s="5"/>
+      <c r="AB18" s="5">
+        <f>AB16-AB17</f>
+        <v>19911</v>
+      </c>
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
       <c r="AE18" s="5"/>
@@ -3520,7 +3588,9 @@
       <c r="Q19" s="5">
         <v>1090</v>
       </c>
-      <c r="R19" s="5"/>
+      <c r="R19" s="5">
+        <v>1203</v>
+      </c>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <v>3577</v>
@@ -3545,10 +3615,12 @@
         <v>4285</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4689</v>
       </c>
-      <c r="AB19" s="5"/>
+      <c r="AB19" s="5">
+        <v>4754</v>
+      </c>
       <c r="AC19" s="5"/>
       <c r="AD19" s="5"/>
       <c r="AE19" s="5"/>
@@ -3605,7 +3677,9 @@
       <c r="Q20" s="5">
         <v>2887</v>
       </c>
-      <c r="R20" s="5"/>
+      <c r="R20" s="5">
+        <v>2879</v>
+      </c>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <v>7934</v>
@@ -3630,10 +3704,12 @@
         <v>12291</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>11399</v>
       </c>
-      <c r="AB20" s="5"/>
+      <c r="AB20" s="5">
+        <v>11360</v>
+      </c>
       <c r="AC20" s="5"/>
       <c r="AD20" s="5"/>
       <c r="AE20" s="5"/>
@@ -3645,23 +3721,23 @@
         <v>232</v>
       </c>
       <c r="C21" s="5">
-        <f t="shared" ref="C21:G21" si="13">C19+C20</f>
+        <f t="shared" ref="C21:G21" si="12">C19+C20</f>
         <v>3920</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4124</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>3959</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>2801</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>4116</v>
       </c>
       <c r="H21" s="5">
@@ -3673,49 +3749,52 @@
         <v>4226</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" ref="J21:Q21" si="14">J19+J20</f>
+        <f t="shared" ref="J21:R21" si="13">J19+J20</f>
         <v>4088</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4048</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4005</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>3887</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4148</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4016</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>4039</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>3977</v>
       </c>
-      <c r="R21" s="5"/>
+      <c r="R21" s="5">
+        <f t="shared" si="13"/>
+        <v>4082</v>
+      </c>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
-        <f t="shared" ref="T21" si="15">T19+T20</f>
+        <f t="shared" ref="T21" si="14">T19+T20</f>
         <v>11511</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" ref="U21" si="16">U19+U20</f>
+        <f t="shared" ref="U21" si="15">U19+U20</f>
         <v>12702</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" ref="V21" si="17">V19+V20</f>
+        <f t="shared" ref="V21" si="16">V19+V20</f>
         <v>13126</v>
       </c>
       <c r="W21" s="5">
@@ -3723,11 +3802,11 @@
         <v>13025</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" ref="X21" si="18">X19+X20</f>
+        <f t="shared" ref="X21" si="17">X19+X20</f>
         <v>14804</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" ref="Y21" si="19">Y19+Y20</f>
+        <f t="shared" ref="Y21" si="18">Y19+Y20</f>
         <v>16377</v>
       </c>
       <c r="Z21" s="5">
@@ -3738,7 +3817,10 @@
         <f>AA19+AA20</f>
         <v>16088</v>
       </c>
-      <c r="AB21" s="5"/>
+      <c r="AB21" s="5">
+        <f>AB19+AB20</f>
+        <v>16114</v>
+      </c>
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5"/>
@@ -3750,77 +3832,80 @@
         <v>29</v>
       </c>
       <c r="C22" s="5">
-        <f t="shared" ref="C22:G22" si="20">C18-C21</f>
+        <f t="shared" ref="C22:G22" si="19">C18-C21</f>
         <v>1695</v>
       </c>
       <c r="D22" s="5">
+        <f t="shared" si="19"/>
+        <v>1587</v>
+      </c>
+      <c r="E22" s="5">
+        <f t="shared" si="19"/>
+        <v>1412</v>
+      </c>
+      <c r="F22" s="5">
+        <f t="shared" si="19"/>
+        <v>1981</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="19"/>
+        <v>1604</v>
+      </c>
+      <c r="H22" s="5">
+        <f t="shared" ref="H22:R22" si="20">H18-H21</f>
+        <v>1825</v>
+      </c>
+      <c r="I22" s="5">
         <f t="shared" si="20"/>
-        <v>1587</v>
-      </c>
-      <c r="E22" s="5">
+        <v>1336</v>
+      </c>
+      <c r="J22" s="5">
         <f t="shared" si="20"/>
-        <v>1412</v>
-      </c>
-      <c r="F22" s="5">
+        <v>1546</v>
+      </c>
+      <c r="K22" s="5">
         <f t="shared" si="20"/>
-        <v>1981</v>
-      </c>
-      <c r="G22" s="5">
+        <v>1209</v>
+      </c>
+      <c r="L22" s="5">
         <f t="shared" si="20"/>
-        <v>1604</v>
-      </c>
-      <c r="H22" s="5">
-        <f t="shared" ref="H22:Q22" si="21">H18-H21</f>
-        <v>1825</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="21"/>
-        <v>1336</v>
-      </c>
-      <c r="J22" s="5">
-        <f t="shared" si="21"/>
-        <v>1546</v>
-      </c>
-      <c r="K22" s="5">
-        <f t="shared" si="21"/>
-        <v>1209</v>
-      </c>
-      <c r="L22" s="5">
-        <f t="shared" si="21"/>
         <v>1384</v>
       </c>
       <c r="M22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>788</v>
       </c>
       <c r="N22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>321</v>
       </c>
       <c r="O22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>927</v>
       </c>
       <c r="P22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>1006</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>553</v>
       </c>
-      <c r="R22" s="5"/>
+      <c r="R22" s="5">
+        <f t="shared" si="20"/>
+        <v>1311</v>
+      </c>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
-        <f t="shared" ref="T22:Y22" si="22">T18-T21</f>
+        <f t="shared" ref="T22:Y22" si="21">T18-T21</f>
         <v>4445</v>
       </c>
       <c r="U22" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>4772</v>
       </c>
       <c r="V22" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>3115</v>
       </c>
       <c r="W22" s="5">
@@ -3832,7 +3917,7 @@
         <v>6675</v>
       </c>
       <c r="Y22" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
         <v>5915</v>
       </c>
       <c r="Z22" s="5">
@@ -3843,7 +3928,10 @@
         <f>AA18-AA21</f>
         <v>3702</v>
       </c>
-      <c r="AB22" s="5"/>
+      <c r="AB22" s="5">
+        <f>AB18-AB21</f>
+        <v>3797</v>
+      </c>
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5"/>
@@ -3900,7 +3988,9 @@
       <c r="Q23" s="5">
         <v>-15</v>
       </c>
-      <c r="R23" s="5"/>
+      <c r="R23" s="5">
+        <v>-8</v>
+      </c>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
         <v>54</v>
@@ -3925,10 +4015,12 @@
         <v>-161</v>
       </c>
       <c r="AA23" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-107</v>
       </c>
-      <c r="AB23" s="5"/>
+      <c r="AB23" s="5">
+        <v>-50</v>
+      </c>
       <c r="AC23" s="5"/>
       <c r="AD23" s="5"/>
       <c r="AE23" s="5"/>
@@ -3985,7 +4077,9 @@
       <c r="Q24" s="5">
         <v>-82</v>
       </c>
-      <c r="R24" s="5"/>
+      <c r="R24" s="5">
+        <v>-10</v>
+      </c>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
         <v>66</v>
@@ -4010,10 +4104,12 @@
         <v>-228</v>
       </c>
       <c r="AA24" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>-76</v>
       </c>
-      <c r="AB24" s="5"/>
+      <c r="AB24" s="5">
+        <v>-53</v>
+      </c>
       <c r="AC24" s="5"/>
       <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
@@ -4025,89 +4121,92 @@
         <v>31</v>
       </c>
       <c r="C25" s="5">
-        <f t="shared" ref="C25:G25" si="23">C22-C23-C24</f>
+        <f t="shared" ref="C25:G25" si="22">C22-C23-C24</f>
         <v>1828</v>
       </c>
       <c r="D25" s="5">
+        <f t="shared" si="22"/>
+        <v>1650</v>
+      </c>
+      <c r="E25" s="5">
+        <f t="shared" si="22"/>
+        <v>1477</v>
+      </c>
+      <c r="F25" s="5">
+        <f t="shared" si="22"/>
+        <v>1696</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" si="22"/>
+        <v>1648</v>
+      </c>
+      <c r="H25" s="5">
+        <f t="shared" ref="H25:R25" si="23">H22-H23-H24</f>
+        <v>1922</v>
+      </c>
+      <c r="I25" s="5">
         <f t="shared" si="23"/>
-        <v>1650</v>
-      </c>
-      <c r="E25" s="5">
+        <v>1404</v>
+      </c>
+      <c r="J25" s="5">
         <f t="shared" si="23"/>
-        <v>1477</v>
-      </c>
-      <c r="F25" s="5">
+        <v>1726</v>
+      </c>
+      <c r="K25" s="5">
         <f t="shared" si="23"/>
-        <v>1696</v>
-      </c>
-      <c r="G25" s="5">
+        <v>1307</v>
+      </c>
+      <c r="L25" s="5">
         <f t="shared" si="23"/>
-        <v>1648</v>
-      </c>
-      <c r="H25" s="5">
-        <f t="shared" ref="H25:Q25" si="24">H22-H23-H24</f>
-        <v>1922</v>
-      </c>
-      <c r="I25" s="5">
-        <f t="shared" si="24"/>
-        <v>1404</v>
-      </c>
-      <c r="J25" s="5">
-        <f t="shared" si="24"/>
-        <v>1726</v>
-      </c>
-      <c r="K25" s="5">
-        <f t="shared" si="24"/>
-        <v>1307</v>
-      </c>
-      <c r="L25" s="5">
-        <f t="shared" si="24"/>
         <v>1416</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>844</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>318</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>922</v>
       </c>
       <c r="P25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>999</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>650</v>
       </c>
-      <c r="R25" s="5"/>
+      <c r="R25" s="5">
+        <f t="shared" si="23"/>
+        <v>1329</v>
+      </c>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
-        <f t="shared" ref="T25:Y25" si="25">T22-T23-T24</f>
+        <f t="shared" ref="T25:Y25" si="24">T22-T23-T24</f>
         <v>4325</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>4801</v>
       </c>
       <c r="V25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>2887</v>
       </c>
       <c r="W25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6661</v>
       </c>
       <c r="X25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6651</v>
       </c>
       <c r="Y25" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>6201</v>
       </c>
       <c r="Z25" s="5">
@@ -4118,7 +4217,10 @@
         <f>AA22-AA23-AA24</f>
         <v>3885</v>
       </c>
-      <c r="AB25" s="5"/>
+      <c r="AB25" s="5">
+        <f>AB22-AB23-AB24</f>
+        <v>3900</v>
+      </c>
       <c r="AC25" s="5"/>
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
@@ -4175,7 +4277,9 @@
       <c r="Q26" s="5">
         <v>130</v>
       </c>
-      <c r="R26" s="5"/>
+      <c r="R26" s="5">
+        <v>260</v>
+      </c>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
         <v>2392</v>
@@ -4200,10 +4304,12 @@
         <v>1000</v>
       </c>
       <c r="AA26" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>666</v>
       </c>
-      <c r="AB26" s="5"/>
+      <c r="AB26" s="5">
+        <v>792</v>
+      </c>
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
       <c r="AE26" s="5"/>
@@ -4215,23 +4321,23 @@
         <v>33</v>
       </c>
       <c r="C27" s="5">
-        <f t="shared" ref="C27:G27" si="26">C25-C26</f>
+        <f t="shared" ref="C27:G27" si="25">C25-C26</f>
         <v>1468</v>
       </c>
       <c r="D27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1331</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1240</v>
       </c>
       <c r="F27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>2007</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1450</v>
       </c>
       <c r="H27" s="5">
@@ -4251,33 +4357,36 @@
         <v>1051</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27:Q27" si="27">L25-L26</f>
+        <f t="shared" ref="L27:R27" si="26">L25-L26</f>
         <v>1163</v>
       </c>
       <c r="M27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>794</v>
       </c>
       <c r="N27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>211</v>
       </c>
       <c r="O27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>727</v>
       </c>
       <c r="P27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>792</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>520</v>
       </c>
-      <c r="R27" s="5"/>
+      <c r="R27" s="5">
+        <f t="shared" si="26"/>
+        <v>1069</v>
+      </c>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
-        <f t="shared" ref="T27:Y27" si="28">T25-T26</f>
+        <f t="shared" ref="T27:Y27" si="27">T25-T26</f>
         <v>1933</v>
       </c>
       <c r="U27" s="5">
@@ -4285,19 +4394,19 @@
         <v>4029</v>
       </c>
       <c r="V27" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>2539</v>
       </c>
       <c r="W27" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>5727</v>
       </c>
       <c r="X27" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>6046</v>
       </c>
       <c r="Y27" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>5070</v>
       </c>
       <c r="Z27" s="5">
@@ -4308,7 +4417,10 @@
         <f>AA25-AA26</f>
         <v>3219</v>
       </c>
-      <c r="AB27" s="5"/>
+      <c r="AB27" s="5">
+        <f>AB25-AB26</f>
+        <v>3108</v>
+      </c>
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
@@ -4353,66 +4465,69 @@
         <v>35</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:Q29" si="29">C27/C30</f>
+        <f t="shared" ref="C29:R29" si="28">C27/C30</f>
         <v>0.92994376447237848</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.84315745947734044</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.78551108170691364</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1.2713876943433675</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.95275008437176922</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>1.0415002416821773</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.77646747051808662</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.99469496021220161</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.70174267209721575</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.7822168415388755</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.53717610445842634</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.14288616509785332</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.49234728430177438</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.53531598513011147</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>0.35123269165822357</v>
       </c>
-      <c r="R29" s="9"/>
+      <c r="R29" s="9">
+        <f t="shared" si="28"/>
+        <v>0.72103062188048028</v>
+      </c>
       <c r="S29" s="5"/>
       <c r="T29" s="9">
         <v>1.19</v>
@@ -4440,7 +4555,10 @@
         <f>AA27/AA30</f>
         <v>2.1679322479080025</v>
       </c>
-      <c r="AB29" s="5"/>
+      <c r="AB29" s="9">
+        <f>AB27/AB30</f>
+        <v>2.100283822138127</v>
+      </c>
       <c r="AC29" s="5"/>
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
@@ -4500,30 +4618,32 @@
       <c r="Q30" s="5">
         <v>1480.5</v>
       </c>
-      <c r="R30" s="5"/>
+      <c r="R30" s="5">
+        <v>1482.6</v>
+      </c>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
-        <f t="shared" ref="T30:Y30" si="30">T27/T29</f>
+        <f t="shared" ref="T30:Y30" si="29">T27/T29</f>
         <v>1624.3697478991598</v>
       </c>
       <c r="U30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1580</v>
       </c>
       <c r="V30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1557.6687116564419</v>
       </c>
       <c r="W30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1573.3516483516482</v>
       </c>
       <c r="X30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1578.5900783289817</v>
       </c>
       <c r="Y30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>1550.4587155963302</v>
       </c>
       <c r="Z30" s="5">
@@ -4533,7 +4653,9 @@
         <f>+AVERAGE(K30:N30)</f>
         <v>1484.825</v>
       </c>
-      <c r="AB30" s="5"/>
+      <c r="AB30" s="5">
+        <v>1479.8</v>
+      </c>
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
@@ -4583,50 +4705,53 @@
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10">
-        <f t="shared" ref="G32:G37" si="31">G9/C9-1</f>
+        <f t="shared" ref="G32:G37" si="30">G9/C9-1</f>
         <v>3.7835839290115914E-2</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:H37" si="32">H9/D9-1</f>
+        <f t="shared" ref="H32:H37" si="31">H9/D9-1</f>
         <v>1.2111947318908856E-2</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" ref="I32:I37" si="33">I9/E9-1</f>
+        <f t="shared" ref="I32:I37" si="32">I9/E9-1</f>
         <v>2.4090338770389019E-2</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" ref="J32:J37" si="34">J9/F9-1</f>
+        <f t="shared" ref="J32:J37" si="33">J9/F9-1</f>
         <v>0.80834248079034032</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" ref="K32:K37" si="35">K9/G9-1</f>
+        <f t="shared" ref="K32:K37" si="34">K9/G9-1</f>
         <v>-0.11388196176226106</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" ref="L32:L37" si="36">L9/H9-1</f>
+        <f t="shared" ref="L32:L37" si="35">L9/H9-1</f>
         <v>-0.11060764494016495</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" ref="M32:Q37" si="37">M9/I9-1</f>
+        <f t="shared" ref="M32:R37" si="36">M9/I9-1</f>
         <v>-0.11688311688311692</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.12771640160252518</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-6.9686411149826322E-3</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>5.2253429131288165E-4</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>2.0116537180909999E-2</v>
       </c>
-      <c r="R32" s="10"/>
+      <c r="R32" s="10">
+        <f t="shared" si="36"/>
+        <v>-1.1412665274878164E-2</v>
+      </c>
       <c r="S32" s="10"/>
       <c r="T32" s="10">
         <f>T7/T16</f>
@@ -4651,6 +4776,9 @@
         <v>0.44</v>
       </c>
       <c r="AA32" s="10">
+        <v>0.44</v>
+      </c>
+      <c r="AB32" s="10">
         <v>0.44</v>
       </c>
     </row>
@@ -4664,50 +4792,53 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10">
+        <f t="shared" si="30"/>
+        <v>-1.3395457192778126E-2</v>
+      </c>
+      <c r="H33" s="10">
         <f t="shared" si="31"/>
-        <v>-1.3395457192778126E-2</v>
-      </c>
-      <c r="H33" s="10">
+        <v>-5.2714812862414417E-3</v>
+      </c>
+      <c r="I33" s="10">
         <f t="shared" si="32"/>
-        <v>-5.2714812862414417E-3</v>
-      </c>
-      <c r="I33" s="10">
+        <v>-2.6915113871635588E-2</v>
+      </c>
+      <c r="J33" s="10">
         <f t="shared" si="33"/>
-        <v>-2.6915113871635588E-2</v>
-      </c>
-      <c r="J33" s="10">
+        <v>0.1233941852603111</v>
+      </c>
+      <c r="K33" s="10">
         <f t="shared" si="34"/>
-        <v>0.1233941852603111</v>
-      </c>
-      <c r="K33" s="10">
+        <v>-0.10507674144037782</v>
+      </c>
+      <c r="L33" s="10">
         <f t="shared" si="35"/>
-        <v>-0.10507674144037782</v>
-      </c>
-      <c r="L33" s="10">
+        <v>-9.5389507154213238E-3</v>
+      </c>
+      <c r="M33" s="10">
         <f t="shared" si="36"/>
-        <v>-9.5389507154213238E-3</v>
-      </c>
-      <c r="M33" s="10">
-        <f t="shared" si="37"/>
         <v>-2.9483282674772071E-2</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-9.6599458320794418E-2</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>9.2678100263852148E-2</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>4.4943820224719211E-2</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-2.8186658315064728E-3</v>
       </c>
-      <c r="R33" s="10"/>
+      <c r="R33" s="10">
+        <f t="shared" si="36"/>
+        <v>1.4656895403064585E-2</v>
+      </c>
       <c r="S33" s="10"/>
       <c r="T33" s="10">
         <f>T8/T16</f>
@@ -4732,6 +4863,9 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="AA33" s="10">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AB33" s="10">
         <v>0.56000000000000005</v>
       </c>
     </row>
@@ -4744,81 +4878,88 @@
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="10">
+        <f t="shared" si="30"/>
+        <v>9.259259259259256E-2</v>
+      </c>
+      <c r="H34" s="10">
         <f t="shared" si="31"/>
-        <v>9.259259259259256E-2</v>
-      </c>
-      <c r="H34" s="10">
+        <v>0.1740196078431373</v>
+      </c>
+      <c r="I34" s="10">
         <f t="shared" si="32"/>
-        <v>0.1740196078431373</v>
-      </c>
-      <c r="I34" s="10">
+        <v>0.20843672456575679</v>
+      </c>
+      <c r="J34" s="10">
         <f t="shared" si="33"/>
-        <v>0.20843672456575679</v>
-      </c>
-      <c r="J34" s="10">
+        <v>0.76758409785932713</v>
+      </c>
+      <c r="K34" s="10">
         <f t="shared" si="34"/>
-        <v>0.76758409785932713</v>
-      </c>
-      <c r="K34" s="10">
+        <v>0.13559322033898313</v>
+      </c>
+      <c r="L34" s="10">
         <f t="shared" si="35"/>
-        <v>0.13559322033898313</v>
-      </c>
-      <c r="L34" s="10">
+        <v>0.13569937369519836</v>
+      </c>
+      <c r="M34" s="10">
         <f t="shared" si="36"/>
-        <v>0.13569937369519836</v>
-      </c>
-      <c r="M34" s="10">
+        <v>-2.0533880903490731E-2</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="36"/>
+        <v>-1.9031141868512069E-2</v>
+      </c>
+      <c r="O34" s="10">
+        <f t="shared" si="36"/>
+        <v>4.4776119402984982E-2</v>
+      </c>
+      <c r="P34" s="10">
+        <f t="shared" si="36"/>
+        <v>1.1029411764705843E-2</v>
+      </c>
+      <c r="Q34" s="10">
+        <f t="shared" si="36"/>
+        <v>-1.8867924528301883E-2</v>
+      </c>
+      <c r="R34" s="10">
+        <f t="shared" si="36"/>
+        <v>-2.821869488536155E-2</v>
+      </c>
+      <c r="T34" s="10">
+        <f t="shared" ref="T34:Z34" si="37">T9/T16</f>
+        <v>0.61180866554935842</v>
+      </c>
+      <c r="U34" s="10">
         <f t="shared" si="37"/>
-        <v>-2.0533880903490731E-2</v>
-      </c>
-      <c r="N34" s="10">
+        <v>0.61921926528107984</v>
+      </c>
+      <c r="V34" s="10">
         <f t="shared" si="37"/>
-        <v>-1.9031141868512069E-2</v>
-      </c>
-      <c r="O34" s="10">
+        <v>0.62307836269817929</v>
+      </c>
+      <c r="W34" s="10">
         <f t="shared" si="37"/>
-        <v>4.4776119402984982E-2</v>
-      </c>
-      <c r="P34" s="10">
+        <v>0.62914814315865109</v>
+      </c>
+      <c r="X34" s="10">
         <f t="shared" si="37"/>
-        <v>1.1029411764705843E-2</v>
-      </c>
-      <c r="Q34" s="10">
+        <v>0.62391350888460717</v>
+      </c>
+      <c r="Y34" s="10">
         <f t="shared" si="37"/>
-        <v>-1.8867924528301883E-2</v>
-      </c>
-      <c r="R34" s="10"/>
-      <c r="T34" s="10">
-        <f t="shared" ref="T34:Z34" si="38">T9/T16</f>
-        <v>0.61180866554935842</v>
-      </c>
-      <c r="U34" s="10">
+        <v>0.64695316008356596</v>
+      </c>
+      <c r="Z34" s="10">
+        <f t="shared" si="37"/>
+        <v>0.65081188427241932</v>
+      </c>
+      <c r="AA34" s="10">
+        <f t="shared" ref="AA34:AB34" si="38">AA9/AA16</f>
+        <v>0.63724114103090113</v>
+      </c>
+      <c r="AB34" s="10">
         <f t="shared" si="38"/>
-        <v>0.61921926528107984</v>
-      </c>
-      <c r="V34" s="10">
-        <f t="shared" si="38"/>
-        <v>0.62307836269817929</v>
-      </c>
-      <c r="W34" s="10">
-        <f t="shared" si="38"/>
-        <v>0.62914814315865109</v>
-      </c>
-      <c r="X34" s="10">
-        <f t="shared" si="38"/>
-        <v>0.62391350888460717</v>
-      </c>
-      <c r="Y34" s="10">
-        <f t="shared" si="38"/>
-        <v>0.64695316008356596</v>
-      </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="38"/>
-        <v>0.65081188427241932</v>
-      </c>
-      <c r="AA34" s="10">
-        <f t="shared" ref="AA34" si="39">AA9/AA16</f>
-        <v>0.63724114103090113</v>
+        <v>0.63634208371050471</v>
       </c>
     </row>
     <row r="35" spans="1:35" x14ac:dyDescent="0.2">
@@ -4830,81 +4971,88 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10">
+        <f t="shared" si="30"/>
+        <v>-7.1428571428571397E-2</v>
+      </c>
+      <c r="H35" s="10">
         <f t="shared" si="31"/>
-        <v>-7.1428571428571397E-2</v>
-      </c>
-      <c r="H35" s="10">
+        <v>-0.33333333333333337</v>
+      </c>
+      <c r="I35" s="10">
         <f t="shared" si="32"/>
-        <v>-0.33333333333333337</v>
-      </c>
-      <c r="I35" s="10">
+        <v>-0.25</v>
+      </c>
+      <c r="J35" s="10">
         <f t="shared" si="33"/>
-        <v>-0.25</v>
-      </c>
-      <c r="J35" s="10">
+        <v>-0.81034482758620685</v>
+      </c>
+      <c r="K35" s="10">
         <f t="shared" si="34"/>
-        <v>-0.81034482758620685</v>
-      </c>
-      <c r="K35" s="10">
+        <v>7.6923076923076872E-2</v>
+      </c>
+      <c r="L35" s="10">
         <f t="shared" si="35"/>
-        <v>7.6923076923076872E-2</v>
-      </c>
-      <c r="L35" s="10">
+        <v>8.3333333333333259E-2</v>
+      </c>
+      <c r="M35" s="10">
         <f t="shared" si="36"/>
-        <v>8.3333333333333259E-2</v>
-      </c>
-      <c r="M35" s="10">
-        <f t="shared" si="37"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.18181818181818177</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.30769230769230771</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.41666666666666663</v>
       </c>
-      <c r="R35" s="10"/>
+      <c r="R35" s="10">
+        <f t="shared" si="36"/>
+        <v>1.6666666666666665</v>
+      </c>
       <c r="T35" s="10">
-        <f t="shared" ref="T35:Z35" si="40">T10/T16</f>
+        <f t="shared" ref="T35:Z35" si="39">T10/T16</f>
         <v>0.29488694123142017</v>
       </c>
       <c r="U35" s="10">
+        <f t="shared" si="39"/>
+        <v>0.29526804202776286</v>
+      </c>
+      <c r="V35" s="10">
+        <f t="shared" si="39"/>
+        <v>0.29283747292997886</v>
+      </c>
+      <c r="W35" s="10">
+        <f t="shared" si="39"/>
+        <v>0.28885446135883963</v>
+      </c>
+      <c r="X35" s="10">
+        <f t="shared" si="39"/>
+        <v>0.29045172339970027</v>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="39"/>
+        <v>0.27028135189487867</v>
+      </c>
+      <c r="Z35" s="10">
+        <f t="shared" si="39"/>
+        <v>0.26819438495385695</v>
+      </c>
+      <c r="AA35" s="10">
+        <f t="shared" ref="AA35:AB35" si="40">AA10/AA16</f>
+        <v>0.27996717700662938</v>
+      </c>
+      <c r="AB35" s="10">
         <f t="shared" si="40"/>
-        <v>0.29526804202776286</v>
-      </c>
-      <c r="V35" s="10">
-        <f t="shared" si="40"/>
-        <v>0.29283747292997886</v>
-      </c>
-      <c r="W35" s="10">
-        <f t="shared" si="40"/>
-        <v>0.28885446135883963</v>
-      </c>
-      <c r="X35" s="10">
-        <f t="shared" si="40"/>
-        <v>0.29045172339970027</v>
-      </c>
-      <c r="Y35" s="10">
-        <f t="shared" si="40"/>
-        <v>0.27028135189487867</v>
-      </c>
-      <c r="Z35" s="10">
-        <f t="shared" si="40"/>
-        <v>0.26819438495385695</v>
-      </c>
-      <c r="AA35" s="10">
-        <f t="shared" ref="AA35" si="41">AA10/AA16</f>
-        <v>0.27996717700662938</v>
+        <v>0.28986163196689513</v>
       </c>
     </row>
     <row r="36" spans="1:35" x14ac:dyDescent="0.2">
@@ -4916,81 +5064,88 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10">
+        <f t="shared" si="30"/>
+        <v>2.5315405046480777E-2</v>
+      </c>
+      <c r="H36" s="10">
         <f t="shared" si="31"/>
-        <v>2.5315405046480777E-2</v>
-      </c>
-      <c r="H36" s="10">
+        <v>1.1631562401760442E-2</v>
+      </c>
+      <c r="I36" s="10">
         <f t="shared" si="32"/>
-        <v>1.1631562401760442E-2</v>
-      </c>
-      <c r="I36" s="10">
+        <v>1.5468298487166354E-2</v>
+      </c>
+      <c r="J36" s="10">
         <f t="shared" si="33"/>
-        <v>1.5468298487166354E-2</v>
-      </c>
-      <c r="J36" s="10">
+        <v>0.53823752848822481</v>
+      </c>
+      <c r="K36" s="10">
         <f t="shared" si="34"/>
-        <v>0.53823752848822481</v>
-      </c>
-      <c r="K36" s="10">
+        <v>-0.10054237836962676</v>
+      </c>
+      <c r="L36" s="10">
         <f t="shared" si="35"/>
-        <v>-0.10054237836962676</v>
-      </c>
-      <c r="L36" s="10">
+        <v>-7.1628340584213746E-2</v>
+      </c>
+      <c r="M36" s="10">
         <f t="shared" si="36"/>
-        <v>-7.1628340584213746E-2</v>
-      </c>
-      <c r="M36" s="10">
-        <f t="shared" si="37"/>
         <v>-8.8550385001673892E-2</v>
       </c>
       <c r="N36" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.11408346365956046</v>
       </c>
       <c r="O36" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>2.2590225902259009E-2</v>
       </c>
       <c r="P36" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>1.4560669456066933E-2</v>
       </c>
       <c r="Q36" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>1.120293847566578E-2</v>
       </c>
-      <c r="R36" s="10"/>
+      <c r="R36" s="10">
+        <f t="shared" si="36"/>
+        <v>-3.6235250394871521E-3</v>
+      </c>
       <c r="T36" s="10">
-        <f t="shared" ref="T36:Z36" si="42">T11/T16</f>
+        <f t="shared" ref="T36:Z36" si="41">T11/T16</f>
         <v>3.8354809462318326E-2</v>
       </c>
       <c r="U36" s="10">
+        <f t="shared" si="41"/>
+        <v>3.589232303090728E-2</v>
+      </c>
+      <c r="V36" s="10">
+        <f t="shared" si="41"/>
+        <v>3.4221853861989678E-2</v>
+      </c>
+      <c r="W36" s="10">
+        <f t="shared" si="41"/>
+        <v>3.102968251829898E-2</v>
+      </c>
+      <c r="X36" s="10">
+        <f t="shared" si="41"/>
+        <v>3.4767715692571186E-2</v>
+      </c>
+      <c r="Y36" s="10">
+        <f t="shared" si="41"/>
+        <v>3.3719272897670696E-2</v>
+      </c>
+      <c r="Z36" s="10">
+        <f t="shared" si="41"/>
+        <v>4.039951715275885E-2</v>
+      </c>
+      <c r="AA36" s="10">
+        <f t="shared" ref="AA36:AB36" si="42">AA11/AA16</f>
+        <v>4.7312617417780561E-2</v>
+      </c>
+      <c r="AB36" s="10">
         <f t="shared" si="42"/>
-        <v>3.589232303090728E-2</v>
-      </c>
-      <c r="V36" s="10">
-        <f t="shared" si="42"/>
-        <v>3.4221853861989678E-2</v>
-      </c>
-      <c r="W36" s="10">
-        <f t="shared" si="42"/>
-        <v>3.102968251829898E-2</v>
-      </c>
-      <c r="X36" s="10">
-        <f t="shared" si="42"/>
-        <v>3.4767715692571186E-2</v>
-      </c>
-      <c r="Y36" s="10">
-        <f t="shared" si="42"/>
-        <v>3.3719272897670696E-2</v>
-      </c>
-      <c r="Z36" s="10">
-        <f t="shared" si="42"/>
-        <v>4.039951715275885E-2</v>
-      </c>
-      <c r="AA36" s="10">
-        <f t="shared" ref="AA36" si="43">AA11/AA16</f>
-        <v>4.7312617417780561E-2</v>
+        <v>4.73942842363895E-2</v>
       </c>
     </row>
     <row r="37" spans="1:35" x14ac:dyDescent="0.2">
@@ -5002,81 +5157,88 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10">
+        <f t="shared" si="30"/>
+        <v>-8.5536547433903598E-2</v>
+      </c>
+      <c r="H37" s="10">
         <f t="shared" si="31"/>
-        <v>-8.5536547433903598E-2</v>
-      </c>
-      <c r="H37" s="10">
+        <v>-0.11433447098976113</v>
+      </c>
+      <c r="I37" s="10">
         <f t="shared" si="32"/>
-        <v>-0.11433447098976113</v>
-      </c>
-      <c r="I37" s="10">
+        <v>-0.19117647058823528</v>
+      </c>
+      <c r="J37" s="10">
         <f t="shared" si="33"/>
-        <v>-0.19117647058823528</v>
-      </c>
-      <c r="J37" s="10">
+        <v>-4.9504950495049549E-2</v>
+      </c>
+      <c r="K37" s="10">
         <f t="shared" si="34"/>
-        <v>-4.9504950495049549E-2</v>
-      </c>
-      <c r="K37" s="10">
+        <v>-0.14795918367346939</v>
+      </c>
+      <c r="L37" s="10">
         <f t="shared" si="35"/>
-        <v>-0.14795918367346939</v>
-      </c>
-      <c r="L37" s="10">
+        <v>-0.17341040462427748</v>
+      </c>
+      <c r="M37" s="10">
         <f t="shared" si="36"/>
-        <v>-0.17341040462427748</v>
-      </c>
-      <c r="M37" s="10">
-        <f t="shared" si="37"/>
         <v>-0.18181818181818177</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.25624999999999998</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.26946107784431139</v>
       </c>
       <c r="P37" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.30069930069930073</v>
       </c>
       <c r="Q37" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>-0.3481481481481481</v>
       </c>
-      <c r="R37" s="10"/>
+      <c r="R37" s="10">
+        <f t="shared" si="36"/>
+        <v>-0.31652661064425769</v>
+      </c>
       <c r="T37" s="10">
-        <f t="shared" ref="T37:Z37" si="44">T14/T16</f>
+        <f t="shared" ref="T37:Z37" si="43">T14/T16</f>
         <v>5.1817457482759566E-2</v>
       </c>
       <c r="U37" s="10">
+        <f t="shared" si="43"/>
+        <v>4.8725618017741647E-2</v>
+      </c>
+      <c r="V37" s="10">
+        <f t="shared" si="43"/>
+        <v>4.9354329866588241E-2</v>
+      </c>
+      <c r="W37" s="10">
+        <f t="shared" si="43"/>
+        <v>4.9508285059948809E-2</v>
+      </c>
+      <c r="X37" s="10">
+        <f t="shared" si="43"/>
+        <v>5.0224791265253692E-2</v>
+      </c>
+      <c r="Y37" s="10">
+        <f t="shared" si="43"/>
+        <v>4.7386609914676768E-2</v>
+      </c>
+      <c r="Z37" s="10">
+        <f t="shared" si="43"/>
+        <v>4.0535804680503093E-2</v>
+      </c>
+      <c r="AA37" s="10">
+        <f t="shared" ref="AA37:AB37" si="44">AA14/AA16</f>
+        <v>3.6537174199399683E-2</v>
+      </c>
+      <c r="AB37" s="10">
         <f t="shared" si="44"/>
-        <v>4.8725618017741647E-2</v>
-      </c>
-      <c r="V37" s="10">
-        <f t="shared" si="44"/>
-        <v>4.9354329866588241E-2</v>
-      </c>
-      <c r="W37" s="10">
-        <f t="shared" si="44"/>
-        <v>4.9508285059948809E-2</v>
-      </c>
-      <c r="X37" s="10">
-        <f t="shared" si="44"/>
-        <v>5.0224791265253692E-2</v>
-      </c>
-      <c r="Y37" s="10">
-        <f t="shared" si="44"/>
-        <v>4.7386609914676768E-2</v>
-      </c>
-      <c r="Z37" s="10">
-        <f t="shared" si="44"/>
-        <v>4.0535804680503093E-2</v>
-      </c>
-      <c r="AA37" s="10">
-        <f t="shared" ref="AA37" si="45">AA14/AA16</f>
-        <v>3.6537174199399683E-2</v>
+        <v>2.5302814776498986E-2</v>
       </c>
     </row>
     <row r="38" spans="1:35" x14ac:dyDescent="0.2">
@@ -5100,179 +5262,191 @@
         <v>-2.8238828389034909E-2</v>
       </c>
       <c r="H38" s="13">
-        <f t="shared" ref="H38:Q38" si="46">H16/D16-1</f>
+        <f t="shared" ref="H38:R38" si="45">H16/D16-1</f>
         <v>5.482538490424238E-3</v>
       </c>
       <c r="I38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>3.1476997578692156E-3</v>
       </c>
       <c r="J38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>0.51550853570569855</v>
       </c>
       <c r="K38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-0.10433572919081846</v>
       </c>
       <c r="L38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-7.7233343292500756E-2</v>
       </c>
       <c r="M38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-9.3330115053503859E-2</v>
       </c>
       <c r="N38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-0.11970490242741549</v>
       </c>
       <c r="O38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>1.1303822590387425E-2</v>
       </c>
       <c r="P38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>5.9090173223248499E-3</v>
       </c>
       <c r="Q38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>8.8739018546446502E-4</v>
       </c>
-      <c r="R38" s="13"/>
+      <c r="R38" s="13">
+        <f t="shared" si="45"/>
+        <v>-1.1264305668198582E-2</v>
+      </c>
       <c r="S38" s="13"/>
       <c r="T38" s="12" t="s">
         <v>43</v>
       </c>
       <c r="U38" s="13">
-        <f t="shared" ref="U38:AA38" si="47">U16/T16-1</f>
+        <f t="shared" ref="U38:AB38" si="46">U16/T16-1</f>
         <v>7.4731433909388079E-2</v>
       </c>
       <c r="V38" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-4.3817266150267153E-2</v>
       </c>
       <c r="W38" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>0.19076009945726269</v>
       </c>
       <c r="X38" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>4.8767344739323759E-2</v>
       </c>
       <c r="Y38" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>9.6488974523656568E-2</v>
       </c>
       <c r="Z38" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>2.8310912392370824E-3</v>
       </c>
       <c r="AA38" s="13">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-9.8380125384525563E-2</v>
       </c>
-      <c r="AB38" s="10"/>
+      <c r="AB38" s="13">
+        <f t="shared" si="46"/>
+        <v>1.9218726381480256E-3</v>
+      </c>
     </row>
     <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B39" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C39" s="10">
-        <f t="shared" ref="C39:N39" si="48">C18/C16</f>
+        <f t="shared" ref="C39:N39" si="47">C18/C16</f>
         <v>0.44257901789233073</v>
       </c>
       <c r="D39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.42891475779196397</v>
+      </c>
+      <c r="E39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.43349475383373687</v>
+      </c>
+      <c r="F39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.57489781197403222</v>
+      </c>
+      <c r="G39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.44207434886776414</v>
+      </c>
+      <c r="H39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.44599641469973111</v>
+      </c>
+      <c r="I39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.44750181028240404</v>
+      </c>
+      <c r="J39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.44693003331746789</v>
+      </c>
+      <c r="K39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.45361981189058592</v>
+      </c>
+      <c r="L39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.43621499109600131</v>
+      </c>
+      <c r="M39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.41485491170467653</v>
+      </c>
+      <c r="N39" s="10">
+        <f t="shared" si="47"/>
+        <v>0.40272145624943678</v>
+      </c>
+      <c r="O39" s="10">
+        <f t="shared" ref="O39:P39" si="48">O18/O16</f>
+        <v>0.42175767918088736</v>
+      </c>
+      <c r="P39" s="10">
         <f t="shared" si="48"/>
-        <v>0.42891475779196397</v>
-      </c>
-      <c r="E39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.43349475383373687</v>
-      </c>
-      <c r="F39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.57489781197403222</v>
-      </c>
-      <c r="G39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.44207434886776414</v>
-      </c>
-      <c r="H39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.44599641469973111</v>
-      </c>
-      <c r="I39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.44750181028240404</v>
-      </c>
-      <c r="J39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.44693003331746789</v>
-      </c>
-      <c r="K39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.45361981189058592</v>
-      </c>
-      <c r="L39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.43621499109600131</v>
-      </c>
-      <c r="M39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.41485491170467653</v>
-      </c>
-      <c r="N39" s="10">
-        <f t="shared" si="48"/>
-        <v>0.40272145624943678</v>
-      </c>
-      <c r="O39" s="10">
-        <f t="shared" ref="O39:P39" si="49">O18/O16</f>
-        <v>0.42175767918088736</v>
-      </c>
-      <c r="P39" s="10">
+        <v>0.40597086988009978</v>
+      </c>
+      <c r="Q39" s="10">
+        <f t="shared" ref="Q39:R39" si="49">Q18/Q16</f>
+        <v>0.40163135029701214</v>
+      </c>
+      <c r="R39" s="10">
         <f t="shared" si="49"/>
-        <v>0.40597086988009978</v>
-      </c>
-      <c r="Q39" s="10">
-        <f t="shared" ref="Q39" si="50">Q18/Q16</f>
-        <v>0.40163135029701214</v>
-      </c>
-      <c r="R39" s="10"/>
+        <v>0.49152387896463728</v>
+      </c>
       <c r="S39" s="10"/>
       <c r="T39" s="10">
-        <f t="shared" ref="T39:AA39" si="51">T18/T16</f>
+        <f t="shared" ref="T39:AA39" si="50">T18/T16</f>
         <v>0.43838777921257244</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.44671114860546568</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.43421650669732376</v>
       </c>
       <c r="W39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.44820153576721</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.45983729394134021</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.43524610969014194</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.44560180678322497</v>
       </c>
       <c r="AA39" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>0.42734673605562634</v>
       </c>
-      <c r="AB39" s="10"/>
+      <c r="AB39" s="10">
+        <f t="shared" ref="AB39" si="51">AB18/AB16</f>
+        <v>0.42913487650329757</v>
+      </c>
     </row>
     <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B40" s="3" t="s">
@@ -5335,10 +5509,13 @@
         <v>8.095276414259274E-2</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" ref="Q40" si="54">Q22/Q16</f>
+        <f t="shared" ref="Q40:R40" si="54">Q22/Q16</f>
         <v>4.9029169252593312E-2</v>
       </c>
-      <c r="R40" s="10"/>
+      <c r="R40" s="10">
+        <f t="shared" si="54"/>
+        <v>0.11948596427269413</v>
+      </c>
       <c r="S40" s="10"/>
       <c r="T40" s="10">
         <f t="shared" ref="T40:AA40" si="55">T22/T16</f>
@@ -5372,196 +5549,208 @@
         <f t="shared" si="55"/>
         <v>7.9941264117126265E-2</v>
       </c>
-      <c r="AB40" s="10"/>
+      <c r="AB40" s="10">
+        <f t="shared" ref="AB40" si="56">AB22/AB16</f>
+        <v>8.1835423940687102E-2</v>
+      </c>
     </row>
     <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B41" s="3" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" ref="C41:N41" si="56">C27/C16</f>
+        <f t="shared" ref="C41:N41" si="57">C27/C16</f>
         <v>0.11570899345787027</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>9.9962448366503948E-2</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.10008071025020178</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.24128396249098341</v>
       </c>
       <c r="G41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.11206430172347168</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.11786674634000598</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>9.4295599002333252E-2</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.11899095668729176</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>9.0689446889291564E-2</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>9.4139549943338188E-2</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>7.045878072588517E-2</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>1.9014147967919257E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" ref="O41:P41" si="57">O27/O16</f>
+        <f t="shared" ref="O41:P41" si="58">O27/O16</f>
         <v>6.2030716723549491E-2</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>6.3732196024784749E-2</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" ref="Q41" si="58">Q27/Q16</f>
+        <f t="shared" ref="Q41:R41" si="59">Q27/Q16</f>
         <v>4.6103377959038919E-2</v>
       </c>
-      <c r="R41" s="10"/>
+      <c r="R41" s="10">
+        <f t="shared" si="59"/>
+        <v>9.7429821363470656E-2</v>
+      </c>
       <c r="S41" s="10"/>
       <c r="T41" s="10">
-        <f t="shared" ref="T41:AA41" si="59">T27/T16</f>
+        <f t="shared" ref="T41:AA41" si="60">T27/T16</f>
         <v>5.3108772701046789E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.10299869621903521</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.7882255434056085E-2</v>
       </c>
       <c r="W41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.12858682473393507</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.12943695140226932</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>9.8990569537458259E-2</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.11097698687745804</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.9511326092120324E-2</v>
       </c>
-      <c r="AB41" s="10"/>
+      <c r="AB41" s="10">
+        <f t="shared" ref="AB41" si="61">AB27/AB16</f>
+        <v>6.6985645933014357E-2</v>
+      </c>
     </row>
     <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B42" s="3" t="s">
         <v>42</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" ref="C42:N42" si="60">C26/C25</f>
+        <f t="shared" ref="C42:N42" si="62">C26/C25</f>
         <v>0.19693654266958424</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.19333333333333333</v>
       </c>
       <c r="E42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.16046039268788084</v>
       </c>
       <c r="F42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>-0.18337264150943397</v>
       </c>
       <c r="G42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.12014563106796117</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.17898022892819979</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.16524216524216523</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.13093858632676708</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.19586840091813312</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.1786723163841808</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>5.9241706161137442E-2</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>0.33647798742138363</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" ref="O42:P42" si="61">O26/O25</f>
+        <f t="shared" ref="O42:P42" si="63">O26/O25</f>
         <v>0.21149674620390455</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>0.2072072072072072</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" ref="Q42" si="62">Q26/Q25</f>
+        <f t="shared" ref="Q42:R42" si="64">Q26/Q25</f>
         <v>0.2</v>
       </c>
-      <c r="R42" s="10"/>
+      <c r="R42" s="10">
+        <f t="shared" si="64"/>
+        <v>0.19563581640331076</v>
+      </c>
       <c r="S42" s="10"/>
       <c r="T42" s="10">
-        <f t="shared" ref="T42:Y42" si="63">T26/T25</f>
+        <f t="shared" ref="T42:Y42" si="65">T26/T25</f>
         <v>0.55306358381502885</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.16079983336804832</v>
       </c>
       <c r="V42" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.12054035330793211</v>
       </c>
       <c r="W42" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.14021918630836211</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>9.0963764847391368E-2</v>
       </c>
       <c r="Y42" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="65"/>
         <v>0.18238993710691823</v>
       </c>
       <c r="Z42" s="10">
@@ -5570,7 +5759,9 @@
       <c r="AA42" s="10">
         <v>0.09</v>
       </c>
-      <c r="AB42" s="10"/>
+      <c r="AB42" s="10">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="T43" s="14"/>
@@ -5670,8 +5861,12 @@
       <c r="Z47" s="5">
         <v>9860</v>
       </c>
-      <c r="AA47" s="5"/>
-      <c r="AB47" s="5"/>
+      <c r="AA47" s="5">
+        <v>7464</v>
+      </c>
+      <c r="AB47" s="5">
+        <v>7563</v>
+      </c>
       <c r="AC47" s="5"/>
       <c r="AD47" s="5"/>
       <c r="AE47" s="5"/>
@@ -5732,8 +5927,12 @@
       <c r="Z48" s="5">
         <v>1722</v>
       </c>
-      <c r="AA48" s="5"/>
-      <c r="AB48" s="5"/>
+      <c r="AA48" s="5">
+        <v>1687</v>
+      </c>
+      <c r="AB48" s="5">
+        <v>1464</v>
+      </c>
       <c r="AC48" s="5"/>
       <c r="AD48" s="5"/>
       <c r="AE48" s="5"/>
@@ -5794,8 +5993,12 @@
       <c r="Z49" s="5">
         <v>4427</v>
       </c>
-      <c r="AA49" s="5"/>
-      <c r="AB49" s="5"/>
+      <c r="AA49" s="5">
+        <v>4717</v>
+      </c>
+      <c r="AB49" s="5">
+        <v>5931</v>
+      </c>
       <c r="AC49" s="5"/>
       <c r="AD49" s="5"/>
       <c r="AE49" s="5"/>
@@ -5856,8 +6059,12 @@
       <c r="Z50" s="5">
         <v>7519</v>
       </c>
-      <c r="AA50" s="5"/>
-      <c r="AB50" s="5"/>
+      <c r="AA50" s="5">
+        <v>7489</v>
+      </c>
+      <c r="AB50" s="5">
+        <v>7501</v>
+      </c>
       <c r="AC50" s="5"/>
       <c r="AD50" s="5"/>
       <c r="AE50" s="5"/>
@@ -5918,8 +6125,12 @@
       <c r="Z51" s="5">
         <v>1854</v>
       </c>
-      <c r="AA51" s="5"/>
-      <c r="AB51" s="5"/>
+      <c r="AA51" s="5">
+        <v>2005</v>
+      </c>
+      <c r="AB51" s="5">
+        <v>2144</v>
+      </c>
       <c r="AC51" s="5"/>
       <c r="AD51" s="5"/>
       <c r="AE51" s="5"/>
@@ -5933,31 +6144,31 @@
         <v>51</v>
       </c>
       <c r="C52" s="8">
-        <f t="shared" ref="C52:I52" si="64">SUM(C47:C51)</f>
+        <f t="shared" ref="C52:I52" si="66">SUM(C47:C51)</f>
         <v>0</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="E52" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>25202</v>
       </c>
       <c r="F52" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>0</v>
       </c>
       <c r="G52" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>24250</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>24631</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="66"/>
         <v>24753</v>
       </c>
       <c r="J52" s="8">
@@ -5977,35 +6188,41 @@
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
       <c r="T52" s="8">
-        <f t="shared" ref="T52:Z52" si="65">SUM(T47:T51)</f>
+        <f t="shared" ref="T52:AB52" si="67">SUM(T47:T51)</f>
         <v>15134</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>16525</v>
       </c>
       <c r="V52" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>20556</v>
       </c>
       <c r="W52" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>26291</v>
       </c>
       <c r="X52" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>28213</v>
       </c>
       <c r="Y52" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>25202</v>
       </c>
       <c r="Z52" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="67"/>
         <v>25382</v>
       </c>
-      <c r="AA52" s="5"/>
-      <c r="AB52" s="5"/>
+      <c r="AA52" s="8">
+        <f t="shared" si="67"/>
+        <v>23362</v>
+      </c>
+      <c r="AB52" s="8">
+        <f t="shared" si="67"/>
+        <v>24603</v>
+      </c>
       <c r="AC52" s="5"/>
       <c r="AD52" s="5"/>
       <c r="AE52" s="5"/>
@@ -6066,8 +6283,12 @@
       <c r="Z53" s="5">
         <v>5000</v>
       </c>
-      <c r="AA53" s="5"/>
-      <c r="AB53" s="5"/>
+      <c r="AA53" s="5">
+        <v>4828</v>
+      </c>
+      <c r="AB53" s="5">
+        <v>4796</v>
+      </c>
       <c r="AC53" s="5"/>
       <c r="AD53" s="5"/>
       <c r="AE53" s="5"/>
@@ -6128,8 +6349,12 @@
       <c r="Z54" s="5">
         <v>2718</v>
       </c>
-      <c r="AA54" s="5"/>
-      <c r="AB54" s="5"/>
+      <c r="AA54" s="5">
+        <v>2712</v>
+      </c>
+      <c r="AB54" s="5">
+        <v>2838</v>
+      </c>
       <c r="AC54" s="5"/>
       <c r="AD54" s="5"/>
       <c r="AE54" s="5"/>
@@ -6190,8 +6415,12 @@
       <c r="Z55" s="5">
         <v>259</v>
       </c>
-      <c r="AA55" s="5"/>
-      <c r="AB55" s="5"/>
+      <c r="AA55" s="5">
+        <v>259</v>
+      </c>
+      <c r="AB55" s="5">
+        <v>259</v>
+      </c>
       <c r="AC55" s="5"/>
       <c r="AD55" s="5"/>
       <c r="AE55" s="5"/>
@@ -6252,8 +6481,12 @@
       <c r="Z56" s="5">
         <v>240</v>
       </c>
-      <c r="AA56" s="5"/>
-      <c r="AB56" s="5"/>
+      <c r="AA56" s="5">
+        <v>240</v>
+      </c>
+      <c r="AB56" s="5">
+        <v>240</v>
+      </c>
       <c r="AC56" s="5"/>
       <c r="AD56" s="5"/>
       <c r="AE56" s="5"/>
@@ -6314,8 +6547,12 @@
       <c r="Z57" s="5">
         <v>4511</v>
       </c>
-      <c r="AA57" s="5"/>
-      <c r="AB57" s="5"/>
+      <c r="AA57" s="5">
+        <v>5178</v>
+      </c>
+      <c r="AB57" s="5">
+        <v>5674</v>
+      </c>
       <c r="AC57" s="5"/>
       <c r="AD57" s="5"/>
       <c r="AE57" s="5"/>
@@ -6329,31 +6566,31 @@
         <v>57</v>
       </c>
       <c r="C58" s="8">
-        <f t="shared" ref="C58:I58" si="66">SUM(C53:C57)</f>
+        <f t="shared" ref="C58:I58" si="68">SUM(C53:C57)</f>
         <v>0</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="E58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>12329</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>0</v>
       </c>
       <c r="G58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>12536</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>12572</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="68"/>
         <v>12603</v>
       </c>
       <c r="J58" s="8">
@@ -6373,35 +6610,41 @@
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
       <c r="T58" s="8">
-        <f t="shared" ref="T58:Z58" si="67">SUM(T53:T57)</f>
+        <f t="shared" ref="T58:AB58" si="69">SUM(T53:T57)</f>
         <v>7402</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>7192</v>
       </c>
       <c r="V58" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>10786</v>
       </c>
       <c r="W58" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>11449</v>
       </c>
       <c r="X58" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>12108</v>
       </c>
       <c r="Y58" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>12329</v>
       </c>
       <c r="Z58" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="69"/>
         <v>12728</v>
       </c>
-      <c r="AA58" s="5"/>
-      <c r="AB58" s="5"/>
+      <c r="AA58" s="8">
+        <f t="shared" si="69"/>
+        <v>13217</v>
+      </c>
+      <c r="AB58" s="8">
+        <f t="shared" si="69"/>
+        <v>13807</v>
+      </c>
       <c r="AC58" s="5"/>
       <c r="AD58" s="5"/>
       <c r="AE58" s="5"/>
@@ -6450,31 +6693,31 @@
         <v>58</v>
       </c>
       <c r="C60" s="8">
-        <f t="shared" ref="C60:I60" si="68">C58+C52</f>
+        <f t="shared" ref="C60:I60" si="70">C58+C52</f>
         <v>0</v>
       </c>
       <c r="D60" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="E60" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>37531</v>
       </c>
       <c r="F60" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>0</v>
       </c>
       <c r="G60" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>36786</v>
       </c>
       <c r="H60" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>37203</v>
       </c>
       <c r="I60" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="70"/>
         <v>37356</v>
       </c>
       <c r="J60" s="8">
@@ -6494,35 +6737,41 @@
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
       <c r="T60" s="8">
-        <f t="shared" ref="T60:Z60" si="69">T58+T52</f>
+        <f t="shared" ref="T60:AB60" si="71">T58+T52</f>
         <v>22536</v>
       </c>
       <c r="U60" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>23717</v>
       </c>
       <c r="V60" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>31342</v>
       </c>
       <c r="W60" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>37740</v>
       </c>
       <c r="X60" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>40321</v>
       </c>
       <c r="Y60" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>37531</v>
       </c>
       <c r="Z60" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="71"/>
         <v>38110</v>
       </c>
-      <c r="AA60" s="5"/>
-      <c r="AB60" s="5"/>
+      <c r="AA60" s="8">
+        <f t="shared" si="71"/>
+        <v>36579</v>
+      </c>
+      <c r="AB60" s="8">
+        <f t="shared" si="71"/>
+        <v>38410</v>
+      </c>
       <c r="AC60" s="5"/>
       <c r="AD60" s="5"/>
       <c r="AE60" s="5"/>
@@ -6594,7 +6843,7 @@
       <c r="X62" s="5"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
-      <c r="AA62" s="5"/>
+      <c r="AA62" s="8"/>
       <c r="AB62" s="5"/>
       <c r="AC62" s="5"/>
       <c r="AD62" s="5"/>
@@ -6656,8 +6905,12 @@
       <c r="Z63" s="5">
         <v>1000</v>
       </c>
-      <c r="AA63" s="5"/>
-      <c r="AB63" s="5"/>
+      <c r="AA63" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB63" s="5">
+        <v>2000</v>
+      </c>
       <c r="AC63" s="5"/>
       <c r="AD63" s="5"/>
       <c r="AE63" s="5"/>
@@ -6716,11 +6969,15 @@
         <v>6</v>
       </c>
       <c r="Z64" s="5">
-        <f t="shared" ref="Z64" si="70">I64</f>
+        <f t="shared" ref="Z64" si="72">I64</f>
         <v>6</v>
       </c>
-      <c r="AA64" s="5"/>
-      <c r="AB64" s="5"/>
+      <c r="AA64" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB64" s="5">
+        <v>0</v>
+      </c>
       <c r="AC64" s="5"/>
       <c r="AD64" s="5"/>
       <c r="AE64" s="5"/>
@@ -6781,8 +7038,12 @@
       <c r="Z65" s="5">
         <v>2851</v>
       </c>
-      <c r="AA65" s="5"/>
-      <c r="AB65" s="5"/>
+      <c r="AA65" s="5">
+        <v>3479</v>
+      </c>
+      <c r="AB65" s="5">
+        <v>3600</v>
+      </c>
       <c r="AC65" s="5"/>
       <c r="AD65" s="5"/>
       <c r="AE65" s="5"/>
@@ -6843,8 +7104,12 @@
       <c r="Z66" s="5">
         <v>477</v>
       </c>
-      <c r="AA66" s="5"/>
-      <c r="AB66" s="5"/>
+      <c r="AA66" s="5">
+        <v>502</v>
+      </c>
+      <c r="AB66" s="5">
+        <v>478</v>
+      </c>
       <c r="AC66" s="5"/>
       <c r="AD66" s="5"/>
       <c r="AE66" s="5"/>
@@ -6905,8 +7170,12 @@
       <c r="Z67" s="5">
         <v>5725</v>
       </c>
-      <c r="AA67" s="5"/>
-      <c r="AB67" s="5"/>
+      <c r="AA67" s="5">
+        <v>5916</v>
+      </c>
+      <c r="AB67" s="5">
+        <v>6092</v>
+      </c>
       <c r="AC67" s="5"/>
       <c r="AD67" s="5"/>
       <c r="AE67" s="5"/>
@@ -6967,8 +7236,12 @@
       <c r="Z68" s="5">
         <v>534</v>
       </c>
-      <c r="AA68" s="5"/>
-      <c r="AB68" s="5"/>
+      <c r="AA68" s="5">
+        <v>669</v>
+      </c>
+      <c r="AB68" s="5">
+        <v>377</v>
+      </c>
       <c r="AC68" s="5"/>
       <c r="AD68" s="5"/>
       <c r="AE68" s="5"/>
@@ -6982,31 +7255,31 @@
         <v>51</v>
       </c>
       <c r="C69" s="8">
-        <f t="shared" ref="C69:I69" si="71">SUM(C63:C68)</f>
+        <f t="shared" ref="C69:I69" si="73">SUM(C63:C68)</f>
         <v>0</v>
       </c>
       <c r="D69" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="E69" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>9256</v>
       </c>
       <c r="F69" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>0</v>
       </c>
       <c r="G69" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>8461</v>
       </c>
       <c r="H69" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>8999</v>
       </c>
       <c r="I69" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="73"/>
         <v>9029</v>
       </c>
       <c r="J69" s="8">
@@ -7026,35 +7299,41 @@
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
       <c r="T69" s="8">
-        <f t="shared" ref="T69:V69" si="72">SUM(T63:T68)</f>
+        <f t="shared" ref="T69:V69" si="74">SUM(T63:T68)</f>
         <v>6040</v>
       </c>
       <c r="U69" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>7866</v>
       </c>
       <c r="V69" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="74"/>
         <v>8284</v>
       </c>
       <c r="W69" s="8">
-        <f t="shared" ref="W69" si="73">SUM(W63:W68)</f>
+        <f t="shared" ref="W69" si="75">SUM(W63:W68)</f>
         <v>9674</v>
       </c>
       <c r="X69" s="8">
-        <f t="shared" ref="X69" si="74">SUM(X63:X68)</f>
+        <f t="shared" ref="X69" si="76">SUM(X63:X68)</f>
         <v>10730</v>
       </c>
       <c r="Y69" s="8">
-        <f t="shared" ref="Y69" si="75">SUM(Y63:Y68)</f>
+        <f t="shared" ref="Y69" si="77">SUM(Y63:Y68)</f>
         <v>9256</v>
       </c>
       <c r="Z69" s="8">
-        <f t="shared" ref="Z69" si="76">SUM(Z63:Z68)</f>
+        <f t="shared" ref="Z69:AB69" si="78">SUM(Z63:Z68)</f>
         <v>10593</v>
       </c>
-      <c r="AA69" s="5"/>
-      <c r="AB69" s="5"/>
+      <c r="AA69" s="8">
+        <f t="shared" si="78"/>
+        <v>10566</v>
+      </c>
+      <c r="AB69" s="8">
+        <f t="shared" si="78"/>
+        <v>12547</v>
+      </c>
       <c r="AC69" s="5"/>
       <c r="AD69" s="5"/>
       <c r="AE69" s="5"/>
@@ -7115,8 +7394,12 @@
       <c r="Z70" s="5">
         <v>7903</v>
       </c>
-      <c r="AA70" s="5"/>
-      <c r="AB70" s="5"/>
+      <c r="AA70" s="5">
+        <v>7961</v>
+      </c>
+      <c r="AB70" s="5">
+        <v>5942</v>
+      </c>
       <c r="AC70" s="5"/>
       <c r="AD70" s="5"/>
       <c r="AE70" s="5"/>
@@ -7177,8 +7460,12 @@
       <c r="Z71" s="5">
         <v>2566</v>
       </c>
-      <c r="AA71" s="5"/>
-      <c r="AB71" s="5"/>
+      <c r="AA71" s="5">
+        <v>2550</v>
+      </c>
+      <c r="AB71" s="5">
+        <v>2613</v>
+      </c>
       <c r="AC71" s="5"/>
       <c r="AD71" s="5"/>
       <c r="AE71" s="5"/>
@@ -7239,8 +7526,12 @@
       <c r="Z72" s="5">
         <v>2618</v>
       </c>
-      <c r="AA72" s="5"/>
-      <c r="AB72" s="5"/>
+      <c r="AA72" s="5">
+        <v>2289</v>
+      </c>
+      <c r="AB72" s="5">
+        <v>2443</v>
+      </c>
       <c r="AC72" s="5"/>
       <c r="AD72" s="5"/>
       <c r="AE72" s="5"/>
@@ -7254,31 +7545,31 @@
         <v>69</v>
       </c>
       <c r="C73" s="8">
-        <f t="shared" ref="C73:I73" si="77">SUM(C70:C72)</f>
+        <f t="shared" ref="C73:I73" si="79">SUM(C70:C72)</f>
         <v>0</v>
       </c>
       <c r="D73" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="E73" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>14271</v>
       </c>
       <c r="F73" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="G73" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>14354</v>
       </c>
       <c r="H73" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>14058</v>
       </c>
       <c r="I73" s="8">
-        <f t="shared" si="77"/>
+        <f t="shared" si="79"/>
         <v>14101</v>
       </c>
       <c r="J73" s="8">
@@ -7298,35 +7589,41 @@
       <c r="R73" s="5"/>
       <c r="S73" s="5"/>
       <c r="T73" s="8">
-        <f t="shared" ref="T73:Z73" si="78">SUM(T70:T72)</f>
+        <f t="shared" ref="T73:AB73" si="80">SUM(T70:T72)</f>
         <v>6684</v>
       </c>
       <c r="U73" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>6811</v>
       </c>
       <c r="V73" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>15003</v>
       </c>
       <c r="W73" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>15299</v>
       </c>
       <c r="X73" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>14310</v>
       </c>
       <c r="Y73" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>14271</v>
       </c>
       <c r="Z73" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="80"/>
         <v>13087</v>
       </c>
-      <c r="AA73" s="5"/>
-      <c r="AB73" s="5"/>
+      <c r="AA73" s="8">
+        <f t="shared" si="80"/>
+        <v>12800</v>
+      </c>
+      <c r="AB73" s="8">
+        <f t="shared" si="80"/>
+        <v>10998</v>
+      </c>
       <c r="AC73" s="5"/>
       <c r="AD73" s="5"/>
       <c r="AE73" s="5"/>
@@ -7375,31 +7672,31 @@
         <v>70</v>
       </c>
       <c r="C75" s="8">
-        <f t="shared" ref="C75:I75" si="79">C73+C69</f>
+        <f t="shared" ref="C75:I75" si="81">C73+C69</f>
         <v>0</v>
       </c>
       <c r="D75" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="E75" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>23527</v>
       </c>
       <c r="F75" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="G75" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>22815</v>
       </c>
       <c r="H75" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>23057</v>
       </c>
       <c r="I75" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="81"/>
         <v>23130</v>
       </c>
       <c r="J75" s="8">
@@ -7419,35 +7716,41 @@
       <c r="R75" s="5"/>
       <c r="S75" s="5"/>
       <c r="T75" s="8">
-        <f t="shared" ref="T75:Z75" si="80">T73+T69</f>
+        <f t="shared" ref="T75:AB75" si="82">T73+T69</f>
         <v>12724</v>
       </c>
       <c r="U75" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>14677</v>
       </c>
       <c r="V75" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>23287</v>
       </c>
       <c r="W75" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>24973</v>
       </c>
       <c r="X75" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>25040</v>
       </c>
       <c r="Y75" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>23527</v>
       </c>
       <c r="Z75" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="82"/>
         <v>23680</v>
       </c>
-      <c r="AA75" s="5"/>
-      <c r="AB75" s="5"/>
+      <c r="AA75" s="8">
+        <f t="shared" si="82"/>
+        <v>23366</v>
+      </c>
+      <c r="AB75" s="8">
+        <f t="shared" si="82"/>
+        <v>23545</v>
+      </c>
       <c r="AC75" s="5"/>
       <c r="AD75" s="5"/>
       <c r="AE75" s="5"/>
@@ -7579,8 +7882,12 @@
       <c r="Z78" s="5">
         <v>0</v>
       </c>
-      <c r="AA78" s="5"/>
-      <c r="AB78" s="5"/>
+      <c r="AA78" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="5">
+        <v>0</v>
+      </c>
       <c r="AC78" s="5"/>
       <c r="AD78" s="5"/>
       <c r="AE78" s="5"/>
@@ -7639,8 +7946,12 @@
       <c r="Z79" s="5">
         <v>3</v>
       </c>
-      <c r="AA79" s="5"/>
-      <c r="AB79" s="5"/>
+      <c r="AA79" s="5">
+        <v>3</v>
+      </c>
+      <c r="AB79" s="5">
+        <v>3</v>
+      </c>
       <c r="AC79" s="5"/>
       <c r="AD79" s="5"/>
       <c r="AE79" s="5"/>
@@ -7699,8 +8010,12 @@
       <c r="Z80" s="5">
         <v>13409</v>
       </c>
-      <c r="AA80" s="5"/>
-      <c r="AB80" s="5"/>
+      <c r="AA80" s="5">
+        <v>14195</v>
+      </c>
+      <c r="AB80" s="5">
+        <v>15158</v>
+      </c>
       <c r="AC80" s="5"/>
       <c r="AD80" s="5"/>
       <c r="AE80" s="5"/>
@@ -7759,8 +8074,12 @@
       <c r="Z81" s="5">
         <v>53</v>
       </c>
-      <c r="AA81" s="5"/>
-      <c r="AB81" s="5"/>
+      <c r="AA81" s="5">
+        <v>-258</v>
+      </c>
+      <c r="AB81" s="5">
+        <v>-141</v>
+      </c>
       <c r="AC81" s="5"/>
       <c r="AD81" s="5"/>
       <c r="AE81" s="5"/>
@@ -7819,8 +8138,12 @@
       <c r="Z82" s="5">
         <v>965</v>
       </c>
-      <c r="AA82" s="5"/>
-      <c r="AB82" s="5"/>
+      <c r="AA82" s="5">
+        <v>-727</v>
+      </c>
+      <c r="AB82" s="5">
+        <v>-155</v>
+      </c>
       <c r="AC82" s="5"/>
       <c r="AD82" s="5"/>
       <c r="AE82" s="5"/>
@@ -7834,31 +8157,31 @@
         <v>77</v>
       </c>
       <c r="C83" s="8">
-        <f t="shared" ref="C83:I83" si="81">SUM(C78:C82)</f>
+        <f t="shared" ref="C83:I83" si="83">SUM(C78:C82)</f>
         <v>0</v>
       </c>
       <c r="D83" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="E83" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>14004</v>
       </c>
       <c r="F83" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="G83" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>13971</v>
       </c>
       <c r="H83" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>14146</v>
       </c>
       <c r="I83" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="83"/>
         <v>14226</v>
       </c>
       <c r="J83" s="8">
@@ -7877,35 +8200,41 @@
       <c r="R83" s="5"/>
       <c r="S83" s="5"/>
       <c r="T83" s="8">
-        <f t="shared" ref="T83:Z83" si="82">SUM(T78:T82)</f>
+        <f t="shared" ref="T83:AB83" si="84">SUM(T78:T82)</f>
         <v>9812</v>
       </c>
       <c r="U83" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>9040</v>
       </c>
       <c r="V83" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>8055</v>
       </c>
       <c r="W83" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>12767</v>
       </c>
       <c r="X83" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>15281</v>
       </c>
       <c r="Y83" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>14004</v>
       </c>
       <c r="Z83" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="84"/>
         <v>14430</v>
       </c>
-      <c r="AA83" s="5"/>
-      <c r="AB83" s="5"/>
+      <c r="AA83" s="8">
+        <f t="shared" si="84"/>
+        <v>13213</v>
+      </c>
+      <c r="AB83" s="8">
+        <f t="shared" si="84"/>
+        <v>14865</v>
+      </c>
       <c r="AC83" s="5"/>
       <c r="AD83" s="5"/>
       <c r="AE83" s="5"/>
@@ -7954,19 +8283,19 @@
         <v>78</v>
       </c>
       <c r="C85" s="8">
-        <f t="shared" ref="C85:I85" si="83">C83+C75</f>
+        <f t="shared" ref="C85:I85" si="85">C83+C75</f>
         <v>0</v>
       </c>
       <c r="D85" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="E85" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>37531</v>
       </c>
       <c r="F85" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>0</v>
       </c>
       <c r="G85" s="8">
@@ -7974,11 +8303,11 @@
         <v>36786</v>
       </c>
       <c r="H85" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>37203</v>
       </c>
       <c r="I85" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="85"/>
         <v>37356</v>
       </c>
       <c r="J85" s="8">
@@ -8002,31 +8331,37 @@
         <v>22536</v>
       </c>
       <c r="U85" s="8">
-        <f t="shared" ref="U85:Z85" si="84">U83+U75</f>
+        <f t="shared" ref="U85:AB85" si="86">U83+U75</f>
         <v>23717</v>
       </c>
       <c r="V85" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>31342</v>
       </c>
       <c r="W85" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>37740</v>
       </c>
       <c r="X85" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>40321</v>
       </c>
       <c r="Y85" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>37531</v>
       </c>
       <c r="Z85" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="86"/>
         <v>38110</v>
       </c>
-      <c r="AA85" s="5"/>
-      <c r="AB85" s="5"/>
+      <c r="AA85" s="8">
+        <f t="shared" si="86"/>
+        <v>36579</v>
+      </c>
+      <c r="AB85" s="8">
+        <f t="shared" si="86"/>
+        <v>38410</v>
+      </c>
       <c r="AC85" s="5"/>
       <c r="AD85" s="5"/>
       <c r="AE85" s="5"/>
@@ -8116,35 +8451,35 @@
         <v>80</v>
       </c>
       <c r="C88" s="5">
-        <f t="shared" ref="C88:J88" si="85">C27</f>
+        <f t="shared" ref="C88:J88" si="87">C27</f>
         <v>1468</v>
       </c>
       <c r="D88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1331</v>
       </c>
       <c r="E88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1240</v>
       </c>
       <c r="F88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>2007</v>
       </c>
       <c r="G88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1450</v>
       </c>
       <c r="H88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1578</v>
       </c>
       <c r="I88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1172</v>
       </c>
       <c r="J88" s="5">
-        <f t="shared" si="85"/>
+        <f t="shared" si="87"/>
         <v>1500</v>
       </c>
       <c r="K88" s="5"/>
@@ -8157,35 +8492,41 @@
       <c r="R88" s="5"/>
       <c r="S88" s="5"/>
       <c r="T88" s="5">
-        <f t="shared" ref="T88:Z88" si="86">T27</f>
+        <f t="shared" ref="T88:AB88" si="88">T27</f>
         <v>1933</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>4029</v>
       </c>
       <c r="V88" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>2539</v>
       </c>
       <c r="W88" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>5727</v>
       </c>
       <c r="X88" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>6046</v>
       </c>
       <c r="Y88" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>5070</v>
       </c>
       <c r="Z88" s="5">
-        <f t="shared" si="86"/>
+        <f t="shared" si="88"/>
         <v>5700</v>
       </c>
-      <c r="AA88" s="5"/>
-      <c r="AB88" s="5"/>
+      <c r="AA88" s="5">
+        <f t="shared" si="88"/>
+        <v>3219</v>
+      </c>
+      <c r="AB88" s="5">
+        <f t="shared" si="88"/>
+        <v>3108</v>
+      </c>
       <c r="AC88" s="5"/>
       <c r="AD88" s="5"/>
       <c r="AE88" s="5"/>
@@ -8238,8 +8579,12 @@
       <c r="Z89" s="5">
         <v>796</v>
       </c>
-      <c r="AA89" s="5"/>
-      <c r="AB89" s="5"/>
+      <c r="AA89" s="5">
+        <v>775</v>
+      </c>
+      <c r="AB89" s="5">
+        <v>747</v>
+      </c>
       <c r="AC89" s="5"/>
       <c r="AD89" s="5"/>
       <c r="AE89" s="5"/>
@@ -8292,8 +8637,12 @@
       <c r="Z90" s="5">
         <v>-497</v>
       </c>
-      <c r="AA90" s="5"/>
-      <c r="AB90" s="5"/>
+      <c r="AA90" s="5">
+        <v>-288</v>
+      </c>
+      <c r="AB90" s="5">
+        <v>-96</v>
+      </c>
       <c r="AC90" s="5"/>
       <c r="AD90" s="5"/>
       <c r="AE90" s="5"/>
@@ -8346,8 +8695,12 @@
       <c r="Z91" s="5">
         <v>804</v>
       </c>
-      <c r="AA91" s="5"/>
-      <c r="AB91" s="5"/>
+      <c r="AA91" s="5">
+        <v>709</v>
+      </c>
+      <c r="AB91" s="5">
+        <v>715</v>
+      </c>
       <c r="AC91" s="5"/>
       <c r="AD91" s="5"/>
       <c r="AE91" s="5"/>
@@ -8400,8 +8753,12 @@
       <c r="Z92" s="5">
         <v>48</v>
       </c>
-      <c r="AA92" s="5"/>
-      <c r="AB92" s="5"/>
+      <c r="AA92" s="5">
+        <v>33</v>
+      </c>
+      <c r="AB92" s="5">
+        <v>50</v>
+      </c>
       <c r="AC92" s="5"/>
       <c r="AD92" s="5"/>
       <c r="AE92" s="5"/>
@@ -8454,8 +8811,12 @@
       <c r="Z93" s="5">
         <v>-138</v>
       </c>
-      <c r="AA93" s="5"/>
-      <c r="AB93" s="5"/>
+      <c r="AA93" s="5">
+        <v>37</v>
+      </c>
+      <c r="AB93" s="5">
+        <v>22</v>
+      </c>
       <c r="AC93" s="5"/>
       <c r="AD93" s="5"/>
       <c r="AE93" s="5"/>
@@ -8546,8 +8907,12 @@
       <c r="Z95" s="5">
         <v>-329</v>
       </c>
-      <c r="AA95" s="5"/>
-      <c r="AB95" s="5"/>
+      <c r="AA95" s="5">
+        <v>-257</v>
+      </c>
+      <c r="AB95" s="87">
+        <v>-1207</v>
+      </c>
       <c r="AC95" s="5"/>
       <c r="AD95" s="5"/>
       <c r="AE95" s="5"/>
@@ -8600,8 +8965,12 @@
       <c r="Z96" s="5">
         <v>908</v>
       </c>
-      <c r="AA96" s="5"/>
-      <c r="AB96" s="5"/>
+      <c r="AA96" s="5">
+        <v>120</v>
+      </c>
+      <c r="AB96" s="87">
+        <v>-31</v>
+      </c>
       <c r="AC96" s="5"/>
       <c r="AD96" s="5"/>
       <c r="AE96" s="5"/>
@@ -8654,8 +9023,12 @@
       <c r="Z97" s="5">
         <v>-260</v>
       </c>
-      <c r="AA97" s="5"/>
-      <c r="AB97" s="5"/>
+      <c r="AA97" s="5">
+        <v>-224</v>
+      </c>
+      <c r="AB97" s="5">
+        <v>519</v>
+      </c>
       <c r="AC97" s="5"/>
       <c r="AD97" s="5"/>
       <c r="AE97" s="5"/>
@@ -8708,8 +9081,12 @@
       <c r="Z98" s="5">
         <v>397</v>
       </c>
-      <c r="AA98" s="5"/>
-      <c r="AB98" s="5"/>
+      <c r="AA98" s="5">
+        <v>-426</v>
+      </c>
+      <c r="AB98" s="5">
+        <v>-959</v>
+      </c>
       <c r="AC98" s="5"/>
       <c r="AD98" s="5"/>
       <c r="AE98" s="5"/>
@@ -8723,31 +9100,31 @@
         <v>92</v>
       </c>
       <c r="C99" s="5">
-        <f t="shared" ref="C99:I99" si="87">SUM(C95:C98)</f>
+        <f t="shared" ref="C99:I99" si="89">SUM(C95:C98)</f>
         <v>0</v>
       </c>
       <c r="D99" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="E99" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="F99" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="H99" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>0</v>
       </c>
       <c r="I99" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="89"/>
         <v>-285</v>
       </c>
       <c r="J99" s="5">
@@ -8764,35 +9141,41 @@
       <c r="R99" s="5"/>
       <c r="S99" s="5"/>
       <c r="T99" s="5">
-        <f t="shared" ref="T99:Z99" si="88">SUM(T95:T98)</f>
+        <f t="shared" ref="T99:AB99" si="90">SUM(T95:T98)</f>
         <v>1482</v>
       </c>
       <c r="U99" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>562</v>
       </c>
       <c r="V99" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-1245</v>
       </c>
       <c r="W99" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>45</v>
       </c>
       <c r="X99" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-1660</v>
       </c>
       <c r="Y99" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>-513</v>
       </c>
       <c r="Z99" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="90"/>
         <v>716</v>
       </c>
-      <c r="AA99" s="5"/>
-      <c r="AB99" s="5"/>
+      <c r="AA99" s="5">
+        <f t="shared" si="90"/>
+        <v>-787</v>
+      </c>
+      <c r="AB99" s="5">
+        <f t="shared" si="90"/>
+        <v>-1678</v>
+      </c>
       <c r="AC99" s="5"/>
       <c r="AD99" s="5"/>
       <c r="AE99" s="5"/>
@@ -8806,31 +9189,31 @@
         <v>91</v>
       </c>
       <c r="C100" s="8">
-        <f t="shared" ref="C100:I100" si="89">C88+SUM(C89:C93)+C99</f>
+        <f t="shared" ref="C100:I100" si="91">C88+SUM(C89:C93)+C99</f>
         <v>1468</v>
       </c>
       <c r="D100" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>1331</v>
       </c>
       <c r="E100" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>1240</v>
       </c>
       <c r="F100" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>2007</v>
       </c>
       <c r="G100" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>1450</v>
       </c>
       <c r="H100" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>1578</v>
       </c>
       <c r="I100" s="8">
-        <f t="shared" si="89"/>
+        <f t="shared" si="91"/>
         <v>1783</v>
       </c>
       <c r="J100" s="8">
@@ -8847,35 +9230,41 @@
       <c r="R100" s="5"/>
       <c r="S100" s="5"/>
       <c r="T100" s="8">
-        <f t="shared" ref="T100:Z100" si="90">T88+SUM(T89:T93)+T99</f>
+        <f t="shared" ref="T100:AB100" si="92">T88+SUM(T89:T93)+T99</f>
         <v>4955</v>
       </c>
       <c r="U100" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>5903</v>
       </c>
       <c r="V100" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>2485</v>
       </c>
       <c r="W100" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>6657</v>
       </c>
       <c r="X100" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>5188</v>
       </c>
       <c r="Y100" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>5841</v>
       </c>
       <c r="Z100" s="8">
-        <f t="shared" si="90"/>
+        <f t="shared" si="92"/>
         <v>7429</v>
       </c>
-      <c r="AA100" s="5"/>
-      <c r="AB100" s="5"/>
+      <c r="AA100" s="8">
+        <f t="shared" si="92"/>
+        <v>3698</v>
+      </c>
+      <c r="AB100" s="8">
+        <f t="shared" si="92"/>
+        <v>2868</v>
+      </c>
       <c r="AC100" s="5"/>
       <c r="AD100" s="5"/>
       <c r="AE100" s="5"/>
@@ -8926,8 +9315,12 @@
       <c r="Z101" s="5">
         <v>-4767</v>
       </c>
-      <c r="AA101" s="5"/>
-      <c r="AB101" s="5"/>
+      <c r="AA101" s="5">
+        <v>-3234</v>
+      </c>
+      <c r="AB101" s="5">
+        <v>-1316</v>
+      </c>
       <c r="AC101" s="5"/>
       <c r="AD101" s="5"/>
       <c r="AE101" s="5"/>
@@ -8978,8 +9371,12 @@
       <c r="Z102" s="5">
         <v>2269</v>
       </c>
-      <c r="AA102" s="5"/>
-      <c r="AB102" s="5"/>
+      <c r="AA102" s="5">
+        <v>319</v>
+      </c>
+      <c r="AB102" s="5">
+        <v>556</v>
+      </c>
       <c r="AC102" s="5"/>
       <c r="AD102" s="5"/>
       <c r="AE102" s="5"/>
@@ -9030,8 +9427,12 @@
       <c r="Z103" s="5">
         <v>4219</v>
       </c>
-      <c r="AA103" s="5"/>
-      <c r="AB103" s="5"/>
+      <c r="AA103" s="5">
+        <v>3062</v>
+      </c>
+      <c r="AB103" s="5">
+        <v>1021</v>
+      </c>
       <c r="AC103" s="5"/>
       <c r="AD103" s="5"/>
       <c r="AE103" s="5"/>
@@ -9082,8 +9483,12 @@
       <c r="Z104" s="5">
         <v>-812</v>
       </c>
-      <c r="AA104" s="5"/>
-      <c r="AB104" s="5"/>
+      <c r="AA104" s="5">
+        <v>-430</v>
+      </c>
+      <c r="AB104" s="5">
+        <v>-684</v>
+      </c>
       <c r="AC104" s="5"/>
       <c r="AD104" s="5"/>
       <c r="AE104" s="5"/>
@@ -9134,8 +9539,12 @@
       <c r="Z105" s="5">
         <v>-15</v>
       </c>
-      <c r="AA105" s="5"/>
-      <c r="AB105" s="5"/>
+      <c r="AA105" s="5">
+        <v>8</v>
+      </c>
+      <c r="AB105" s="5">
+        <v>-65</v>
+      </c>
       <c r="AC105" s="5"/>
       <c r="AD105" s="5"/>
       <c r="AE105" s="5"/>
@@ -9149,31 +9558,31 @@
         <v>106</v>
       </c>
       <c r="C106" s="8">
-        <f t="shared" ref="C106:I106" si="91">SUM(C101:C105)</f>
+        <f t="shared" ref="C106:I106" si="93">SUM(C101:C105)</f>
         <v>0</v>
       </c>
       <c r="D106" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="E106" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="F106" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="G106" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="H106" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="I106" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="93"/>
         <v>0</v>
       </c>
       <c r="J106" s="8">
@@ -9190,35 +9599,41 @@
       <c r="R106" s="5"/>
       <c r="S106" s="5"/>
       <c r="T106" s="8">
-        <f t="shared" ref="T106:Z106" si="92">SUM(T101:T105)</f>
+        <f t="shared" ref="T106:AB106" si="94">SUM(T101:T105)</f>
         <v>276</v>
       </c>
       <c r="U106" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>-264</v>
       </c>
       <c r="V106" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>-1028</v>
       </c>
       <c r="W106" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>-3800</v>
       </c>
       <c r="X106" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>-1524</v>
       </c>
       <c r="Y106" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>564</v>
       </c>
       <c r="Z106" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="94"/>
         <v>894</v>
       </c>
-      <c r="AA106" s="5"/>
-      <c r="AB106" s="5"/>
+      <c r="AA106" s="8">
+        <f t="shared" si="94"/>
+        <v>-275</v>
+      </c>
+      <c r="AB106" s="8">
+        <f t="shared" si="94"/>
+        <v>-488</v>
+      </c>
       <c r="AC106" s="5"/>
       <c r="AD106" s="5"/>
       <c r="AE106" s="5"/>
@@ -9269,8 +9684,12 @@
       <c r="Z107" s="5">
         <v>0</v>
       </c>
-      <c r="AA107" s="5"/>
-      <c r="AB107" s="5"/>
+      <c r="AA107" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB107" s="5">
+        <v>0</v>
+      </c>
       <c r="AC107" s="5"/>
       <c r="AD107" s="5"/>
       <c r="AE107" s="5"/>
@@ -9321,8 +9740,12 @@
       <c r="Z108" s="5">
         <v>0</v>
       </c>
-      <c r="AA108" s="5"/>
-      <c r="AB108" s="5"/>
+      <c r="AA108" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="5">
+        <v>0</v>
+      </c>
       <c r="AC108" s="5"/>
       <c r="AD108" s="5"/>
       <c r="AE108" s="5"/>
@@ -9373,8 +9796,12 @@
       <c r="Z109" s="5">
         <v>0</v>
       </c>
-      <c r="AA109" s="5"/>
-      <c r="AB109" s="5"/>
+      <c r="AA109" s="87">
+        <v>-1000</v>
+      </c>
+      <c r="AB109" s="5">
+        <v>0</v>
+      </c>
       <c r="AC109" s="5"/>
       <c r="AD109" s="5"/>
       <c r="AE109" s="5"/>
@@ -9425,8 +9852,12 @@
       <c r="Z110" s="5">
         <v>667</v>
       </c>
-      <c r="AA110" s="5"/>
-      <c r="AB110" s="5"/>
+      <c r="AA110" s="5">
+        <v>551</v>
+      </c>
+      <c r="AB110" s="5">
+        <v>354</v>
+      </c>
       <c r="AC110" s="5"/>
       <c r="AD110" s="5"/>
       <c r="AE110" s="5"/>
@@ -9477,8 +9908,12 @@
       <c r="Z111" s="5">
         <v>-4250</v>
       </c>
-      <c r="AA111" s="5"/>
-      <c r="AB111" s="5"/>
+      <c r="AA111" s="5">
+        <v>-2985</v>
+      </c>
+      <c r="AB111" s="5">
+        <v>-146</v>
+      </c>
       <c r="AC111" s="5"/>
       <c r="AD111" s="5"/>
       <c r="AE111" s="5"/>
@@ -9529,8 +9964,12 @@
       <c r="Z112" s="5">
         <v>-2169</v>
       </c>
-      <c r="AA112" s="5"/>
-      <c r="AB112" s="5"/>
+      <c r="AA112" s="5">
+        <v>-2300</v>
+      </c>
+      <c r="AB112" s="5">
+        <v>-2407</v>
+      </c>
       <c r="AC112" s="5"/>
       <c r="AD112" s="5"/>
       <c r="AE112" s="5"/>
@@ -9581,8 +10020,12 @@
       <c r="Z113" s="5">
         <v>-136</v>
       </c>
-      <c r="AA113" s="5"/>
-      <c r="AB113" s="5"/>
+      <c r="AA113" s="5">
+        <v>-86</v>
+      </c>
+      <c r="AB113" s="5">
+        <v>-93</v>
+      </c>
       <c r="AC113" s="5"/>
       <c r="AD113" s="5"/>
       <c r="AE113" s="5"/>
@@ -9600,31 +10043,31 @@
         <v>0</v>
       </c>
       <c r="D114" s="8">
-        <f t="shared" ref="D114:J114" si="93">SUM(D108:D113)</f>
+        <f t="shared" ref="D114:J114" si="95">SUM(D108:D113)</f>
         <v>0</v>
       </c>
       <c r="E114" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="F114" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="G114" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="H114" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="I114" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="J114" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="95"/>
         <v>0</v>
       </c>
       <c r="K114" s="8"/>
@@ -9637,23 +10080,23 @@
       <c r="R114" s="5"/>
       <c r="S114" s="5"/>
       <c r="T114" s="8">
-        <f t="shared" ref="T114:X114" si="94">SUM(T107:T113)</f>
+        <f t="shared" ref="T114:X114" si="96">SUM(T107:T113)</f>
         <v>-4835</v>
       </c>
       <c r="U114" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>-5293</v>
       </c>
       <c r="V114" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>2491</v>
       </c>
       <c r="W114" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>-1459</v>
       </c>
       <c r="X114" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="96"/>
         <v>-4836</v>
       </c>
       <c r="Y114" s="8">
@@ -9661,11 +10104,17 @@
         <v>-7447</v>
       </c>
       <c r="Z114" s="8">
-        <f t="shared" ref="Z114" si="95">SUM(Z108:Z113)</f>
+        <f t="shared" ref="Z114:AB114" si="97">SUM(Z108:Z113)</f>
         <v>-5888</v>
       </c>
-      <c r="AA114" s="5"/>
-      <c r="AB114" s="5"/>
+      <c r="AA114" s="8">
+        <f t="shared" si="97"/>
+        <v>-5820</v>
+      </c>
+      <c r="AB114" s="8">
+        <f t="shared" si="97"/>
+        <v>-2292</v>
+      </c>
       <c r="AC114" s="5"/>
       <c r="AD114" s="5"/>
       <c r="AE114" s="5"/>
@@ -9716,8 +10165,12 @@
       <c r="Z115" s="5">
         <v>-16</v>
       </c>
-      <c r="AA115" s="5"/>
-      <c r="AB115" s="5"/>
+      <c r="AA115" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB115" s="5">
+        <v>11</v>
+      </c>
       <c r="AC115" s="5"/>
       <c r="AD115" s="5"/>
       <c r="AE115" s="5"/>
@@ -9735,31 +10188,31 @@
         <v>1468</v>
       </c>
       <c r="D116" s="8">
-        <f t="shared" ref="D116:J116" si="96">D100+D106+D114+D115</f>
+        <f t="shared" ref="D116:J116" si="98">D100+D106+D114+D115</f>
         <v>1331</v>
       </c>
       <c r="E116" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1240</v>
       </c>
       <c r="F116" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>2007</v>
       </c>
       <c r="G116" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1450</v>
       </c>
       <c r="H116" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1578</v>
       </c>
       <c r="I116" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1783</v>
       </c>
       <c r="J116" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="98"/>
         <v>1500</v>
       </c>
       <c r="K116" s="8"/>
@@ -9772,35 +10225,41 @@
       <c r="R116" s="5"/>
       <c r="S116" s="5"/>
       <c r="T116" s="8">
-        <f t="shared" ref="T116" si="97">T100+T106+T114+T115</f>
+        <f t="shared" ref="T116" si="99">T100+T106+T114+T115</f>
         <v>441</v>
       </c>
       <c r="U116" s="8">
-        <f t="shared" ref="U116" si="98">U100+U106+U114+U115</f>
+        <f t="shared" ref="U116" si="100">U100+U106+U114+U115</f>
         <v>217</v>
       </c>
       <c r="V116" s="8">
-        <f t="shared" ref="V116" si="99">V100+V106+V114+V115</f>
+        <f t="shared" ref="V116" si="101">V100+V106+V114+V115</f>
         <v>3882</v>
       </c>
       <c r="W116" s="8">
-        <f t="shared" ref="W116" si="100">W100+W106+W114+W115</f>
+        <f t="shared" ref="W116" si="102">W100+W106+W114+W115</f>
         <v>1541</v>
       </c>
       <c r="X116" s="8">
-        <f t="shared" ref="X116" si="101">X100+X106+X114+X115</f>
+        <f t="shared" ref="X116" si="103">X100+X106+X114+X115</f>
         <v>-1315</v>
       </c>
       <c r="Y116" s="8">
-        <f t="shared" ref="Y116" si="102">Y100+Y106+Y114+Y115</f>
+        <f t="shared" ref="Y116" si="104">Y100+Y106+Y114+Y115</f>
         <v>-1133</v>
       </c>
       <c r="Z116" s="8">
-        <f t="shared" ref="Z116" si="103">Z100+Z106+Z114+Z115</f>
+        <f t="shared" ref="Z116:AB116" si="105">Z100+Z106+Z114+Z115</f>
         <v>2419</v>
       </c>
-      <c r="AA116" s="5"/>
-      <c r="AB116" s="5"/>
+      <c r="AA116" s="8">
+        <f t="shared" si="105"/>
+        <v>-2396</v>
+      </c>
+      <c r="AB116" s="8">
+        <f t="shared" si="105"/>
+        <v>99</v>
+      </c>
       <c r="AC116" s="5"/>
       <c r="AD116" s="5"/>
       <c r="AE116" s="5"/>
@@ -9892,8 +10351,14 @@
         <f>Y119</f>
         <v>7441</v>
       </c>
-      <c r="AA118" s="5"/>
-      <c r="AB118" s="5"/>
+      <c r="AA118" s="87">
+        <f>+Z119</f>
+        <v>9860</v>
+      </c>
+      <c r="AB118" s="5">
+        <f>+AA119</f>
+        <v>7464</v>
+      </c>
       <c r="AC118" s="5"/>
       <c r="AD118" s="5"/>
       <c r="AE118" s="5"/>
@@ -9951,8 +10416,14 @@
         <f>Z118+Z116</f>
         <v>9860</v>
       </c>
-      <c r="AA119" s="5"/>
-      <c r="AB119" s="5"/>
+      <c r="AA119" s="5">
+        <f>+AA116+AA118</f>
+        <v>7464</v>
+      </c>
+      <c r="AB119" s="5">
+        <f>+AB116+AB118</f>
+        <v>7563</v>
+      </c>
       <c r="AC119" s="5"/>
       <c r="AD119" s="5"/>
       <c r="AE119" s="5"/>
@@ -11432,7 +11903,7 @@
       </c>
       <c r="I32" s="5">
         <f>Main!I5</f>
-        <v>71078.804999999993</v>
+        <v>65348.117867149995</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.2">
@@ -11498,7 +11969,7 @@
       </c>
       <c r="I34" s="5">
         <f>I32+I33</f>
-        <v>70971.804999999993</v>
+        <v>65241.117867149995</v>
       </c>
     </row>
     <row r="35" spans="2:13" x14ac:dyDescent="0.2">
@@ -11543,15 +12014,15 @@
       </c>
       <c r="I36" s="30">
         <f>I32/Model!Z27</f>
-        <v>12.469965789473683</v>
+        <v>11.46458208195614</v>
       </c>
       <c r="L36" s="30">
         <f>AVERAGE(C36:I36)</f>
-        <v>37.663704329021492</v>
+        <v>37.520078085090418</v>
       </c>
       <c r="M36" s="30">
         <f>AVERAGE(D36:J36)</f>
-        <v>33.534825918872421</v>
+        <v>33.367261967619491</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.2">
@@ -11583,15 +12054,15 @@
       </c>
       <c r="I37" s="30">
         <f>I36/((Model!Z27/Model!Y27-1)*100)</f>
-        <v>1.0035353421052633</v>
+        <v>0.9226258913574229</v>
       </c>
       <c r="L37" s="30">
         <f t="shared" ref="L37:M41" si="11">AVERAGE(C37:I37)</f>
-        <v>0.52785477850712292</v>
+        <v>0.51436987004914958</v>
       </c>
       <c r="M37" s="30">
         <f t="shared" si="11"/>
-        <v>0.52785477850712292</v>
+        <v>0.51436987004914958</v>
       </c>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.2">
@@ -11624,15 +12095,15 @@
       </c>
       <c r="I38" s="30">
         <f>Ratios!I32/Model!Z83</f>
-        <v>4.9257661122661114</v>
+        <v>4.5286290968225913</v>
       </c>
       <c r="L38" s="30">
         <f t="shared" si="11"/>
-        <v>12.807956364460727</v>
+        <v>12.751222505111652</v>
       </c>
       <c r="M38" s="30">
         <f t="shared" si="11"/>
-        <v>12.892563572966997</v>
+        <v>12.826374070393078</v>
       </c>
     </row>
     <row r="39" spans="2:13" x14ac:dyDescent="0.2">
@@ -11665,15 +12136,15 @@
       </c>
       <c r="I39" s="30">
         <f>I32/(Model!Z83-Model!Z55-Model!Z56)</f>
-        <v>5.1022040772378148</v>
+        <v>4.6908418539336729</v>
       </c>
       <c r="L39" s="30">
         <f t="shared" si="11"/>
-        <v>13.423508813549367</v>
+        <v>13.364742781648776</v>
       </c>
       <c r="M39" s="30">
         <f t="shared" si="11"/>
-        <v>13.514690502807355</v>
+        <v>13.446130132256664</v>
       </c>
     </row>
     <row r="40" spans="2:13" x14ac:dyDescent="0.2">
@@ -11706,15 +12177,15 @@
       </c>
       <c r="I40" s="30">
         <f>I32/Model!Z100</f>
-        <v>9.5677486875757154</v>
+        <v>8.7963545385852733</v>
       </c>
       <c r="L40" s="30">
         <f t="shared" si="11"/>
-        <v>29.853737370264522</v>
+        <v>29.743538206123027</v>
       </c>
       <c r="M40" s="30">
         <f t="shared" si="11"/>
-        <v>30.76980183043112</v>
+        <v>30.641236138932712</v>
       </c>
     </row>
     <row r="41" spans="2:13" x14ac:dyDescent="0.2">
@@ -11747,15 +12218,15 @@
       </c>
       <c r="I41" s="30">
         <f>I32/Model!Z16</f>
-        <v>1.3838792297807716</v>
+        <v>1.2723047752647871</v>
       </c>
       <c r="L41" s="30">
         <f t="shared" si="11"/>
-        <v>3.3783270766697293</v>
+        <v>3.3623878688817315</v>
       </c>
       <c r="M41" s="30">
         <f t="shared" si="11"/>
-        <v>3.3887230724049111</v>
+        <v>3.3701273299855803</v>
       </c>
     </row>
     <row r="42" spans="2:13" x14ac:dyDescent="0.2">
@@ -11793,15 +12264,15 @@
       </c>
       <c r="I43" s="30">
         <f>I34/Model!Z16</f>
-        <v>1.3817959775709667</v>
+        <v>1.2702215230549823</v>
       </c>
       <c r="L43" s="30">
         <f t="shared" ref="L43:M46" si="12">AVERAGE(C43:I43)</f>
-        <v>3.379393257920138</v>
+        <v>3.3634540501321402</v>
       </c>
       <c r="M43" s="30">
         <f t="shared" si="12"/>
-        <v>3.3965380049213181</v>
+        <v>3.3779422625019873</v>
       </c>
     </row>
     <row r="44" spans="2:13" x14ac:dyDescent="0.2">
@@ -11834,15 +12305,15 @@
       </c>
       <c r="I44" s="30">
         <f>I34/Model!Z22</f>
-        <v>11.245730470606876</v>
+        <v>10.337683071961653</v>
       </c>
       <c r="L44" s="30">
         <f t="shared" si="12"/>
-        <v>28.299496661152855</v>
+        <v>28.16977560420354</v>
       </c>
       <c r="M44" s="30">
         <f t="shared" si="12"/>
-        <v>28.544550669023749</v>
+        <v>28.393209435916216</v>
       </c>
     </row>
     <row r="45" spans="2:13" x14ac:dyDescent="0.2">
@@ -11875,15 +12346,15 @@
       </c>
       <c r="I45" s="30">
         <f>Ratios!I34/(Model!Z22+Model!Y89+Model!Y92)</f>
-        <v>9.8984386331938623</v>
+        <v>9.0991796188493712</v>
       </c>
       <c r="L45" s="30">
         <f t="shared" si="12"/>
-        <v>23.82133753468408</v>
+        <v>23.707157675492006</v>
       </c>
       <c r="M45" s="30">
         <f t="shared" si="12"/>
-        <v>23.983178510752566</v>
+        <v>23.849968675028482</v>
       </c>
     </row>
     <row r="46" spans="2:13" x14ac:dyDescent="0.2">
@@ -11916,15 +12387,15 @@
       </c>
       <c r="I46" s="30">
         <f>I34/(Model!Z22*(1-Model!Z42)+Model!Z89+Model!Z92+Model!Y104+Model!Y98)</f>
-        <v>13.159961691152063</v>
+        <v>12.097347838618877</v>
       </c>
       <c r="L46" s="30">
         <f t="shared" si="12"/>
-        <v>28.95381718861475</v>
+        <v>28.802015209681436</v>
       </c>
       <c r="M46" s="30">
         <f t="shared" si="12"/>
-        <v>26.579673512163527</v>
+        <v>26.402571203407998</v>
       </c>
     </row>
   </sheetData>
@@ -12012,7 +12483,7 @@
       </c>
       <c r="J3" s="34">
         <f>Main!I3</f>
-        <v>48.01</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.2">
@@ -12027,7 +12498,7 @@
       </c>
       <c r="J4" s="36">
         <f ca="1">V60</f>
-        <v>69.159308361532567</v>
+        <v>69.732016495904531</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.2">
@@ -12042,7 +12513,7 @@
       </c>
       <c r="J5" s="38">
         <f ca="1">J4/J3-1</f>
-        <v>0.44051881611190513</v>
+        <v>0.58301967073563077</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.2">
@@ -13613,7 +14084,7 @@
       <c r="Q56" s="11"/>
       <c r="V56" s="11">
         <f>Main!I6</f>
-        <v>8057</v>
+        <v>9027</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.2">
@@ -13641,7 +14112,7 @@
       <c r="U57" s="64"/>
       <c r="V57" s="64">
         <f>Main!I7</f>
-        <v>8029</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.2">
@@ -13654,7 +14125,7 @@
       <c r="Q58" s="11"/>
       <c r="V58" s="11">
         <f ca="1">V55+V56-V57</f>
-        <v>102390.35602924897</v>
+        <v>103447.35602924897</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.2">
@@ -13682,7 +14153,7 @@
       <c r="U59" s="64"/>
       <c r="V59" s="64">
         <f>Main!I4</f>
-        <v>1480.5</v>
+        <v>1483.498703</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.2">
@@ -13691,7 +14162,7 @@
       </c>
       <c r="V60" s="30">
         <f ca="1">V58/V59</f>
-        <v>69.159308361532567</v>
+        <v>69.732016495904531</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.2">
@@ -13724,19 +14195,19 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="66"/>
-      <c r="C66" s="80" t="s">
+      <c r="C66" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="D66" s="80"/>
-      <c r="E66" s="80"/>
-      <c r="F66" s="80"/>
-      <c r="G66" s="80"/>
-      <c r="H66" s="80"/>
-      <c r="I66" s="80"/>
-      <c r="J66" s="81"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="81"/>
+      <c r="F66" s="81"/>
+      <c r="G66" s="81"/>
+      <c r="H66" s="81"/>
+      <c r="I66" s="81"/>
+      <c r="J66" s="82"/>
     </row>
     <row r="67" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="82" t="s">
+      <c r="B67" s="83" t="s">
         <v>187</v>
       </c>
       <c r="C67" s="67"/>
@@ -13749,7 +14220,7 @@
       <c r="J67" s="68"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B68" s="82"/>
+      <c r="B68" s="83"/>
       <c r="C68" s="69"/>
       <c r="D68" s="70"/>
       <c r="E68" s="70"/>
@@ -13760,7 +14231,7 @@
       <c r="J68" s="70"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="82"/>
+      <c r="B69" s="83"/>
       <c r="C69" s="69"/>
       <c r="D69" s="70"/>
       <c r="E69" s="70"/>
@@ -13771,7 +14242,7 @@
       <c r="J69" s="70"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B70" s="82"/>
+      <c r="B70" s="83"/>
       <c r="C70" s="69"/>
       <c r="D70" s="70"/>
       <c r="E70" s="70"/>
@@ -13782,7 +14253,7 @@
       <c r="J70" s="70"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B71" s="82"/>
+      <c r="B71" s="83"/>
       <c r="C71" s="69"/>
       <c r="D71" s="70"/>
       <c r="E71" s="70"/>
@@ -13793,7 +14264,7 @@
       <c r="J71" s="70"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B72" s="82"/>
+      <c r="B72" s="83"/>
       <c r="C72" s="69"/>
       <c r="D72" s="70"/>
       <c r="E72" s="70"/>
@@ -13804,7 +14275,7 @@
       <c r="J72" s="70"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B73" s="82"/>
+      <c r="B73" s="83"/>
       <c r="C73" s="69"/>
       <c r="D73" s="70"/>
       <c r="E73" s="70"/>
@@ -13815,7 +14286,7 @@
       <c r="J73" s="70"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B74" s="83"/>
+      <c r="B74" s="84"/>
       <c r="C74" s="69"/>
       <c r="D74" s="70"/>
       <c r="E74" s="70"/>
@@ -14100,7 +14571,7 @@
       </c>
       <c r="F35" s="76">
         <f>+Main!I7</f>
-        <v>8029</v>
+        <v>7942</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -14109,7 +14580,7 @@
       </c>
       <c r="F36" s="76">
         <f>+Main!I5</f>
-        <v>71078.804999999993</v>
+        <v>65348.117867149995</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -14118,7 +14589,7 @@
       </c>
       <c r="F37" s="76">
         <f>F35+F36</f>
-        <v>79107.804999999993</v>
+        <v>73290.117867149995</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.2">
@@ -14141,23 +14612,23 @@
       <c r="E41" s="20"/>
       <c r="F41" s="74">
         <f>(F32*(F35/F37)*(1-F39))+((F36/F37)*F22)</f>
-        <v>8.1373477775778413E-2</v>
+        <v>8.0970289291025482E-2</v>
       </c>
       <c r="H41" s="72" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="84" t="s">
+      <c r="B48" s="85" t="s">
         <v>275</v>
       </c>
-      <c r="C48" s="84"/>
-      <c r="D48" s="84"/>
-      <c r="H48" s="84" t="s">
+      <c r="C48" s="85"/>
+      <c r="D48" s="85"/>
+      <c r="H48" s="85" t="s">
         <v>276</v>
       </c>
-      <c r="I48" s="84"/>
-      <c r="J48" s="84"/>
+      <c r="I48" s="85"/>
+      <c r="J48" s="85"/>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">

--- a/NKE.xlsx
+++ b/NKE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5317A824-7CA5-44EA-870A-555A9F93E829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8940F39D-2F1C-4DA5-BE48-893DB47F2961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{B022B215-4C4C-4E36-8893-AFDEA07171F9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{B022B215-4C4C-4E36-8893-AFDEA07171F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1384,6 +1384,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1399,8 +1401,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="172" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2049,7 +2049,7 @@
       <c r="F10" s="24" t="s">
         <v>231</v>
       </c>
-      <c r="H10" s="86" t="s">
+      <c r="H10" s="81" t="s">
         <v>157</v>
       </c>
       <c r="I10" s="30">
@@ -2765,7 +2765,7 @@
         <v>13775</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" ref="AA10:AB26" si="6">+SUM(K10:N10)</f>
+        <f t="shared" ref="AA10:AA26" si="6">+SUM(K10:N10)</f>
         <v>12965</v>
       </c>
       <c r="AB10" s="5">
@@ -3028,39 +3028,39 @@
       </c>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
-        <f>+SUM(T9:T12)</f>
+        <f t="shared" ref="T13:AB13" si="8">+SUM(T9:T12)</f>
         <v>34485</v>
       </c>
       <c r="U13" s="5">
-        <f>+SUM(U9:U12)</f>
+        <f t="shared" si="8"/>
         <v>37218</v>
       </c>
       <c r="V13" s="5">
-        <f>+SUM(V9:V12)</f>
+        <f t="shared" si="8"/>
         <v>35568</v>
       </c>
       <c r="W13" s="5">
-        <f>+SUM(W9:W12)</f>
+        <f t="shared" si="8"/>
         <v>42293</v>
       </c>
       <c r="X13" s="5">
-        <f>+SUM(X9:X12)</f>
+        <f t="shared" si="8"/>
         <v>44436</v>
       </c>
       <c r="Y13" s="5">
-        <f>+SUM(Y9:Y12)</f>
+        <f t="shared" si="8"/>
         <v>48763</v>
       </c>
       <c r="Z13" s="5">
-        <f>+SUM(Z9:Z12)</f>
+        <f t="shared" si="8"/>
         <v>49322</v>
       </c>
       <c r="AA13" s="5">
-        <f>+SUM(AA9:AA12)</f>
+        <f t="shared" si="8"/>
         <v>44714</v>
       </c>
       <c r="AB13" s="5">
-        <f>+SUM(AB9:AB12)</f>
+        <f t="shared" si="8"/>
         <v>45222</v>
       </c>
       <c r="AC13" s="5"/>
@@ -3084,7 +3084,7 @@
         <v>612</v>
       </c>
       <c r="F14" s="5">
-        <f t="shared" ref="F14:F15" si="8">X14-SUM(C14:E14)</f>
+        <f t="shared" ref="F14:F15" si="9">X14-SUM(C14:E14)</f>
         <v>505</v>
       </c>
       <c r="G14" s="5">
@@ -3175,7 +3175,7 @@
         <v>12</v>
       </c>
       <c r="F15" s="5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>-85</v>
       </c>
       <c r="G15" s="5">
@@ -3432,92 +3432,92 @@
         <v>26</v>
       </c>
       <c r="C18" s="5">
-        <f t="shared" ref="C18:G18" si="9">C16-C17</f>
+        <f t="shared" ref="C18:G18" si="10">C16-C17</f>
         <v>5615</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5711</v>
       </c>
       <c r="E18" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5371</v>
       </c>
       <c r="F18" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4782</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5720</v>
       </c>
       <c r="H18" s="5">
-        <f t="shared" ref="H18:R18" si="10">H16-H17</f>
+        <f t="shared" ref="H18:R18" si="11">H16-H17</f>
         <v>5971</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5562</v>
       </c>
       <c r="J18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5634</v>
       </c>
       <c r="K18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5257</v>
       </c>
       <c r="L18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5389</v>
       </c>
       <c r="M18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4675</v>
       </c>
       <c r="N18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4469</v>
       </c>
       <c r="O18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4943</v>
       </c>
       <c r="P18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5045</v>
       </c>
       <c r="Q18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>4530</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5393</v>
       </c>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
-        <f t="shared" ref="T18:Y18" si="11">T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="12">T16-T17</f>
         <v>15956</v>
       </c>
       <c r="U18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>17474</v>
       </c>
       <c r="V18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>16241</v>
       </c>
       <c r="W18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19962</v>
       </c>
       <c r="X18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>21479</v>
       </c>
       <c r="Y18" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>22292</v>
       </c>
       <c r="Z18" s="5">
@@ -3721,23 +3721,23 @@
         <v>232</v>
       </c>
       <c r="C21" s="5">
-        <f t="shared" ref="C21:G21" si="12">C19+C20</f>
+        <f t="shared" ref="C21:G21" si="13">C19+C20</f>
         <v>3920</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4124</v>
       </c>
       <c r="E21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3959</v>
       </c>
       <c r="F21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2801</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4116</v>
       </c>
       <c r="H21" s="5">
@@ -3749,52 +3749,52 @@
         <v>4226</v>
       </c>
       <c r="J21" s="5">
-        <f t="shared" ref="J21:R21" si="13">J19+J20</f>
+        <f t="shared" ref="J21:R21" si="14">J19+J20</f>
         <v>4088</v>
       </c>
       <c r="K21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4048</v>
       </c>
       <c r="L21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4005</v>
       </c>
       <c r="M21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3887</v>
       </c>
       <c r="N21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4148</v>
       </c>
       <c r="O21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4016</v>
       </c>
       <c r="P21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4039</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3977</v>
       </c>
       <c r="R21" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4082</v>
       </c>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
-        <f t="shared" ref="T21" si="14">T19+T20</f>
+        <f t="shared" ref="T21" si="15">T19+T20</f>
         <v>11511</v>
       </c>
       <c r="U21" s="5">
-        <f t="shared" ref="U21" si="15">U19+U20</f>
+        <f t="shared" ref="U21" si="16">U19+U20</f>
         <v>12702</v>
       </c>
       <c r="V21" s="5">
-        <f t="shared" ref="V21" si="16">V19+V20</f>
+        <f t="shared" ref="V21" si="17">V19+V20</f>
         <v>13126</v>
       </c>
       <c r="W21" s="5">
@@ -3802,11 +3802,11 @@
         <v>13025</v>
       </c>
       <c r="X21" s="5">
-        <f t="shared" ref="X21" si="17">X19+X20</f>
+        <f t="shared" ref="X21" si="18">X19+X20</f>
         <v>14804</v>
       </c>
       <c r="Y21" s="5">
-        <f t="shared" ref="Y21" si="18">Y19+Y20</f>
+        <f t="shared" ref="Y21" si="19">Y19+Y20</f>
         <v>16377</v>
       </c>
       <c r="Z21" s="5">
@@ -3832,80 +3832,80 @@
         <v>29</v>
       </c>
       <c r="C22" s="5">
-        <f t="shared" ref="C22:G22" si="19">C18-C21</f>
+        <f t="shared" ref="C22:G22" si="20">C18-C21</f>
         <v>1695</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1587</v>
       </c>
       <c r="E22" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1412</v>
       </c>
       <c r="F22" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1981</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1604</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" ref="H22:R22" si="20">H18-H21</f>
+        <f t="shared" ref="H22:R22" si="21">H18-H21</f>
         <v>1825</v>
       </c>
       <c r="I22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1336</v>
       </c>
       <c r="J22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1546</v>
       </c>
       <c r="K22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1209</v>
       </c>
       <c r="L22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1384</v>
       </c>
       <c r="M22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>788</v>
       </c>
       <c r="N22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>321</v>
       </c>
       <c r="O22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>927</v>
       </c>
       <c r="P22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1006</v>
       </c>
       <c r="Q22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>553</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1311</v>
       </c>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
-        <f t="shared" ref="T22:Y22" si="21">T18-T21</f>
+        <f t="shared" ref="T22:Y22" si="22">T18-T21</f>
         <v>4445</v>
       </c>
       <c r="U22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>4772</v>
       </c>
       <c r="V22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3115</v>
       </c>
       <c r="W22" s="5">
@@ -3917,7 +3917,7 @@
         <v>6675</v>
       </c>
       <c r="Y22" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>5915</v>
       </c>
       <c r="Z22" s="5">
@@ -4121,92 +4121,92 @@
         <v>31</v>
       </c>
       <c r="C25" s="5">
-        <f t="shared" ref="C25:G25" si="22">C22-C23-C24</f>
+        <f t="shared" ref="C25:G25" si="23">C22-C23-C24</f>
         <v>1828</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1650</v>
       </c>
       <c r="E25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1477</v>
       </c>
       <c r="F25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1696</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1648</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" ref="H25:R25" si="23">H22-H23-H24</f>
+        <f t="shared" ref="H25:R25" si="24">H22-H23-H24</f>
         <v>1922</v>
       </c>
       <c r="I25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1404</v>
       </c>
       <c r="J25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1726</v>
       </c>
       <c r="K25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1307</v>
       </c>
       <c r="L25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1416</v>
       </c>
       <c r="M25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>844</v>
       </c>
       <c r="N25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>318</v>
       </c>
       <c r="O25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>922</v>
       </c>
       <c r="P25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>999</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>650</v>
       </c>
       <c r="R25" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1329</v>
       </c>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
-        <f t="shared" ref="T25:Y25" si="24">T22-T23-T24</f>
+        <f t="shared" ref="T25:Y25" si="25">T22-T23-T24</f>
         <v>4325</v>
       </c>
       <c r="U25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4801</v>
       </c>
       <c r="V25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2887</v>
       </c>
       <c r="W25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6661</v>
       </c>
       <c r="X25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6651</v>
       </c>
       <c r="Y25" s="5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6201</v>
       </c>
       <c r="Z25" s="5">
@@ -4321,23 +4321,23 @@
         <v>33</v>
       </c>
       <c r="C27" s="5">
-        <f t="shared" ref="C27:G27" si="25">C25-C26</f>
+        <f t="shared" ref="C27:G27" si="26">C25-C26</f>
         <v>1468</v>
       </c>
       <c r="D27" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1331</v>
       </c>
       <c r="E27" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1240</v>
       </c>
       <c r="F27" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>2007</v>
       </c>
       <c r="G27" s="5">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1450</v>
       </c>
       <c r="H27" s="5">
@@ -4357,36 +4357,36 @@
         <v>1051</v>
       </c>
       <c r="L27" s="5">
-        <f t="shared" ref="L27:R27" si="26">L25-L26</f>
+        <f t="shared" ref="L27:R27" si="27">L25-L26</f>
         <v>1163</v>
       </c>
       <c r="M27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>794</v>
       </c>
       <c r="N27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>211</v>
       </c>
       <c r="O27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>727</v>
       </c>
       <c r="P27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>792</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>520</v>
       </c>
       <c r="R27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1069</v>
       </c>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
-        <f t="shared" ref="T27:Y27" si="27">T25-T26</f>
+        <f t="shared" ref="T27:Y27" si="28">T25-T26</f>
         <v>1933</v>
       </c>
       <c r="U27" s="5">
@@ -4394,19 +4394,19 @@
         <v>4029</v>
       </c>
       <c r="V27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2539</v>
       </c>
       <c r="W27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5727</v>
       </c>
       <c r="X27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6046</v>
       </c>
       <c r="Y27" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>5070</v>
       </c>
       <c r="Z27" s="5">
@@ -4465,67 +4465,67 @@
         <v>35</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:R29" si="28">C27/C30</f>
+        <f t="shared" ref="C29:R29" si="29">C27/C30</f>
         <v>0.92994376447237848</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.84315745947734044</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.78551108170691364</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.2713876943433675</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.95275008437176922</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1.0415002416821773</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.77646747051808662</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.99469496021220161</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.70174267209721575</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.7822168415388755</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.53717610445842634</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.14288616509785332</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.49234728430177438</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.53531598513011147</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.35123269165822357</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0.72103062188048028</v>
       </c>
       <c r="S29" s="5"/>
@@ -4623,27 +4623,27 @@
       </c>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
-        <f t="shared" ref="T30:Y30" si="29">T27/T29</f>
+        <f t="shared" ref="T30:Y30" si="30">T27/T29</f>
         <v>1624.3697478991598</v>
       </c>
       <c r="U30" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1580</v>
       </c>
       <c r="V30" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1557.6687116564419</v>
       </c>
       <c r="W30" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1573.3516483516482</v>
       </c>
       <c r="X30" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1578.5900783289817</v>
       </c>
       <c r="Y30" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1550.4587155963302</v>
       </c>
       <c r="Z30" s="5">
@@ -4705,51 +4705,51 @@
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10">
-        <f t="shared" ref="G32:G37" si="30">G9/C9-1</f>
+        <f t="shared" ref="G32:G37" si="31">G9/C9-1</f>
         <v>3.7835839290115914E-2</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:H37" si="31">H9/D9-1</f>
+        <f t="shared" ref="H32:H37" si="32">H9/D9-1</f>
         <v>1.2111947318908856E-2</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" ref="I32:I37" si="32">I9/E9-1</f>
+        <f t="shared" ref="I32:I37" si="33">I9/E9-1</f>
         <v>2.4090338770389019E-2</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" ref="J32:J37" si="33">J9/F9-1</f>
+        <f t="shared" ref="J32:J37" si="34">J9/F9-1</f>
         <v>0.80834248079034032</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" ref="K32:K37" si="34">K9/G9-1</f>
+        <f t="shared" ref="K32:K37" si="35">K9/G9-1</f>
         <v>-0.11388196176226106</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" ref="L32:L37" si="35">L9/H9-1</f>
+        <f t="shared" ref="L32:L37" si="36">L9/H9-1</f>
         <v>-0.11060764494016495</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" ref="M32:R37" si="36">M9/I9-1</f>
+        <f t="shared" ref="M32:R37" si="37">M9/I9-1</f>
         <v>-0.11688311688311692</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.12771640160252518</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-6.9686411149826322E-3</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5.2253429131288165E-4</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.0116537180909999E-2</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.1412665274878164E-2</v>
       </c>
       <c r="S32" s="10"/>
@@ -4792,51 +4792,51 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-1.3395457192778126E-2</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-5.2714812862414417E-3</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-2.6915113871635588E-2</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.1233941852603111</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.10507674144037782</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-9.5389507154213238E-3</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-2.9483282674772071E-2</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-9.6599458320794418E-2</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9.2678100263852148E-2</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.4943820224719211E-2</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-2.8186658315064728E-3</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4656895403064585E-2</v>
       </c>
       <c r="S33" s="10"/>
@@ -4878,87 +4878,87 @@
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
       <c r="G34" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.259259259259256E-2</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.1740196078431373</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.20843672456575679</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.76758409785932713</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.13559322033898313</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>0.13569937369519836</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-2.0533880903490731E-2</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.9031141868512069E-2</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4.4776119402984982E-2</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.1029411764705843E-2</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-1.8867924528301883E-2</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-2.821869488536155E-2</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" ref="T34:Z34" si="37">T9/T16</f>
+        <f t="shared" ref="T34:Z34" si="38">T9/T16</f>
         <v>0.61180866554935842</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.61921926528107984</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.62307836269817929</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.62914814315865109</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.62391350888460717</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.64695316008356596</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.65081188427241932</v>
       </c>
       <c r="AA34" s="10">
-        <f t="shared" ref="AA34:AB34" si="38">AA9/AA16</f>
+        <f t="shared" ref="AA34:AB34" si="39">AA9/AA16</f>
         <v>0.63724114103090113</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>0.63634208371050471</v>
       </c>
     </row>
@@ -4971,87 +4971,87 @@
       <c r="E35" s="10"/>
       <c r="F35" s="10"/>
       <c r="G35" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-7.1428571428571397E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-0.33333333333333337</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-0.25</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-0.81034482758620685</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>7.6923076923076872E-2</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>8.3333333333333259E-2</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.18181818181818177</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.3571428571428571</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.30769230769230771</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.41666666666666663</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.6666666666666665</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" ref="T35:Z35" si="39">T10/T16</f>
+        <f t="shared" ref="T35:Z35" si="40">T10/T16</f>
         <v>0.29488694123142017</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.29526804202776286</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.29283747292997886</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.28885446135883963</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.29045172339970027</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.27028135189487867</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.26819438495385695</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" ref="AA35:AB35" si="40">AA10/AA16</f>
+        <f t="shared" ref="AA35:AB35" si="41">AA10/AA16</f>
         <v>0.27996717700662938</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.28986163196689513</v>
       </c>
     </row>
@@ -5064,87 +5064,87 @@
       <c r="E36" s="10"/>
       <c r="F36" s="10"/>
       <c r="G36" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>2.5315405046480777E-2</v>
       </c>
       <c r="H36" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.1631562401760442E-2</v>
       </c>
       <c r="I36" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1.5468298487166354E-2</v>
       </c>
       <c r="J36" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.53823752848822481</v>
       </c>
       <c r="K36" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.10054237836962676</v>
       </c>
       <c r="L36" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-7.1628340584213746E-2</v>
       </c>
       <c r="M36" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-8.8550385001673892E-2</v>
       </c>
       <c r="N36" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.11408346365956046</v>
       </c>
       <c r="O36" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2.2590225902259009E-2</v>
       </c>
       <c r="P36" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.4560669456066933E-2</v>
       </c>
       <c r="Q36" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>1.120293847566578E-2</v>
       </c>
       <c r="R36" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-3.6235250394871521E-3</v>
       </c>
       <c r="T36" s="10">
-        <f t="shared" ref="T36:Z36" si="41">T11/T16</f>
+        <f t="shared" ref="T36:Z36" si="42">T11/T16</f>
         <v>3.8354809462318326E-2</v>
       </c>
       <c r="U36" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.589232303090728E-2</v>
       </c>
       <c r="V36" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.4221853861989678E-2</v>
       </c>
       <c r="W36" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.102968251829898E-2</v>
       </c>
       <c r="X36" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.4767715692571186E-2</v>
       </c>
       <c r="Y36" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>3.3719272897670696E-2</v>
       </c>
       <c r="Z36" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>4.039951715275885E-2</v>
       </c>
       <c r="AA36" s="10">
-        <f t="shared" ref="AA36:AB36" si="42">AA11/AA16</f>
+        <f t="shared" ref="AA36:AB36" si="43">AA11/AA16</f>
         <v>4.7312617417780561E-2</v>
       </c>
       <c r="AB36" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>4.73942842363895E-2</v>
       </c>
     </row>
@@ -5157,87 +5157,87 @@
       <c r="E37" s="10"/>
       <c r="F37" s="10"/>
       <c r="G37" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>-8.5536547433903598E-2</v>
       </c>
       <c r="H37" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-0.11433447098976113</v>
       </c>
       <c r="I37" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>-0.19117647058823528</v>
       </c>
       <c r="J37" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.9504950495049549E-2</v>
       </c>
       <c r="K37" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>-0.14795918367346939</v>
       </c>
       <c r="L37" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.17341040462427748</v>
       </c>
       <c r="M37" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.18181818181818177</v>
       </c>
       <c r="N37" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.25624999999999998</v>
       </c>
       <c r="O37" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.26946107784431139</v>
       </c>
       <c r="P37" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.30069930069930073</v>
       </c>
       <c r="Q37" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.3481481481481481</v>
       </c>
       <c r="R37" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>-0.31652661064425769</v>
       </c>
       <c r="T37" s="10">
-        <f t="shared" ref="T37:Z37" si="43">T14/T16</f>
+        <f t="shared" ref="T37:Z37" si="44">T14/T16</f>
         <v>5.1817457482759566E-2</v>
       </c>
       <c r="U37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>4.8725618017741647E-2</v>
       </c>
       <c r="V37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>4.9354329866588241E-2</v>
       </c>
       <c r="W37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>4.9508285059948809E-2</v>
       </c>
       <c r="X37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>5.0224791265253692E-2</v>
       </c>
       <c r="Y37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>4.7386609914676768E-2</v>
       </c>
       <c r="Z37" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>4.0535804680503093E-2</v>
       </c>
       <c r="AA37" s="10">
-        <f t="shared" ref="AA37:AB37" si="44">AA14/AA16</f>
+        <f t="shared" ref="AA37:AB37" si="45">AA14/AA16</f>
         <v>3.6537174199399683E-2</v>
       </c>
       <c r="AB37" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>2.5302814776498986E-2</v>
       </c>
     </row>
@@ -5262,47 +5262,47 @@
         <v>-2.8238828389034909E-2</v>
       </c>
       <c r="H38" s="13">
-        <f t="shared" ref="H38:R38" si="45">H16/D16-1</f>
+        <f t="shared" ref="H38:R38" si="46">H16/D16-1</f>
         <v>5.482538490424238E-3</v>
       </c>
       <c r="I38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>3.1476997578692156E-3</v>
       </c>
       <c r="J38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.51550853570569855</v>
       </c>
       <c r="K38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.10433572919081846</v>
       </c>
       <c r="L38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-7.7233343292500756E-2</v>
       </c>
       <c r="M38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-9.3330115053503859E-2</v>
       </c>
       <c r="N38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.11970490242741549</v>
       </c>
       <c r="O38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.1303822590387425E-2</v>
       </c>
       <c r="P38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>5.9090173223248499E-3</v>
       </c>
       <c r="Q38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>8.8739018546446502E-4</v>
       </c>
       <c r="R38" s="13">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-1.1264305668198582E-2</v>
       </c>
       <c r="S38" s="13"/>
@@ -5310,35 +5310,35 @@
         <v>43</v>
       </c>
       <c r="U38" s="13">
-        <f t="shared" ref="U38:AB38" si="46">U16/T16-1</f>
+        <f t="shared" ref="U38:AB38" si="47">U16/T16-1</f>
         <v>7.4731433909388079E-2</v>
       </c>
       <c r="V38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-4.3817266150267153E-2</v>
       </c>
       <c r="W38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>0.19076009945726269</v>
       </c>
       <c r="X38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>4.8767344739323759E-2</v>
       </c>
       <c r="Y38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>9.6488974523656568E-2</v>
       </c>
       <c r="Z38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>2.8310912392370824E-3</v>
       </c>
       <c r="AA38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-9.8380125384525563E-2</v>
       </c>
       <c r="AB38" s="13">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>1.9218726381480256E-3</v>
       </c>
     </row>
@@ -5347,104 +5347,104 @@
         <v>39</v>
       </c>
       <c r="C39" s="10">
-        <f t="shared" ref="C39:N39" si="47">C18/C16</f>
+        <f t="shared" ref="C39:N39" si="48">C18/C16</f>
         <v>0.44257901789233073</v>
       </c>
       <c r="D39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.42891475779196397</v>
       </c>
       <c r="E39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.43349475383373687</v>
       </c>
       <c r="F39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.57489781197403222</v>
       </c>
       <c r="G39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.44207434886776414</v>
       </c>
       <c r="H39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.44599641469973111</v>
       </c>
       <c r="I39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.44750181028240404</v>
       </c>
       <c r="J39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.44693003331746789</v>
       </c>
       <c r="K39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.45361981189058592</v>
       </c>
       <c r="L39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.43621499109600131</v>
       </c>
       <c r="M39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.41485491170467653</v>
       </c>
       <c r="N39" s="10">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.40272145624943678</v>
       </c>
       <c r="O39" s="10">
-        <f t="shared" ref="O39:P39" si="48">O18/O16</f>
+        <f t="shared" ref="O39:P39" si="49">O18/O16</f>
         <v>0.42175767918088736</v>
       </c>
       <c r="P39" s="10">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.40597086988009978</v>
       </c>
       <c r="Q39" s="10">
-        <f t="shared" ref="Q39:R39" si="49">Q18/Q16</f>
+        <f t="shared" ref="Q39:R39" si="50">Q18/Q16</f>
         <v>0.40163135029701214</v>
       </c>
       <c r="R39" s="10">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.49152387896463728</v>
       </c>
       <c r="S39" s="10"/>
       <c r="T39" s="10">
-        <f t="shared" ref="T39:AA39" si="50">T18/T16</f>
+        <f t="shared" ref="T39:AA39" si="51">T18/T16</f>
         <v>0.43838777921257244</v>
       </c>
       <c r="U39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44671114860546568</v>
       </c>
       <c r="V39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.43421650669732376</v>
       </c>
       <c r="W39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44820153576721</v>
       </c>
       <c r="X39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.45983729394134021</v>
       </c>
       <c r="Y39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.43524610969014194</v>
       </c>
       <c r="Z39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.44560180678322497</v>
       </c>
       <c r="AA39" s="10">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.42734673605562634</v>
       </c>
       <c r="AB39" s="10">
-        <f t="shared" ref="AB39" si="51">AB18/AB16</f>
+        <f t="shared" ref="AB39" si="52">AB18/AB16</f>
         <v>0.42913487650329757</v>
       </c>
     </row>
@@ -5453,104 +5453,104 @@
         <v>40</v>
       </c>
       <c r="C40" s="10">
-        <f t="shared" ref="C40:N40" si="52">C22/C16</f>
+        <f t="shared" ref="C40:N40" si="53">C22/C16</f>
         <v>0.13360132419011586</v>
       </c>
       <c r="D40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.11918888471648517</v>
       </c>
       <c r="E40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.11396287328490719</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.23815821110843952</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.12396630342375763</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.1363161039737078</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.10749054630300105</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.12264001269236871</v>
       </c>
       <c r="K40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.10432306497540772</v>
       </c>
       <c r="L40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.1120284927958556</v>
       </c>
       <c r="M40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>6.9926346614606436E-2</v>
       </c>
       <c r="N40" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>2.8926736955934035E-2</v>
       </c>
       <c r="O40" s="10">
-        <f t="shared" ref="O40:P40" si="53">O22/O16</f>
+        <f t="shared" ref="O40:P40" si="54">O22/O16</f>
         <v>7.909556313993174E-2</v>
       </c>
       <c r="P40" s="10">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>8.095276414259274E-2</v>
       </c>
       <c r="Q40" s="10">
-        <f t="shared" ref="Q40:R40" si="54">Q22/Q16</f>
+        <f t="shared" ref="Q40:R40" si="55">Q22/Q16</f>
         <v>4.9029169252593312E-2</v>
       </c>
       <c r="R40" s="10">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.11948596427269413</v>
       </c>
       <c r="S40" s="10"/>
       <c r="T40" s="10">
-        <f t="shared" ref="T40:AA40" si="55">T22/T16</f>
+        <f t="shared" ref="T40:AA40" si="56">T22/T16</f>
         <v>0.12212544989971701</v>
       </c>
       <c r="U40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.12199299537285579</v>
       </c>
       <c r="V40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>8.3282089671951443E-2</v>
       </c>
       <c r="W40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.15575463649018814</v>
       </c>
       <c r="X40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.14290301862556198</v>
       </c>
       <c r="Y40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.11548899779370131</v>
       </c>
       <c r="Z40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.12287294108484872</v>
       </c>
       <c r="AA40" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>7.9941264117126265E-2</v>
       </c>
       <c r="AB40" s="10">
-        <f t="shared" ref="AB40" si="56">AB22/AB16</f>
+        <f t="shared" ref="AB40" si="57">AB22/AB16</f>
         <v>8.1835423940687102E-2</v>
       </c>
     </row>
@@ -5559,104 +5559,104 @@
         <v>41</v>
       </c>
       <c r="C41" s="10">
-        <f t="shared" ref="C41:N41" si="57">C27/C16</f>
+        <f t="shared" ref="C41:N41" si="58">C27/C16</f>
         <v>0.11570899345787027</v>
       </c>
       <c r="D41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9.9962448366503948E-2</v>
       </c>
       <c r="E41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.10008071025020178</v>
       </c>
       <c r="F41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.24128396249098341</v>
       </c>
       <c r="G41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.11206430172347168</v>
       </c>
       <c r="H41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.11786674634000598</v>
       </c>
       <c r="I41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9.4295599002333252E-2</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.11899095668729176</v>
       </c>
       <c r="K41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9.0689446889291564E-2</v>
       </c>
       <c r="L41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9.4139549943338188E-2</v>
       </c>
       <c r="M41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>7.045878072588517E-2</v>
       </c>
       <c r="N41" s="10">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>1.9014147967919257E-2</v>
       </c>
       <c r="O41" s="10">
-        <f t="shared" ref="O41:P41" si="58">O27/O16</f>
+        <f t="shared" ref="O41:P41" si="59">O27/O16</f>
         <v>6.2030716723549491E-2</v>
       </c>
       <c r="P41" s="10">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>6.3732196024784749E-2</v>
       </c>
       <c r="Q41" s="10">
-        <f t="shared" ref="Q41:R41" si="59">Q27/Q16</f>
+        <f t="shared" ref="Q41:R41" si="60">Q27/Q16</f>
         <v>4.6103377959038919E-2</v>
       </c>
       <c r="R41" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>9.7429821363470656E-2</v>
       </c>
       <c r="S41" s="10"/>
       <c r="T41" s="10">
-        <f t="shared" ref="T41:AA41" si="60">T27/T16</f>
+        <f t="shared" ref="T41:AA41" si="61">T27/T16</f>
         <v>5.3108772701046789E-2</v>
       </c>
       <c r="U41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.10299869621903521</v>
       </c>
       <c r="V41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.7882255434056085E-2</v>
       </c>
       <c r="W41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.12858682473393507</v>
       </c>
       <c r="X41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.12943695140226932</v>
       </c>
       <c r="Y41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>9.8990569537458259E-2</v>
       </c>
       <c r="Z41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>0.11097698687745804</v>
       </c>
       <c r="AA41" s="10">
-        <f t="shared" si="60"/>
+        <f t="shared" si="61"/>
         <v>6.9511326092120324E-2</v>
       </c>
       <c r="AB41" s="10">
-        <f t="shared" ref="AB41" si="61">AB27/AB16</f>
+        <f t="shared" ref="AB41" si="62">AB27/AB16</f>
         <v>6.6985645933014357E-2</v>
       </c>
     </row>
@@ -5665,92 +5665,92 @@
         <v>42</v>
       </c>
       <c r="C42" s="10">
-        <f t="shared" ref="C42:N42" si="62">C26/C25</f>
+        <f t="shared" ref="C42:N42" si="63">C26/C25</f>
         <v>0.19693654266958424</v>
       </c>
       <c r="D42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.19333333333333333</v>
       </c>
       <c r="E42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.16046039268788084</v>
       </c>
       <c r="F42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>-0.18337264150943397</v>
       </c>
       <c r="G42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.12014563106796117</v>
       </c>
       <c r="H42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.17898022892819979</v>
       </c>
       <c r="I42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.16524216524216523</v>
       </c>
       <c r="J42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.13093858632676708</v>
       </c>
       <c r="K42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.19586840091813312</v>
       </c>
       <c r="L42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.1786723163841808</v>
       </c>
       <c r="M42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>5.9241706161137442E-2</v>
       </c>
       <c r="N42" s="10">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0.33647798742138363</v>
       </c>
       <c r="O42" s="10">
-        <f t="shared" ref="O42:P42" si="63">O26/O25</f>
+        <f t="shared" ref="O42:P42" si="64">O26/O25</f>
         <v>0.21149674620390455</v>
       </c>
       <c r="P42" s="10">
-        <f t="shared" si="63"/>
+        <f t="shared" si="64"/>
         <v>0.2072072072072072</v>
       </c>
       <c r="Q42" s="10">
-        <f t="shared" ref="Q42:R42" si="64">Q26/Q25</f>
+        <f t="shared" ref="Q42:R42" si="65">Q26/Q25</f>
         <v>0.2</v>
       </c>
       <c r="R42" s="10">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0.19563581640331076</v>
       </c>
       <c r="S42" s="10"/>
       <c r="T42" s="10">
-        <f t="shared" ref="T42:Y42" si="65">T26/T25</f>
+        <f t="shared" ref="T42:Y42" si="66">T26/T25</f>
         <v>0.55306358381502885</v>
       </c>
       <c r="U42" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.16079983336804832</v>
       </c>
       <c r="V42" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.12054035330793211</v>
       </c>
       <c r="W42" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.14021918630836211</v>
       </c>
       <c r="X42" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>9.0963764847391368E-2</v>
       </c>
       <c r="Y42" s="10">
-        <f t="shared" si="65"/>
+        <f t="shared" si="66"/>
         <v>0.18238993710691823</v>
       </c>
       <c r="Z42" s="10">
@@ -6144,31 +6144,31 @@
         <v>51</v>
       </c>
       <c r="C52" s="8">
-        <f t="shared" ref="C52:I52" si="66">SUM(C47:C51)</f>
+        <f t="shared" ref="C52:I52" si="67">SUM(C47:C51)</f>
         <v>0</v>
       </c>
       <c r="D52" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="E52" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>25202</v>
       </c>
       <c r="F52" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>0</v>
       </c>
       <c r="G52" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>24250</v>
       </c>
       <c r="H52" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>24631</v>
       </c>
       <c r="I52" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>24753</v>
       </c>
       <c r="J52" s="8">
@@ -6188,39 +6188,39 @@
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
       <c r="T52" s="8">
-        <f t="shared" ref="T52:AB52" si="67">SUM(T47:T51)</f>
+        <f t="shared" ref="T52:AB52" si="68">SUM(T47:T51)</f>
         <v>15134</v>
       </c>
       <c r="U52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>16525</v>
       </c>
       <c r="V52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>20556</v>
       </c>
       <c r="W52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>26291</v>
       </c>
       <c r="X52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>28213</v>
       </c>
       <c r="Y52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>25202</v>
       </c>
       <c r="Z52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>25382</v>
       </c>
       <c r="AA52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>23362</v>
       </c>
       <c r="AB52" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="68"/>
         <v>24603</v>
       </c>
       <c r="AC52" s="5"/>
@@ -6566,31 +6566,31 @@
         <v>57</v>
       </c>
       <c r="C58" s="8">
-        <f t="shared" ref="C58:I58" si="68">SUM(C53:C57)</f>
+        <f t="shared" ref="C58:I58" si="69">SUM(C53:C57)</f>
         <v>0</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="E58" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>12329</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>0</v>
       </c>
       <c r="G58" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>12536</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>12572</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>12603</v>
       </c>
       <c r="J58" s="8">
@@ -6610,39 +6610,39 @@
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
       <c r="T58" s="8">
-        <f t="shared" ref="T58:AB58" si="69">SUM(T53:T57)</f>
+        <f t="shared" ref="T58:AB58" si="70">SUM(T53:T57)</f>
         <v>7402</v>
       </c>
       <c r="U58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>7192</v>
       </c>
       <c r="V58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>10786</v>
       </c>
       <c r="W58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>11449</v>
       </c>
       <c r="X58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>12108</v>
       </c>
       <c r="Y58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>12329</v>
       </c>
       <c r="Z58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>12728</v>
       </c>
       <c r="AA58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>13217</v>
       </c>
       <c r="AB58" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>13807</v>
       </c>
       <c r="AC58" s="5"/>
@@ -6693,31 +6693,31 @@
         <v>58</v>
       </c>
       <c r="C60" s="8">
-        <f t="shared" ref="C60:I60" si="70">C58+C52</f>
+        <f t="shared" ref="C60:I60" si="71">C58+C52</f>
         <v>0</v>
       </c>
       <c r="D60" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="E60" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>37531</v>
       </c>
       <c r="F60" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>0</v>
       </c>
       <c r="G60" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>36786</v>
       </c>
       <c r="H60" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>37203</v>
       </c>
       <c r="I60" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>37356</v>
       </c>
       <c r="J60" s="8">
@@ -6737,39 +6737,39 @@
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
       <c r="T60" s="8">
-        <f t="shared" ref="T60:AB60" si="71">T58+T52</f>
+        <f t="shared" ref="T60:AB60" si="72">T58+T52</f>
         <v>22536</v>
       </c>
       <c r="U60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>23717</v>
       </c>
       <c r="V60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>31342</v>
       </c>
       <c r="W60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>37740</v>
       </c>
       <c r="X60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>40321</v>
       </c>
       <c r="Y60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>37531</v>
       </c>
       <c r="Z60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>38110</v>
       </c>
       <c r="AA60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>36579</v>
       </c>
       <c r="AB60" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>38410</v>
       </c>
       <c r="AC60" s="5"/>
@@ -6969,7 +6969,7 @@
         <v>6</v>
       </c>
       <c r="Z64" s="5">
-        <f t="shared" ref="Z64" si="72">I64</f>
+        <f t="shared" ref="Z64" si="73">I64</f>
         <v>6</v>
       </c>
       <c r="AA64" s="5">
@@ -7255,31 +7255,31 @@
         <v>51</v>
       </c>
       <c r="C69" s="8">
-        <f t="shared" ref="C69:I69" si="73">SUM(C63:C68)</f>
+        <f t="shared" ref="C69:I69" si="74">SUM(C63:C68)</f>
         <v>0</v>
       </c>
       <c r="D69" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="E69" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>9256</v>
       </c>
       <c r="F69" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>0</v>
       </c>
       <c r="G69" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8461</v>
       </c>
       <c r="H69" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>8999</v>
       </c>
       <c r="I69" s="8">
-        <f t="shared" si="73"/>
+        <f t="shared" si="74"/>
         <v>9029</v>
       </c>
       <c r="J69" s="8">
@@ -7299,39 +7299,39 @@
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
       <c r="T69" s="8">
-        <f t="shared" ref="T69:V69" si="74">SUM(T63:T68)</f>
+        <f t="shared" ref="T69:V69" si="75">SUM(T63:T68)</f>
         <v>6040</v>
       </c>
       <c r="U69" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>7866</v>
       </c>
       <c r="V69" s="8">
-        <f t="shared" si="74"/>
+        <f t="shared" si="75"/>
         <v>8284</v>
       </c>
       <c r="W69" s="8">
-        <f t="shared" ref="W69" si="75">SUM(W63:W68)</f>
+        <f t="shared" ref="W69" si="76">SUM(W63:W68)</f>
         <v>9674</v>
       </c>
       <c r="X69" s="8">
-        <f t="shared" ref="X69" si="76">SUM(X63:X68)</f>
+        <f t="shared" ref="X69" si="77">SUM(X63:X68)</f>
         <v>10730</v>
       </c>
       <c r="Y69" s="8">
-        <f t="shared" ref="Y69" si="77">SUM(Y63:Y68)</f>
+        <f t="shared" ref="Y69" si="78">SUM(Y63:Y68)</f>
         <v>9256</v>
       </c>
       <c r="Z69" s="8">
-        <f t="shared" ref="Z69:AB69" si="78">SUM(Z63:Z68)</f>
+        <f t="shared" ref="Z69:AB69" si="79">SUM(Z63:Z68)</f>
         <v>10593</v>
       </c>
       <c r="AA69" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>10566</v>
       </c>
       <c r="AB69" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="79"/>
         <v>12547</v>
       </c>
       <c r="AC69" s="5"/>
@@ -7545,31 +7545,31 @@
         <v>69</v>
       </c>
       <c r="C73" s="8">
-        <f t="shared" ref="C73:I73" si="79">SUM(C70:C72)</f>
+        <f t="shared" ref="C73:I73" si="80">SUM(C70:C72)</f>
         <v>0</v>
       </c>
       <c r="D73" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="E73" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>14271</v>
       </c>
       <c r="F73" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="G73" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>14354</v>
       </c>
       <c r="H73" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>14058</v>
       </c>
       <c r="I73" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>14101</v>
       </c>
       <c r="J73" s="8">
@@ -7589,39 +7589,39 @@
       <c r="R73" s="5"/>
       <c r="S73" s="5"/>
       <c r="T73" s="8">
-        <f t="shared" ref="T73:AB73" si="80">SUM(T70:T72)</f>
+        <f t="shared" ref="T73:AB73" si="81">SUM(T70:T72)</f>
         <v>6684</v>
       </c>
       <c r="U73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>6811</v>
       </c>
       <c r="V73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>15003</v>
       </c>
       <c r="W73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>15299</v>
       </c>
       <c r="X73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>14310</v>
       </c>
       <c r="Y73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>14271</v>
       </c>
       <c r="Z73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>13087</v>
       </c>
       <c r="AA73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>12800</v>
       </c>
       <c r="AB73" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>10998</v>
       </c>
       <c r="AC73" s="5"/>
@@ -7672,31 +7672,31 @@
         <v>70</v>
       </c>
       <c r="C75" s="8">
-        <f t="shared" ref="C75:I75" si="81">C73+C69</f>
+        <f t="shared" ref="C75:I75" si="82">C73+C69</f>
         <v>0</v>
       </c>
       <c r="D75" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="E75" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>23527</v>
       </c>
       <c r="F75" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0</v>
       </c>
       <c r="G75" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>22815</v>
       </c>
       <c r="H75" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>23057</v>
       </c>
       <c r="I75" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>23130</v>
       </c>
       <c r="J75" s="8">
@@ -7716,39 +7716,39 @@
       <c r="R75" s="5"/>
       <c r="S75" s="5"/>
       <c r="T75" s="8">
-        <f t="shared" ref="T75:AB75" si="82">T73+T69</f>
+        <f t="shared" ref="T75:AB75" si="83">T73+T69</f>
         <v>12724</v>
       </c>
       <c r="U75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>14677</v>
       </c>
       <c r="V75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>23287</v>
       </c>
       <c r="W75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>24973</v>
       </c>
       <c r="X75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>25040</v>
       </c>
       <c r="Y75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>23527</v>
       </c>
       <c r="Z75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>23680</v>
       </c>
       <c r="AA75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>23366</v>
       </c>
       <c r="AB75" s="8">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>23545</v>
       </c>
       <c r="AC75" s="5"/>
@@ -8157,31 +8157,31 @@
         <v>77</v>
       </c>
       <c r="C83" s="8">
-        <f t="shared" ref="C83:I83" si="83">SUM(C78:C82)</f>
+        <f t="shared" ref="C83:I83" si="84">SUM(C78:C82)</f>
         <v>0</v>
       </c>
       <c r="D83" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="E83" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>14004</v>
       </c>
       <c r="F83" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>0</v>
       </c>
       <c r="G83" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>13971</v>
       </c>
       <c r="H83" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>14146</v>
       </c>
       <c r="I83" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>14226</v>
       </c>
       <c r="J83" s="8">
@@ -8200,39 +8200,39 @@
       <c r="R83" s="5"/>
       <c r="S83" s="5"/>
       <c r="T83" s="8">
-        <f t="shared" ref="T83:AB83" si="84">SUM(T78:T82)</f>
+        <f t="shared" ref="T83:AB83" si="85">SUM(T78:T82)</f>
         <v>9812</v>
       </c>
       <c r="U83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>9040</v>
       </c>
       <c r="V83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>8055</v>
       </c>
       <c r="W83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>12767</v>
       </c>
       <c r="X83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>15281</v>
       </c>
       <c r="Y83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>14004</v>
       </c>
       <c r="Z83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>14430</v>
       </c>
       <c r="AA83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>13213</v>
       </c>
       <c r="AB83" s="8">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>14865</v>
       </c>
       <c r="AC83" s="5"/>
@@ -8283,19 +8283,19 @@
         <v>78</v>
       </c>
       <c r="C85" s="8">
-        <f t="shared" ref="C85:I85" si="85">C83+C75</f>
+        <f t="shared" ref="C85:I85" si="86">C83+C75</f>
         <v>0</v>
       </c>
       <c r="D85" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="E85" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>37531</v>
       </c>
       <c r="F85" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>0</v>
       </c>
       <c r="G85" s="8">
@@ -8303,11 +8303,11 @@
         <v>36786</v>
       </c>
       <c r="H85" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>37203</v>
       </c>
       <c r="I85" s="8">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>37356</v>
       </c>
       <c r="J85" s="8">
@@ -8331,35 +8331,35 @@
         <v>22536</v>
       </c>
       <c r="U85" s="8">
-        <f t="shared" ref="U85:AB85" si="86">U83+U75</f>
+        <f t="shared" ref="U85:AB85" si="87">U83+U75</f>
         <v>23717</v>
       </c>
       <c r="V85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>31342</v>
       </c>
       <c r="W85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>37740</v>
       </c>
       <c r="X85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>40321</v>
       </c>
       <c r="Y85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>37531</v>
       </c>
       <c r="Z85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>38110</v>
       </c>
       <c r="AA85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>36579</v>
       </c>
       <c r="AB85" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>38410</v>
       </c>
       <c r="AC85" s="5"/>
@@ -8451,35 +8451,35 @@
         <v>80</v>
       </c>
       <c r="C88" s="5">
-        <f t="shared" ref="C88:J88" si="87">C27</f>
+        <f t="shared" ref="C88:J88" si="88">C27</f>
         <v>1468</v>
       </c>
       <c r="D88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1331</v>
       </c>
       <c r="E88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1240</v>
       </c>
       <c r="F88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2007</v>
       </c>
       <c r="G88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1450</v>
       </c>
       <c r="H88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1578</v>
       </c>
       <c r="I88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1172</v>
       </c>
       <c r="J88" s="5">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1500</v>
       </c>
       <c r="K88" s="5"/>
@@ -8492,39 +8492,39 @@
       <c r="R88" s="5"/>
       <c r="S88" s="5"/>
       <c r="T88" s="5">
-        <f t="shared" ref="T88:AB88" si="88">T27</f>
+        <f t="shared" ref="T88:AB88" si="89">T27</f>
         <v>1933</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>4029</v>
       </c>
       <c r="V88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>2539</v>
       </c>
       <c r="W88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>5727</v>
       </c>
       <c r="X88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>6046</v>
       </c>
       <c r="Y88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>5070</v>
       </c>
       <c r="Z88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>5700</v>
       </c>
       <c r="AA88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>3219</v>
       </c>
       <c r="AB88" s="5">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>3108</v>
       </c>
       <c r="AC88" s="5"/>
@@ -8910,7 +8910,7 @@
       <c r="AA95" s="5">
         <v>-257</v>
       </c>
-      <c r="AB95" s="87">
+      <c r="AB95" s="82">
         <v>-1207</v>
       </c>
       <c r="AC95" s="5"/>
@@ -8968,7 +8968,7 @@
       <c r="AA96" s="5">
         <v>120</v>
       </c>
-      <c r="AB96" s="87">
+      <c r="AB96" s="82">
         <v>-31</v>
       </c>
       <c r="AC96" s="5"/>
@@ -9100,31 +9100,31 @@
         <v>92</v>
       </c>
       <c r="C99" s="5">
-        <f t="shared" ref="C99:I99" si="89">SUM(C95:C98)</f>
+        <f t="shared" ref="C99:I99" si="90">SUM(C95:C98)</f>
         <v>0</v>
       </c>
       <c r="D99" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="E99" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="F99" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="G99" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="H99" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>0</v>
       </c>
       <c r="I99" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-285</v>
       </c>
       <c r="J99" s="5">
@@ -9141,39 +9141,39 @@
       <c r="R99" s="5"/>
       <c r="S99" s="5"/>
       <c r="T99" s="5">
-        <f t="shared" ref="T99:AB99" si="90">SUM(T95:T98)</f>
+        <f t="shared" ref="T99:AB99" si="91">SUM(T95:T98)</f>
         <v>1482</v>
       </c>
       <c r="U99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>562</v>
       </c>
       <c r="V99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-1245</v>
       </c>
       <c r="W99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>45</v>
       </c>
       <c r="X99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-1660</v>
       </c>
       <c r="Y99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-513</v>
       </c>
       <c r="Z99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>716</v>
       </c>
       <c r="AA99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-787</v>
       </c>
       <c r="AB99" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>-1678</v>
       </c>
       <c r="AC99" s="5"/>
@@ -9189,31 +9189,31 @@
         <v>91</v>
       </c>
       <c r="C100" s="8">
-        <f t="shared" ref="C100:I100" si="91">C88+SUM(C89:C93)+C99</f>
+        <f t="shared" ref="C100:I100" si="92">C88+SUM(C89:C93)+C99</f>
         <v>1468</v>
       </c>
       <c r="D100" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1331</v>
       </c>
       <c r="E100" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1240</v>
       </c>
       <c r="F100" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>2007</v>
       </c>
       <c r="G100" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1450</v>
       </c>
       <c r="H100" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1578</v>
       </c>
       <c r="I100" s="8">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>1783</v>
       </c>
       <c r="J100" s="8">
@@ -9230,39 +9230,39 @@
       <c r="R100" s="5"/>
       <c r="S100" s="5"/>
       <c r="T100" s="8">
-        <f t="shared" ref="T100:AB100" si="92">T88+SUM(T89:T93)+T99</f>
+        <f t="shared" ref="T100:AB100" si="93">T88+SUM(T89:T93)+T99</f>
         <v>4955</v>
       </c>
       <c r="U100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5903</v>
       </c>
       <c r="V100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2485</v>
       </c>
       <c r="W100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>6657</v>
       </c>
       <c r="X100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5188</v>
       </c>
       <c r="Y100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>5841</v>
       </c>
       <c r="Z100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>7429</v>
       </c>
       <c r="AA100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>3698</v>
       </c>
       <c r="AB100" s="8">
-        <f t="shared" si="92"/>
+        <f t="shared" si="93"/>
         <v>2868</v>
       </c>
       <c r="AC100" s="5"/>
@@ -9558,31 +9558,31 @@
         <v>106</v>
       </c>
       <c r="C106" s="8">
-        <f t="shared" ref="C106:I106" si="93">SUM(C101:C105)</f>
+        <f t="shared" ref="C106:I106" si="94">SUM(C101:C105)</f>
         <v>0</v>
       </c>
       <c r="D106" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="E106" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="F106" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="G106" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="H106" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="I106" s="8">
-        <f t="shared" si="93"/>
+        <f t="shared" si="94"/>
         <v>0</v>
       </c>
       <c r="J106" s="8">
@@ -9599,39 +9599,39 @@
       <c r="R106" s="5"/>
       <c r="S106" s="5"/>
       <c r="T106" s="8">
-        <f t="shared" ref="T106:AB106" si="94">SUM(T101:T105)</f>
+        <f t="shared" ref="T106:AB106" si="95">SUM(T101:T105)</f>
         <v>276</v>
       </c>
       <c r="U106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-264</v>
       </c>
       <c r="V106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-1028</v>
       </c>
       <c r="W106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-3800</v>
       </c>
       <c r="X106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-1524</v>
       </c>
       <c r="Y106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>564</v>
       </c>
       <c r="Z106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>894</v>
       </c>
       <c r="AA106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-275</v>
       </c>
       <c r="AB106" s="8">
-        <f t="shared" si="94"/>
+        <f t="shared" si="95"/>
         <v>-488</v>
       </c>
       <c r="AC106" s="5"/>
@@ -9796,7 +9796,7 @@
       <c r="Z109" s="5">
         <v>0</v>
       </c>
-      <c r="AA109" s="87">
+      <c r="AA109" s="82">
         <v>-1000</v>
       </c>
       <c r="AB109" s="5">
@@ -10043,31 +10043,31 @@
         <v>0</v>
       </c>
       <c r="D114" s="8">
-        <f t="shared" ref="D114:J114" si="95">SUM(D108:D113)</f>
+        <f t="shared" ref="D114:J114" si="96">SUM(D108:D113)</f>
         <v>0</v>
       </c>
       <c r="E114" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="F114" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="G114" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="H114" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="I114" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="J114" s="8">
-        <f t="shared" si="95"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="K114" s="8"/>
@@ -10080,23 +10080,23 @@
       <c r="R114" s="5"/>
       <c r="S114" s="5"/>
       <c r="T114" s="8">
-        <f t="shared" ref="T114:X114" si="96">SUM(T107:T113)</f>
+        <f t="shared" ref="T114:X114" si="97">SUM(T107:T113)</f>
         <v>-4835</v>
       </c>
       <c r="U114" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>-5293</v>
       </c>
       <c r="V114" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>2491</v>
       </c>
       <c r="W114" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>-1459</v>
       </c>
       <c r="X114" s="8">
-        <f t="shared" si="96"/>
+        <f t="shared" si="97"/>
         <v>-4836</v>
       </c>
       <c r="Y114" s="8">
@@ -10104,15 +10104,15 @@
         <v>-7447</v>
       </c>
       <c r="Z114" s="8">
-        <f t="shared" ref="Z114:AB114" si="97">SUM(Z108:Z113)</f>
+        <f t="shared" ref="Z114:AB114" si="98">SUM(Z108:Z113)</f>
         <v>-5888</v>
       </c>
       <c r="AA114" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-5820</v>
       </c>
       <c r="AB114" s="8">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>-2292</v>
       </c>
       <c r="AC114" s="5"/>
@@ -10188,31 +10188,31 @@
         <v>1468</v>
       </c>
       <c r="D116" s="8">
-        <f t="shared" ref="D116:J116" si="98">D100+D106+D114+D115</f>
+        <f t="shared" ref="D116:J116" si="99">D100+D106+D114+D115</f>
         <v>1331</v>
       </c>
       <c r="E116" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1240</v>
       </c>
       <c r="F116" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>2007</v>
       </c>
       <c r="G116" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1450</v>
       </c>
       <c r="H116" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1578</v>
       </c>
       <c r="I116" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1783</v>
       </c>
       <c r="J116" s="8">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>1500</v>
       </c>
       <c r="K116" s="8"/>
@@ -10225,39 +10225,39 @@
       <c r="R116" s="5"/>
       <c r="S116" s="5"/>
       <c r="T116" s="8">
-        <f t="shared" ref="T116" si="99">T100+T106+T114+T115</f>
+        <f t="shared" ref="T116" si="100">T100+T106+T114+T115</f>
         <v>441</v>
       </c>
       <c r="U116" s="8">
-        <f t="shared" ref="U116" si="100">U100+U106+U114+U115</f>
+        <f t="shared" ref="U116" si="101">U100+U106+U114+U115</f>
         <v>217</v>
       </c>
       <c r="V116" s="8">
-        <f t="shared" ref="V116" si="101">V100+V106+V114+V115</f>
+        <f t="shared" ref="V116" si="102">V100+V106+V114+V115</f>
         <v>3882</v>
       </c>
       <c r="W116" s="8">
-        <f t="shared" ref="W116" si="102">W100+W106+W114+W115</f>
+        <f t="shared" ref="W116" si="103">W100+W106+W114+W115</f>
         <v>1541</v>
       </c>
       <c r="X116" s="8">
-        <f t="shared" ref="X116" si="103">X100+X106+X114+X115</f>
+        <f t="shared" ref="X116" si="104">X100+X106+X114+X115</f>
         <v>-1315</v>
       </c>
       <c r="Y116" s="8">
-        <f t="shared" ref="Y116" si="104">Y100+Y106+Y114+Y115</f>
+        <f t="shared" ref="Y116" si="105">Y100+Y106+Y114+Y115</f>
         <v>-1133</v>
       </c>
       <c r="Z116" s="8">
-        <f t="shared" ref="Z116:AB116" si="105">Z100+Z106+Z114+Z115</f>
+        <f t="shared" ref="Z116:AB116" si="106">Z100+Z106+Z114+Z115</f>
         <v>2419</v>
       </c>
       <c r="AA116" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>-2396</v>
       </c>
       <c r="AB116" s="8">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>99</v>
       </c>
       <c r="AC116" s="5"/>
@@ -10351,7 +10351,7 @@
         <f>Y119</f>
         <v>7441</v>
       </c>
-      <c r="AA118" s="87">
+      <c r="AA118" s="82">
         <f>+Z119</f>
         <v>9860</v>
       </c>
@@ -14195,19 +14195,19 @@
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B66" s="66"/>
-      <c r="C66" s="81" t="s">
+      <c r="C66" s="83" t="s">
         <v>189</v>
       </c>
-      <c r="D66" s="81"/>
-      <c r="E66" s="81"/>
-      <c r="F66" s="81"/>
-      <c r="G66" s="81"/>
-      <c r="H66" s="81"/>
-      <c r="I66" s="81"/>
-      <c r="J66" s="82"/>
+      <c r="D66" s="83"/>
+      <c r="E66" s="83"/>
+      <c r="F66" s="83"/>
+      <c r="G66" s="83"/>
+      <c r="H66" s="83"/>
+      <c r="I66" s="83"/>
+      <c r="J66" s="84"/>
     </row>
     <row r="67" spans="2:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B67" s="83" t="s">
+      <c r="B67" s="85" t="s">
         <v>187</v>
       </c>
       <c r="C67" s="67"/>
@@ -14220,7 +14220,7 @@
       <c r="J67" s="68"/>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B68" s="83"/>
+      <c r="B68" s="85"/>
       <c r="C68" s="69"/>
       <c r="D68" s="70"/>
       <c r="E68" s="70"/>
@@ -14231,7 +14231,7 @@
       <c r="J68" s="70"/>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B69" s="83"/>
+      <c r="B69" s="85"/>
       <c r="C69" s="69"/>
       <c r="D69" s="70"/>
       <c r="E69" s="70"/>
@@ -14242,7 +14242,7 @@
       <c r="J69" s="70"/>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B70" s="83"/>
+      <c r="B70" s="85"/>
       <c r="C70" s="69"/>
       <c r="D70" s="70"/>
       <c r="E70" s="70"/>
@@ -14253,7 +14253,7 @@
       <c r="J70" s="70"/>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B71" s="83"/>
+      <c r="B71" s="85"/>
       <c r="C71" s="69"/>
       <c r="D71" s="70"/>
       <c r="E71" s="70"/>
@@ -14264,7 +14264,7 @@
       <c r="J71" s="70"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B72" s="83"/>
+      <c r="B72" s="85"/>
       <c r="C72" s="69"/>
       <c r="D72" s="70"/>
       <c r="E72" s="70"/>
@@ -14275,7 +14275,7 @@
       <c r="J72" s="70"/>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B73" s="83"/>
+      <c r="B73" s="85"/>
       <c r="C73" s="69"/>
       <c r="D73" s="70"/>
       <c r="E73" s="70"/>
@@ -14286,7 +14286,7 @@
       <c r="J73" s="70"/>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B74" s="84"/>
+      <c r="B74" s="86"/>
       <c r="C74" s="69"/>
       <c r="D74" s="70"/>
       <c r="E74" s="70"/>
@@ -14619,16 +14619,16 @@
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="85" t="s">
+      <c r="B48" s="87" t="s">
         <v>275</v>
       </c>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="H48" s="85" t="s">
+      <c r="C48" s="87"/>
+      <c r="D48" s="87"/>
+      <c r="H48" s="87" t="s">
         <v>276</v>
       </c>
-      <c r="I48" s="85"/>
-      <c r="J48" s="85"/>
+      <c r="I48" s="87"/>
+      <c r="J48" s="87"/>
     </row>
     <row r="49" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">
